--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy.xlsx
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>23.47936179982776</v>
+        <v>23.47936180407328</v>
       </c>
       <c r="E2">
         <v>36.7783252635105</v>
@@ -645,139 +645,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H2">
-        <v>28.25677527384965</v>
+        <v>28.25677526734539</v>
       </c>
       <c r="I2">
-        <v>0.4226732163016362</v>
+        <v>0.4226732165496458</v>
       </c>
       <c r="J2">
-        <v>0.398603495011786</v>
+        <v>0.398603495288631</v>
       </c>
       <c r="K2">
-        <v>23.62393146363803</v>
+        <v>23.62393146726979</v>
       </c>
       <c r="L2">
-        <v>0.6138839211684494</v>
+        <v>0.6138839210747038</v>
       </c>
       <c r="M2">
-        <v>0.5796215309538708</v>
+        <v>0.5796215308245597</v>
       </c>
       <c r="N2">
-        <v>22.70884395372683</v>
+        <v>22.70884395349958</v>
       </c>
       <c r="O2">
-        <v>0.6560003917844555</v>
+        <v>0.6560003917465025</v>
       </c>
       <c r="P2">
-        <v>0.6115443543940347</v>
+        <v>0.6115443544017672</v>
       </c>
       <c r="Q2">
-        <v>22.37350123445112</v>
+        <v>22.3735012379858</v>
       </c>
       <c r="R2">
-        <v>0.6763348182047245</v>
+        <v>0.6763348180698748</v>
       </c>
       <c r="S2">
-        <v>0.6229120939490871</v>
+        <v>0.6229120938299625</v>
       </c>
       <c r="T2">
-        <v>22.7656038839328</v>
+        <v>22.76560388406136</v>
       </c>
       <c r="U2">
-        <v>0.7075797549612501</v>
+        <v>0.7075797549555246</v>
       </c>
       <c r="V2">
-        <v>0.6094901072200055</v>
+        <v>0.6094901072175753</v>
       </c>
       <c r="W2">
-        <v>22.05782140378277</v>
+        <v>22.05782140459604</v>
       </c>
       <c r="X2">
-        <v>0.7169462343775983</v>
+        <v>0.7169462340363307</v>
       </c>
       <c r="Y2">
-        <v>0.6333952788413868</v>
+        <v>0.6333952788198499</v>
       </c>
       <c r="Z2">
-        <v>21.92155975146008</v>
+        <v>21.92155976930881</v>
       </c>
       <c r="AA2">
-        <v>0.736819128221714</v>
+        <v>0.7368191274659995</v>
       </c>
       <c r="AB2">
-        <v>0.6378565372190187</v>
+        <v>0.6378565366366508</v>
       </c>
       <c r="AC2">
-        <v>22.55024015281616</v>
+        <v>22.55024017814146</v>
       </c>
       <c r="AD2">
-        <v>0.7562501938920931</v>
+        <v>0.7562501931513435</v>
       </c>
       <c r="AE2">
-        <v>0.616711841009653</v>
+        <v>0.6167118401602516</v>
       </c>
       <c r="AF2">
-        <v>22.24582072836179</v>
+        <v>22.24582076989791</v>
       </c>
       <c r="AG2">
-        <v>0.76129717022153</v>
+        <v>0.7612971694326165</v>
       </c>
       <c r="AH2">
-        <v>0.6269624440033628</v>
+        <v>0.6269624426194733</v>
       </c>
       <c r="AI2">
-        <v>22.80961847129263</v>
+        <v>22.80961848918046</v>
       </c>
       <c r="AJ2">
-        <v>0.7675591744150942</v>
+        <v>0.7675591736703034</v>
       </c>
       <c r="AK2">
-        <v>0.6077367071259279</v>
+        <v>0.6077367065273679</v>
       </c>
       <c r="AL2">
-        <v>23.13085951550166</v>
+        <v>23.13085953238961</v>
       </c>
       <c r="AM2">
-        <v>0.7830358521120926</v>
+        <v>0.7830358509581677</v>
       </c>
       <c r="AN2">
-        <v>0.5965602976620978</v>
+        <v>0.5965602970734857</v>
       </c>
       <c r="AO2">
-        <v>24.39420199430904</v>
+        <v>24.394201934821</v>
       </c>
       <c r="AP2">
-        <v>0.7904921357124712</v>
+        <v>0.7904921346024287</v>
       </c>
       <c r="AQ2">
-        <v>0.5512259691986484</v>
+        <v>0.5512259714194218</v>
       </c>
       <c r="AR2">
-        <v>26.00661440017483</v>
+        <v>26.00661446553497</v>
       </c>
       <c r="AS2">
-        <v>0.8137724041543795</v>
+        <v>0.8137724051334142</v>
       </c>
       <c r="AT2">
-        <v>0.4899418299502862</v>
+        <v>0.4899418273956984</v>
       </c>
       <c r="AU2">
-        <v>27.38000470279729</v>
+        <v>27.38000482911537</v>
       </c>
       <c r="AV2">
-        <v>0.830437527315436</v>
+        <v>0.8304375322839344</v>
       </c>
       <c r="AW2">
-        <v>0.4346285606088682</v>
+        <v>0.4346285553972464</v>
       </c>
       <c r="AX2">
-        <v>27.99177357246779</v>
+        <v>27.99177348176308</v>
       </c>
       <c r="AY2">
-        <v>0.8417037666528494</v>
+        <v>0.8417037713012822</v>
       </c>
       <c r="AZ2">
-        <v>0.4090620257545803</v>
+        <v>0.4090620296286822</v>
       </c>
     </row>
     <row r="3">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>23.2717955775616</v>
+        <v>23.27179557147898</v>
       </c>
       <c r="E3">
         <v>36.7783252635105</v>
@@ -809,139 +809,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H3">
-        <v>26.73229248942049</v>
+        <v>26.73229259788859</v>
       </c>
       <c r="I3">
-        <v>0.5005860439610934</v>
+        <v>0.5005860390060386</v>
       </c>
       <c r="J3">
-        <v>0.4617014151424073</v>
+        <v>0.4617014107796591</v>
       </c>
       <c r="K3">
-        <v>23.1301234718599</v>
+        <v>23.13012344976263</v>
       </c>
       <c r="L3">
-        <v>0.6329577775013353</v>
+        <v>0.6329577775419658</v>
       </c>
       <c r="M3">
-        <v>0.5970153335015437</v>
+        <v>0.5970153342728549</v>
       </c>
       <c r="N3">
-        <v>23.47972326849572</v>
+        <v>23.47972323814935</v>
       </c>
       <c r="O3">
-        <v>0.6495964726922731</v>
+        <v>0.6495964732770507</v>
       </c>
       <c r="P3">
-        <v>0.5847151295184726</v>
+        <v>0.5847151305930663</v>
       </c>
       <c r="Q3">
-        <v>24.66771866951647</v>
+        <v>24.66771851689426</v>
       </c>
       <c r="R3">
-        <v>0.6993756497156882</v>
+        <v>0.6993756488499419</v>
       </c>
       <c r="S3">
-        <v>0.5414156004513765</v>
+        <v>0.5414156061427675</v>
       </c>
       <c r="T3">
-        <v>23.82910875232461</v>
+        <v>23.82910870614025</v>
       </c>
       <c r="U3">
-        <v>0.7126751045868035</v>
+        <v>0.7126751050893465</v>
       </c>
       <c r="V3">
-        <v>0.57218006600289</v>
+        <v>0.5721800676545056</v>
       </c>
       <c r="W3">
-        <v>23.83094093948123</v>
+        <v>23.83094078507454</v>
       </c>
       <c r="X3">
-        <v>0.7413693517109444</v>
+        <v>0.7413693552327163</v>
       </c>
       <c r="Y3">
-        <v>0.572126667696974</v>
+        <v>0.5721266732559012</v>
       </c>
       <c r="Z3">
-        <v>25.01781663408177</v>
+        <v>25.01781633236414</v>
       </c>
       <c r="AA3">
-        <v>0.7652751634870232</v>
+        <v>0.7652751710533382</v>
       </c>
       <c r="AB3">
-        <v>0.5283849928401205</v>
+        <v>0.5283850042428816</v>
       </c>
       <c r="AC3">
-        <v>25.4716648375746</v>
+        <v>25.47166442745173</v>
       </c>
       <c r="AD3">
-        <v>0.7825354032661584</v>
+        <v>0.7825354157825678</v>
       </c>
       <c r="AE3">
-        <v>0.5110956021363765</v>
+        <v>0.5110956178832888</v>
       </c>
       <c r="AF3">
-        <v>26.68624568951991</v>
+        <v>26.68624497589242</v>
       </c>
       <c r="AG3">
-        <v>0.801213664010606</v>
+        <v>0.8012136802931529</v>
       </c>
       <c r="AH3">
-        <v>0.463247882323941</v>
+        <v>0.4632479110495982</v>
       </c>
       <c r="AI3">
-        <v>27.14791857375612</v>
+        <v>27.14791725769016</v>
       </c>
       <c r="AJ3">
-        <v>0.8170582807549697</v>
+        <v>0.817058301182893</v>
       </c>
       <c r="AK3">
-        <v>0.4444102361469563</v>
+        <v>0.4444102901054736</v>
       </c>
       <c r="AL3">
-        <v>27.78449469665567</v>
+        <v>27.78449255687448</v>
       </c>
       <c r="AM3">
-        <v>0.8414621102586555</v>
+        <v>0.841462132457485</v>
       </c>
       <c r="AN3">
-        <v>0.4180254343813385</v>
+        <v>0.418025524288794</v>
       </c>
       <c r="AO3">
-        <v>28.80245054738698</v>
+        <v>28.8024477668035</v>
       </c>
       <c r="AP3">
-        <v>0.8532896308971735</v>
+        <v>0.8532896516445603</v>
       </c>
       <c r="AQ3">
-        <v>0.3746319375996299</v>
+        <v>0.3746320583875278</v>
       </c>
       <c r="AR3">
-        <v>29.50270845883072</v>
+        <v>29.50270465386195</v>
       </c>
       <c r="AS3">
-        <v>0.8773430706421189</v>
+        <v>0.8773430821949408</v>
       </c>
       <c r="AT3">
-        <v>0.3437547289082166</v>
+        <v>0.3437548981895753</v>
       </c>
       <c r="AU3">
-        <v>29.53242163429784</v>
+        <v>29.53241786597226</v>
       </c>
       <c r="AV3">
-        <v>0.8890925322691144</v>
+        <v>0.8890925388358178</v>
       </c>
       <c r="AW3">
-        <v>0.3424860092376946</v>
+        <v>0.3424861771020791</v>
       </c>
       <c r="AX3">
-        <v>29.11799223486617</v>
+        <v>29.11798834408776</v>
       </c>
       <c r="AY3">
-        <v>0.9007527255040253</v>
+        <v>0.900752731983964</v>
       </c>
       <c r="AZ3">
-        <v>0.3607250247618591</v>
+        <v>0.3607251949075355</v>
       </c>
     </row>
     <row r="4">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>24.05317834941806</v>
+        <v>24.05317835036776</v>
       </c>
       <c r="E4">
         <v>36.7783252635105</v>
@@ -973,139 +973,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H4">
-        <v>27.71270193078872</v>
+        <v>27.71270192762209</v>
       </c>
       <c r="I4">
-        <v>0.4435334755293588</v>
+        <v>0.4435334756459111</v>
       </c>
       <c r="J4">
-        <v>0.4215462238471482</v>
+        <v>0.4215462239794368</v>
       </c>
       <c r="K4">
-        <v>23.95900755715674</v>
+        <v>23.95900756112623</v>
       </c>
       <c r="L4">
-        <v>0.600791091792698</v>
+        <v>0.6007910916687293</v>
       </c>
       <c r="M4">
-        <v>0.5676225425423789</v>
+        <v>0.5676225423991644</v>
       </c>
       <c r="N4">
-        <v>23.68152186631388</v>
+        <v>23.68152186339831</v>
       </c>
       <c r="O4">
-        <v>0.6203175296441081</v>
+        <v>0.6203175296230591</v>
       </c>
       <c r="P4">
-        <v>0.5775584725828261</v>
+        <v>0.5775584726869331</v>
       </c>
       <c r="Q4">
-        <v>23.34775001382525</v>
+        <v>23.34775001036544</v>
       </c>
       <c r="R4">
-        <v>0.6502090492697123</v>
+        <v>0.6502090492286721</v>
       </c>
       <c r="S4">
-        <v>0.5893636719574695</v>
+        <v>0.5893636720793516</v>
       </c>
       <c r="T4">
-        <v>23.04064602824906</v>
+        <v>23.04064605032697</v>
       </c>
       <c r="U4">
-        <v>0.6907959241636793</v>
+        <v>0.6907959227574074</v>
       </c>
       <c r="V4">
-        <v>0.6000055092807184</v>
+        <v>0.6000055085191652</v>
       </c>
       <c r="W4">
-        <v>21.96183929905626</v>
+        <v>21.96183938574412</v>
       </c>
       <c r="X4">
-        <v>0.7195321711578067</v>
+        <v>0.7195321697462357</v>
       </c>
       <c r="Y4">
-        <v>0.6365759437988273</v>
+        <v>0.6365759409314012</v>
       </c>
       <c r="Z4">
-        <v>21.88309525990694</v>
+        <v>21.88309531924329</v>
       </c>
       <c r="AA4">
-        <v>0.732135750913034</v>
+        <v>0.7321357495885645</v>
       </c>
       <c r="AB4">
-        <v>0.639163927112923</v>
+        <v>0.6391639251558272</v>
       </c>
       <c r="AC4">
-        <v>22.19946555421401</v>
+        <v>22.19946561790364</v>
       </c>
       <c r="AD4">
-        <v>0.7466196098126303</v>
+        <v>0.7466196083368606</v>
       </c>
       <c r="AE4">
-        <v>0.628610880181693</v>
+        <v>0.6286108780380517</v>
       </c>
       <c r="AF4">
-        <v>22.74839691191801</v>
+        <v>22.74839704502971</v>
       </c>
       <c r="AG4">
-        <v>0.7705921354126433</v>
+        <v>0.770592133159886</v>
       </c>
       <c r="AH4">
-        <v>0.6099327624240019</v>
+        <v>0.609932757877123</v>
       </c>
       <c r="AI4">
-        <v>23.483740310076</v>
+        <v>23.48374049850585</v>
       </c>
       <c r="AJ4">
-        <v>0.7932698534804999</v>
+        <v>0.7932698515366601</v>
       </c>
       <c r="AK4">
-        <v>0.5843241548221342</v>
+        <v>0.5843241481825473</v>
       </c>
       <c r="AL4">
-        <v>24.32671634569665</v>
+        <v>24.32671666251298</v>
       </c>
       <c r="AM4">
-        <v>0.8027958470869203</v>
+        <v>0.8027958461074555</v>
       </c>
       <c r="AN4">
-        <v>0.5539149419763322</v>
+        <v>0.5539149304064234</v>
       </c>
       <c r="AO4">
-        <v>25.84163939444025</v>
+        <v>25.84163961930302</v>
       </c>
       <c r="AP4">
-        <v>0.8255327656170132</v>
+        <v>0.825532765737328</v>
       </c>
       <c r="AQ4">
-        <v>0.4964997287565815</v>
+        <v>0.4964997200171531</v>
       </c>
       <c r="AR4">
-        <v>27.07427264268907</v>
+        <v>27.0742727480479</v>
       </c>
       <c r="AS4">
-        <v>0.8393737670387228</v>
+        <v>0.8393737676170778</v>
       </c>
       <c r="AT4">
-        <v>0.4472110040074704</v>
+        <v>0.4472109998163881</v>
       </c>
       <c r="AU4">
-        <v>27.92001816288029</v>
+        <v>27.92001820713771</v>
       </c>
       <c r="AV4">
-        <v>0.848089418138862</v>
+        <v>0.848089419665917</v>
       </c>
       <c r="AW4">
-        <v>0.4120940745849033</v>
+        <v>0.4120940729490042</v>
       </c>
       <c r="AX4">
-        <v>28.73813408029118</v>
+        <v>28.73813382832218</v>
       </c>
       <c r="AY4">
-        <v>0.8618835817022211</v>
+        <v>0.8618835844994979</v>
       </c>
       <c r="AZ4">
-        <v>0.3770516311751237</v>
+        <v>0.3770516421620764</v>
       </c>
     </row>
     <row r="5">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>23.36070687700532</v>
+        <v>23.36070686890877</v>
       </c>
       <c r="E5">
         <v>36.7783252635105</v>
@@ -1137,139 +1137,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H5">
-        <v>23.31581082693482</v>
+        <v>23.31581081908759</v>
       </c>
       <c r="I5">
-        <v>0.6100318168402478</v>
+        <v>0.6100318170587467</v>
       </c>
       <c r="J5">
-        <v>0.5905294755624082</v>
+        <v>0.5905294758379893</v>
       </c>
       <c r="K5">
-        <v>23.09558476159108</v>
+        <v>23.09558474130582</v>
       </c>
       <c r="L5">
-        <v>0.6456035090591881</v>
+        <v>0.6456035093329955</v>
       </c>
       <c r="M5">
-        <v>0.5981915554202726</v>
+        <v>0.598191556127219</v>
       </c>
       <c r="N5">
-        <v>22.91363443450608</v>
+        <v>22.91363441552768</v>
       </c>
       <c r="O5">
-        <v>0.6635752452708878</v>
+        <v>0.6635752454151093</v>
       </c>
       <c r="P5">
-        <v>0.6045045790507451</v>
+        <v>0.6045045797068034</v>
       </c>
       <c r="Q5">
-        <v>23.02380749117621</v>
+        <v>23.0238074657881</v>
       </c>
       <c r="R5">
-        <v>0.6976069644309328</v>
+        <v>0.6976069645916962</v>
       </c>
       <c r="S5">
-        <v>0.6006516118084487</v>
+        <v>0.6006516126895849</v>
       </c>
       <c r="T5">
-        <v>22.79068374320356</v>
+        <v>22.79068368929005</v>
       </c>
       <c r="U5">
-        <v>0.7251106964022684</v>
+        <v>0.7251106978422603</v>
       </c>
       <c r="V5">
-        <v>0.6086788934441667</v>
+        <v>0.6086788952956078</v>
       </c>
       <c r="W5">
-        <v>22.84600379731672</v>
+        <v>22.84600371532622</v>
       </c>
       <c r="X5">
-        <v>0.7369106433437098</v>
+        <v>0.7369106441286662</v>
       </c>
       <c r="Y5">
-        <v>0.606776384219445</v>
+        <v>0.6067763870467067</v>
       </c>
       <c r="Z5">
-        <v>23.35436707169353</v>
+        <v>23.35436700337599</v>
       </c>
       <c r="AA5">
-        <v>0.7444859076384371</v>
+        <v>0.7444859085727902</v>
       </c>
       <c r="AB5">
-        <v>0.5890617907226202</v>
+        <v>0.589061793132282</v>
       </c>
       <c r="AC5">
-        <v>24.54551568034869</v>
+        <v>24.54551550828583</v>
       </c>
       <c r="AD5">
-        <v>0.7624378561161853</v>
+        <v>0.7624378556385814</v>
       </c>
       <c r="AE5">
-        <v>0.5459926364876917</v>
+        <v>0.5459926428681074</v>
       </c>
       <c r="AF5">
-        <v>26.41901902010221</v>
+        <v>26.4190190184177</v>
       </c>
       <c r="AG5">
-        <v>0.78760020111444</v>
+        <v>0.7876002008508051</v>
       </c>
       <c r="AH5">
-        <v>0.4739255027035414</v>
+        <v>0.4739255027385437</v>
       </c>
       <c r="AI5">
-        <v>27.37039749816571</v>
+        <v>27.37039763314572</v>
       </c>
       <c r="AJ5">
-        <v>0.8059649867535625</v>
+        <v>0.8059649884975559</v>
       </c>
       <c r="AK5">
-        <v>0.4352985341614405</v>
+        <v>0.4352985285266296</v>
       </c>
       <c r="AL5">
-        <v>28.17331415445262</v>
+        <v>28.17331431237877</v>
       </c>
       <c r="AM5">
-        <v>0.830366778796621</v>
+        <v>0.8303667791265055</v>
       </c>
       <c r="AN5">
-        <v>0.4015295240755037</v>
+        <v>0.4015295173096729</v>
       </c>
       <c r="AO5">
-        <v>28.26906889631009</v>
+        <v>28.26906895574136</v>
       </c>
       <c r="AP5">
-        <v>0.8490138029684103</v>
+        <v>0.8490138058184866</v>
       </c>
       <c r="AQ5">
-        <v>0.3972988994666473</v>
+        <v>0.3972988967428645</v>
       </c>
       <c r="AR5">
-        <v>28.10907982282071</v>
+        <v>28.1090796478629</v>
       </c>
       <c r="AS5">
-        <v>0.8650169818653041</v>
+        <v>0.8650169849299519</v>
       </c>
       <c r="AT5">
-        <v>0.4040897795225095</v>
+        <v>0.4040897867052587</v>
       </c>
       <c r="AU5">
-        <v>28.05355015124112</v>
+        <v>28.05354989450996</v>
       </c>
       <c r="AV5">
-        <v>0.8763531453168967</v>
+        <v>0.8763531500767945</v>
       </c>
       <c r="AW5">
-        <v>0.4064016711740003</v>
+        <v>0.4064016818476489</v>
       </c>
       <c r="AX5">
-        <v>28.08766662340168</v>
+        <v>28.08766636668398</v>
       </c>
       <c r="AY5">
-        <v>0.8882743931372074</v>
+        <v>0.8882743999407571</v>
       </c>
       <c r="AZ5">
-        <v>0.404993325409037</v>
+        <v>0.4049933359821918</v>
       </c>
     </row>
     <row r="6">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>23.54483530858528</v>
+        <v>23.54483529806313</v>
       </c>
       <c r="E6">
         <v>36.7783252635105</v>
@@ -1301,139 +1301,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H6">
-        <v>23.43250244036427</v>
+        <v>23.43250243264139</v>
       </c>
       <c r="I6">
-        <v>0.6070171617662247</v>
+        <v>0.6070171619989075</v>
       </c>
       <c r="J6">
-        <v>0.5864256049358012</v>
+        <v>0.5864256052085073</v>
       </c>
       <c r="K6">
-        <v>23.22781912041497</v>
+        <v>23.22781909247386</v>
       </c>
       <c r="L6">
-        <v>0.6393045257378471</v>
+        <v>0.6393045265012434</v>
       </c>
       <c r="M6">
-        <v>0.5935788908407292</v>
+        <v>0.5935788918187332</v>
       </c>
       <c r="N6">
-        <v>22.92846559019471</v>
+        <v>22.92846554945187</v>
       </c>
       <c r="O6">
-        <v>0.6610511929476248</v>
+        <v>0.6610511939442824</v>
       </c>
       <c r="P6">
-        <v>0.6039908631011724</v>
+        <v>0.6039908645105515</v>
       </c>
       <c r="Q6">
-        <v>22.78362780411015</v>
+        <v>22.78362773945451</v>
       </c>
       <c r="R6">
-        <v>0.7001481256441999</v>
+        <v>0.7001481274750757</v>
       </c>
       <c r="S6">
-        <v>0.6089097911532259</v>
+        <v>0.6089097933779206</v>
       </c>
       <c r="T6">
-        <v>22.19011519674126</v>
+        <v>22.19011511080117</v>
       </c>
       <c r="U6">
-        <v>0.7246880100477294</v>
+        <v>0.72468801162317</v>
       </c>
       <c r="V6">
-        <v>0.6290467009621706</v>
+        <v>0.6290467038376087</v>
       </c>
       <c r="W6">
-        <v>22.38370731565275</v>
+        <v>22.38370723768977</v>
       </c>
       <c r="X6">
-        <v>0.7307487279863828</v>
+        <v>0.7307487295594213</v>
       </c>
       <c r="Y6">
-        <v>0.6225151607013525</v>
+        <v>0.6225151633310956</v>
       </c>
       <c r="Z6">
-        <v>23.16055306545173</v>
+        <v>23.16055294346231</v>
       </c>
       <c r="AA6">
-        <v>0.749984657749466</v>
+        <v>0.7499846588558752</v>
       </c>
       <c r="AB6">
-        <v>0.5957963809010661</v>
+        <v>0.5957963851700675</v>
       </c>
       <c r="AC6">
-        <v>23.90285760486574</v>
+        <v>23.90285750901236</v>
       </c>
       <c r="AD6">
-        <v>0.7661223764520513</v>
+        <v>0.7661223766813637</v>
       </c>
       <c r="AE6">
-        <v>0.5693968990328666</v>
+        <v>0.5693969025167809</v>
       </c>
       <c r="AF6">
-        <v>24.74372692490482</v>
+        <v>24.74372700118483</v>
       </c>
       <c r="AG6">
-        <v>0.780111668543195</v>
+        <v>0.7801116699312639</v>
       </c>
       <c r="AH6">
-        <v>0.5385332064928584</v>
+        <v>0.5385332036814814</v>
       </c>
       <c r="AI6">
-        <v>25.19797872222351</v>
+        <v>25.1979789361755</v>
       </c>
       <c r="AJ6">
-        <v>0.7929170623352036</v>
+        <v>0.7929170652407993</v>
       </c>
       <c r="AK6">
-        <v>0.5214438396402963</v>
+        <v>0.521443831529654</v>
       </c>
       <c r="AL6">
-        <v>26.02795492257625</v>
+        <v>26.02795525491938</v>
       </c>
       <c r="AM6">
-        <v>0.8099297843089326</v>
+        <v>0.8099297896289367</v>
       </c>
       <c r="AN6">
-        <v>0.489361132552652</v>
+        <v>0.4893611195896905</v>
       </c>
       <c r="AO6">
-        <v>26.50531677819384</v>
+        <v>26.50531685446158</v>
       </c>
       <c r="AP6">
-        <v>0.8274049901785364</v>
+        <v>0.8274049991033307</v>
       </c>
       <c r="AQ6">
-        <v>0.4703783425760318</v>
+        <v>0.4703783395334761</v>
       </c>
       <c r="AR6">
-        <v>26.92223277679762</v>
+        <v>26.92223295573132</v>
       </c>
       <c r="AS6">
-        <v>0.8482249877342345</v>
+        <v>0.8482250004940552</v>
       </c>
       <c r="AT6">
-        <v>0.4534980653519925</v>
+        <v>0.4534980582128631</v>
       </c>
       <c r="AU6">
-        <v>27.0170524531357</v>
+        <v>27.0170524889494</v>
       </c>
       <c r="AV6">
-        <v>0.8595225665143156</v>
+        <v>0.8595225807498292</v>
       </c>
       <c r="AW6">
-        <v>0.4496461070298668</v>
+        <v>0.4496461056890905</v>
       </c>
       <c r="AX6">
-        <v>27.31603019904911</v>
+        <v>27.31603012336472</v>
       </c>
       <c r="AY6">
-        <v>0.8731733790000817</v>
+        <v>0.8731733920375879</v>
       </c>
       <c r="AZ6">
-        <v>0.4374177385588689</v>
+        <v>0.437417741351489</v>
       </c>
     </row>
     <row r="7">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>23.39097559023731</v>
+        <v>23.39097559249948</v>
       </c>
       <c r="E7">
         <v>36.7783252635105</v>
@@ -1465,139 +1465,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H7">
-        <v>27.65982932196518</v>
+        <v>27.65982931818869</v>
       </c>
       <c r="I7">
-        <v>0.4485490768089913</v>
+        <v>0.4485490769484015</v>
       </c>
       <c r="J7">
-        <v>0.4237376363433553</v>
+        <v>0.4237376365007877</v>
       </c>
       <c r="K7">
-        <v>23.6194372408333</v>
+        <v>23.6194372445317</v>
       </c>
       <c r="L7">
-        <v>0.61201724408647</v>
+        <v>0.6120172439931942</v>
       </c>
       <c r="M7">
-        <v>0.5797804709016181</v>
+        <v>0.5797804707700887</v>
       </c>
       <c r="N7">
-        <v>22.18998494112573</v>
+        <v>22.18998494209591</v>
       </c>
       <c r="O7">
-        <v>0.676416279468887</v>
+        <v>0.6764162792676429</v>
       </c>
       <c r="P7">
-        <v>0.6290760928983262</v>
+        <v>0.629076092866513</v>
       </c>
       <c r="Q7">
-        <v>21.94308674972849</v>
+        <v>21.94308674551704</v>
       </c>
       <c r="R7">
-        <v>0.6880526294465205</v>
+        <v>0.6880526294662277</v>
       </c>
       <c r="S7">
-        <v>0.6372842679356893</v>
+        <v>0.637284268074697</v>
       </c>
       <c r="T7">
-        <v>21.92256028117234</v>
+        <v>21.92256027624448</v>
       </c>
       <c r="U7">
-        <v>0.7135555272214058</v>
+        <v>0.7135555270394232</v>
       </c>
       <c r="V7">
-        <v>0.6379197970331528</v>
+        <v>0.6379197971983536</v>
       </c>
       <c r="W7">
-        <v>21.64511187879291</v>
+        <v>21.64511189477068</v>
       </c>
       <c r="X7">
-        <v>0.7202028579663428</v>
+        <v>0.7202028573689703</v>
       </c>
       <c r="Y7">
-        <v>0.646987070811315</v>
+        <v>0.6469870702968176</v>
       </c>
       <c r="Z7">
-        <v>21.93565590148425</v>
+        <v>21.93565594470904</v>
       </c>
       <c r="AA7">
-        <v>0.7360009114323256</v>
+        <v>0.7360009103708571</v>
       </c>
       <c r="AB7">
-        <v>0.6374658916424079</v>
+        <v>0.6374658902149772</v>
       </c>
       <c r="AC7">
-        <v>21.89675551583464</v>
+        <v>21.89675560443411</v>
       </c>
       <c r="AD7">
-        <v>0.753229656421244</v>
+        <v>0.7532296554488426</v>
       </c>
       <c r="AE7">
-        <v>0.6387656202158222</v>
+        <v>0.6387656172937364</v>
       </c>
       <c r="AF7">
-        <v>22.3623168596387</v>
+        <v>22.3623169448436</v>
       </c>
       <c r="AG7">
-        <v>0.7705416090376991</v>
+        <v>0.7705416083314932</v>
       </c>
       <c r="AH7">
-        <v>0.6231026941488707</v>
+        <v>0.6231026912804514</v>
       </c>
       <c r="AI7">
-        <v>23.06116408055109</v>
+        <v>23.06116427168864</v>
       </c>
       <c r="AJ7">
-        <v>0.783722773582618</v>
+        <v>0.783722771844954</v>
       </c>
       <c r="AK7">
-        <v>0.5992399548957057</v>
+        <v>0.5992399483229416</v>
       </c>
       <c r="AL7">
-        <v>23.77279513112846</v>
+        <v>23.77279548604873</v>
       </c>
       <c r="AM7">
-        <v>0.8042615261658581</v>
+        <v>0.8042615248751608</v>
       </c>
       <c r="AN7">
-        <v>0.5741213981328667</v>
+        <v>0.5741213856400273</v>
       </c>
       <c r="AO7">
-        <v>25.36415868254067</v>
+        <v>25.36415910246795</v>
       </c>
       <c r="AP7">
-        <v>0.8234075120408724</v>
+        <v>0.8234075161540007</v>
       </c>
       <c r="AQ7">
-        <v>0.5151055361695721</v>
+        <v>0.5151055200689669</v>
       </c>
       <c r="AR7">
-        <v>26.50750293588183</v>
+        <v>26.50750319935112</v>
       </c>
       <c r="AS7">
-        <v>0.8352283264744101</v>
+        <v>0.8352283296722679</v>
       </c>
       <c r="AT7">
-        <v>0.4702886143887231</v>
+        <v>0.4702886038758084</v>
       </c>
       <c r="AU7">
-        <v>27.71924527517762</v>
+        <v>27.71924526495051</v>
       </c>
       <c r="AV7">
-        <v>0.8483520578819547</v>
+        <v>0.8483520631449875</v>
       </c>
       <c r="AW7">
-        <v>0.4206097948044066</v>
+        <v>0.4206097955608392</v>
       </c>
       <c r="AX7">
-        <v>28.40603324638889</v>
+        <v>28.40603328095265</v>
       </c>
       <c r="AY7">
-        <v>0.8581856967680425</v>
+        <v>0.8581857061046585</v>
       </c>
       <c r="AZ7">
-        <v>0.3914791201438557</v>
+        <v>0.3914791183623219</v>
       </c>
     </row>
     <row r="8">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>23.53393140592127</v>
+        <v>23.53393140693519</v>
       </c>
       <c r="E8">
         <v>36.7783252635105</v>
@@ -1629,139 +1629,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H8">
-        <v>25.78138123984557</v>
+        <v>25.78138124450497</v>
       </c>
       <c r="I8">
-        <v>0.5206052769768158</v>
+        <v>0.5206052768054965</v>
       </c>
       <c r="J8">
-        <v>0.4993576157248136</v>
+        <v>0.4993576155438536</v>
       </c>
       <c r="K8">
-        <v>23.71224410704146</v>
+        <v>23.71224411148756</v>
       </c>
       <c r="L8">
-        <v>0.6078732584528704</v>
+        <v>0.6078732582975199</v>
       </c>
       <c r="M8">
-        <v>0.5764728033376713</v>
+        <v>0.5764728031788809</v>
       </c>
       <c r="N8">
-        <v>22.24928182432465</v>
+        <v>22.24928180941651</v>
       </c>
       <c r="O8">
-        <v>0.6768386823180945</v>
+        <v>0.6768386826477882</v>
       </c>
       <c r="P8">
-        <v>0.6270923041613999</v>
+        <v>0.6270923046611112</v>
       </c>
       <c r="Q8">
-        <v>21.90182965176314</v>
+        <v>21.90182963903971</v>
       </c>
       <c r="R8">
-        <v>0.7037229690604321</v>
+        <v>0.7037229692087383</v>
       </c>
       <c r="S8">
-        <v>0.638617316013244</v>
+        <v>0.6386173164328509</v>
       </c>
       <c r="T8">
-        <v>21.67890324724541</v>
+        <v>21.67890325447064</v>
       </c>
       <c r="U8">
-        <v>0.7121855486138966</v>
+        <v>0.712185548317009</v>
       </c>
       <c r="V8">
-        <v>0.6459393664686576</v>
+        <v>0.6459393662318302</v>
       </c>
       <c r="W8">
-        <v>22.17979856559915</v>
+        <v>22.17979859650915</v>
       </c>
       <c r="X8">
-        <v>0.7348135597008684</v>
+        <v>0.734813558818933</v>
       </c>
       <c r="Y8">
-        <v>0.6293847729504991</v>
+        <v>0.6293847719183233</v>
       </c>
       <c r="Z8">
-        <v>22.22556759793047</v>
+        <v>22.22556763957467</v>
       </c>
       <c r="AA8">
-        <v>0.7427445006452336</v>
+        <v>0.7427444995171902</v>
       </c>
       <c r="AB8">
-        <v>0.6278343407291129</v>
+        <v>0.6278343393386967</v>
       </c>
       <c r="AC8">
-        <v>23.09431545939564</v>
+        <v>23.09431554572522</v>
       </c>
       <c r="AD8">
-        <v>0.7597145142683589</v>
+        <v>0.7597145118491005</v>
       </c>
       <c r="AE8">
-        <v>0.5981098229093306</v>
+        <v>0.5981098199115741</v>
       </c>
       <c r="AF8">
-        <v>24.35021333916427</v>
+        <v>24.35021358243898</v>
       </c>
       <c r="AG8">
-        <v>0.7746048816464201</v>
+        <v>0.774604877817791</v>
       </c>
       <c r="AH8">
-        <v>0.5531791167532928</v>
+        <v>0.5531791078374955</v>
       </c>
       <c r="AI8">
-        <v>24.98238500557315</v>
+        <v>24.98238536285603</v>
       </c>
       <c r="AJ8">
-        <v>0.789588720110749</v>
+        <v>0.7895887154589716</v>
       </c>
       <c r="AK8">
-        <v>0.529599213432713</v>
+        <v>0.5295991999845328</v>
       </c>
       <c r="AL8">
-        <v>25.47480798269329</v>
+        <v>25.47480859711542</v>
       </c>
       <c r="AM8">
-        <v>0.8031058147400687</v>
+        <v>0.8031058128841662</v>
       </c>
       <c r="AN8">
-        <v>0.5108858541575627</v>
+        <v>0.5108858305684637</v>
       </c>
       <c r="AO8">
-        <v>26.43581042765867</v>
+        <v>26.43581124848713</v>
       </c>
       <c r="AP8">
-        <v>0.816693849482493</v>
+        <v>0.8166938500560126</v>
       </c>
       <c r="AQ8">
-        <v>0.473168630552142</v>
+        <v>0.4731685978271125</v>
       </c>
       <c r="AR8">
-        <v>28.06582590484436</v>
+        <v>28.06582651798098</v>
       </c>
       <c r="AS8">
-        <v>0.8268848490434663</v>
+        <v>0.8268848499637843</v>
       </c>
       <c r="AT8">
-        <v>0.4061224310702001</v>
+        <v>0.4061224051349844</v>
       </c>
       <c r="AU8">
-        <v>29.21190612474481</v>
+        <v>29.21190636006076</v>
       </c>
       <c r="AV8">
-        <v>0.8435914127577882</v>
+        <v>0.8435914139994118</v>
       </c>
       <c r="AW8">
-        <v>0.3565150070749667</v>
+        <v>0.3565149967697238</v>
       </c>
       <c r="AX8">
-        <v>29.90236329152732</v>
+        <v>29.90236320309872</v>
       </c>
       <c r="AY8">
-        <v>0.8577375082572827</v>
+        <v>0.8577375092894336</v>
       </c>
       <c r="AZ8">
-        <v>0.3256260343490119</v>
+        <v>0.3256260384090546</v>
       </c>
     </row>
     <row r="9">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>23.52718521722961</v>
+        <v>23.52718521680001</v>
       </c>
       <c r="E9">
         <v>36.7783252635105</v>
@@ -1793,139 +1793,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H9">
-        <v>25.81549343942005</v>
+        <v>25.81549344399123</v>
       </c>
       <c r="I9">
-        <v>0.5205623175890227</v>
+        <v>0.5205623174173816</v>
       </c>
       <c r="J9">
-        <v>0.4980348066975618</v>
+        <v>0.4980348065197885</v>
       </c>
       <c r="K9">
-        <v>23.78134148248057</v>
+        <v>23.78134148689133</v>
       </c>
       <c r="L9">
-        <v>0.60784629969889</v>
+        <v>0.6078462995421252</v>
       </c>
       <c r="M9">
-        <v>0.5740107050761313</v>
+        <v>0.5740107049181028</v>
       </c>
       <c r="N9">
-        <v>22.31708793475688</v>
+        <v>22.31708792029996</v>
       </c>
       <c r="O9">
-        <v>0.6766332412951904</v>
+        <v>0.6766332416224113</v>
       </c>
       <c r="P9">
-        <v>0.6248304379267619</v>
+        <v>0.6248304384128449</v>
       </c>
       <c r="Q9">
-        <v>21.90666932858417</v>
+        <v>21.90666931464622</v>
       </c>
       <c r="R9">
-        <v>0.7028171165111605</v>
+        <v>0.7028171166575812</v>
       </c>
       <c r="S9">
-        <v>0.6384518745722876</v>
+        <v>0.6384518750334458</v>
       </c>
       <c r="T9">
-        <v>21.58081863083466</v>
+        <v>21.58081864312342</v>
       </c>
       <c r="U9">
-        <v>0.7100060660481193</v>
+        <v>0.7100060657366675</v>
       </c>
       <c r="V9">
-        <v>0.6491209975360522</v>
+        <v>0.6491209971385019</v>
       </c>
       <c r="W9">
-        <v>21.94283543883008</v>
+        <v>21.94283546581955</v>
       </c>
       <c r="X9">
-        <v>0.7286237616018298</v>
+        <v>0.7286237605591488</v>
       </c>
       <c r="Y9">
-        <v>0.6371793320637918</v>
+        <v>0.6371793311745546</v>
       </c>
       <c r="Z9">
-        <v>21.88133166841511</v>
+        <v>21.88133169883036</v>
       </c>
       <c r="AA9">
-        <v>0.734203989890325</v>
+        <v>0.7342039886324163</v>
       </c>
       <c r="AB9">
-        <v>0.6392130233742884</v>
+        <v>0.6392130223816563</v>
       </c>
       <c r="AC9">
-        <v>22.12179571661925</v>
+        <v>22.12179576392569</v>
       </c>
       <c r="AD9">
-        <v>0.7416622158583425</v>
+        <v>0.7416622133417443</v>
       </c>
       <c r="AE9">
-        <v>0.6312315995968165</v>
+        <v>0.6312315980287481</v>
       </c>
       <c r="AF9">
-        <v>22.7545906890131</v>
+        <v>22.75459078129503</v>
       </c>
       <c r="AG9">
-        <v>0.7462717478579692</v>
+        <v>0.7462717439651957</v>
       </c>
       <c r="AH9">
-        <v>0.6097434587923387</v>
+        <v>0.6097434556211977</v>
       </c>
       <c r="AI9">
-        <v>23.15439044426712</v>
+        <v>23.1543906093846</v>
       </c>
       <c r="AJ9">
-        <v>0.7541234170239347</v>
+        <v>0.7541234105135952</v>
       </c>
       <c r="AK9">
-        <v>0.5959070036561815</v>
+        <v>0.5959069978885631</v>
       </c>
       <c r="AL9">
-        <v>23.1789632322234</v>
+        <v>23.17896374648262</v>
       </c>
       <c r="AM9">
-        <v>0.7585244018577597</v>
+        <v>0.7585243951298893</v>
       </c>
       <c r="AN9">
-        <v>0.5950464422264008</v>
+        <v>0.5950464242810951</v>
       </c>
       <c r="AO9">
-        <v>23.5017780996801</v>
+        <v>23.50177872759273</v>
       </c>
       <c r="AP9">
-        <v>0.7646851494990351</v>
+        <v>0.7646851437894226</v>
       </c>
       <c r="AQ9">
-        <v>0.583671124713479</v>
+        <v>0.5836711024940165</v>
       </c>
       <c r="AR9">
-        <v>24.34887723415384</v>
+        <v>24.34887796875984</v>
       </c>
       <c r="AS9">
-        <v>0.7689951138495983</v>
+        <v>0.768995108833338</v>
       </c>
       <c r="AT9">
-        <v>0.5530975582934453</v>
+        <v>0.5530975313831483</v>
       </c>
       <c r="AU9">
-        <v>24.82435995276465</v>
+        <v>24.8243608703685</v>
       </c>
       <c r="AV9">
-        <v>0.7761696970643259</v>
+        <v>0.7761696929858984</v>
       </c>
       <c r="AW9">
-        <v>0.5354491004594927</v>
+        <v>0.5354490660997112</v>
       </c>
       <c r="AX9">
-        <v>25.31395596960535</v>
+        <v>25.31395701436464</v>
       </c>
       <c r="AY9">
-        <v>0.7800405819156587</v>
+        <v>0.7800405786905309</v>
       </c>
       <c r="AZ9">
-        <v>0.5168898758492021</v>
+        <v>0.516889835934404</v>
       </c>
     </row>
     <row r="10">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>23.47163699863147</v>
+        <v>23.47163699793424</v>
       </c>
       <c r="E10">
         <v>36.7783252635105</v>
@@ -1957,139 +1957,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H10">
-        <v>25.76083554910897</v>
+        <v>25.76083555376685</v>
       </c>
       <c r="I10">
-        <v>0.5205230327394337</v>
+        <v>0.5205230325672237</v>
       </c>
       <c r="J10">
-        <v>0.5001438566609585</v>
+        <v>0.5001438564801923</v>
       </c>
       <c r="K10">
-        <v>23.7322319048982</v>
+        <v>23.73223190925558</v>
       </c>
       <c r="L10">
-        <v>0.6078334575093147</v>
+        <v>0.6078334573523654</v>
       </c>
       <c r="M10">
-        <v>0.575747383557518</v>
+        <v>0.5757473834017426</v>
       </c>
       <c r="N10">
-        <v>22.2809048808448</v>
+        <v>22.28090486595553</v>
       </c>
       <c r="O10">
-        <v>0.6765871964360762</v>
+        <v>0.6765871967603111</v>
       </c>
       <c r="P10">
-        <v>0.626030842429744</v>
+        <v>0.6260308429297468</v>
       </c>
       <c r="Q10">
-        <v>21.87029309239944</v>
+        <v>21.87029307898137</v>
       </c>
       <c r="R10">
-        <v>0.7027455658396173</v>
+        <v>0.7027455659850992</v>
       </c>
       <c r="S10">
-        <v>0.639675277225833</v>
+        <v>0.6396752776693123</v>
       </c>
       <c r="T10">
-        <v>21.6142275639812</v>
+        <v>21.61422757378801</v>
       </c>
       <c r="U10">
-        <v>0.7099420570343165</v>
+        <v>0.7099420567253972</v>
       </c>
       <c r="V10">
-        <v>0.6480397015468361</v>
+        <v>0.6480397012295885</v>
       </c>
       <c r="W10">
-        <v>21.97449485060585</v>
+        <v>21.9744948749888</v>
       </c>
       <c r="X10">
-        <v>0.7284543386780953</v>
+        <v>0.7284543376309593</v>
       </c>
       <c r="Y10">
-        <v>0.636163030522737</v>
+        <v>0.6361630297195962</v>
       </c>
       <c r="Z10">
-        <v>21.886262984302</v>
+        <v>21.88626301252785</v>
       </c>
       <c r="AA10">
-        <v>0.7338969276303087</v>
+        <v>0.7338969263742887</v>
       </c>
       <c r="AB10">
-        <v>0.6390889266304092</v>
+        <v>0.6390889257052792</v>
       </c>
       <c r="AC10">
-        <v>22.09640952512181</v>
+        <v>22.09640957376618</v>
       </c>
       <c r="AD10">
-        <v>0.7410681466041162</v>
+        <v>0.7410681441106833</v>
       </c>
       <c r="AE10">
-        <v>0.6321072653537733</v>
+        <v>0.6321072637427158</v>
       </c>
       <c r="AF10">
-        <v>22.6627632092852</v>
+        <v>22.66276327791963</v>
       </c>
       <c r="AG10">
-        <v>0.745385805177039</v>
+        <v>0.7453858013393864</v>
       </c>
       <c r="AH10">
-        <v>0.6129545079381332</v>
+        <v>0.6129545056217774</v>
       </c>
       <c r="AI10">
-        <v>23.02881120541415</v>
+        <v>23.02881139306741</v>
       </c>
       <c r="AJ10">
-        <v>0.7525764391054717</v>
+        <v>0.7525764326607678</v>
       </c>
       <c r="AK10">
-        <v>0.6003636467020448</v>
+        <v>0.6003636401994856</v>
       </c>
       <c r="AL10">
-        <v>23.04365911379156</v>
+        <v>23.04365958528609</v>
       </c>
       <c r="AM10">
-        <v>0.7564737602597286</v>
+        <v>0.7564737534581263</v>
       </c>
       <c r="AN10">
-        <v>0.599798906868797</v>
+        <v>0.5997988905413378</v>
       </c>
       <c r="AO10">
-        <v>23.35473207742593</v>
+        <v>23.35473286563528</v>
       </c>
       <c r="AP10">
-        <v>0.7616680137893131</v>
+        <v>0.761668007630717</v>
       </c>
       <c r="AQ10">
-        <v>0.5889343190354048</v>
+        <v>0.58893429127117</v>
       </c>
       <c r="AR10">
-        <v>24.23670951606664</v>
+        <v>24.23671042583342</v>
       </c>
       <c r="AS10">
-        <v>0.7655557673130832</v>
+        <v>0.765555761681513</v>
       </c>
       <c r="AT10">
-        <v>0.557233885964135</v>
+        <v>0.5572338527222908</v>
       </c>
       <c r="AU10">
-        <v>24.80076864372196</v>
+        <v>24.80076950449772</v>
       </c>
       <c r="AV10">
-        <v>0.772519523027285</v>
+        <v>0.7725195181219768</v>
       </c>
       <c r="AW10">
-        <v>0.5363409841546602</v>
+        <v>0.5363409520090223</v>
       </c>
       <c r="AX10">
-        <v>25.44689490386961</v>
+        <v>25.4468960698928</v>
       </c>
       <c r="AY10">
-        <v>0.7766760465580256</v>
+        <v>0.7766760425429213</v>
       </c>
       <c r="AZ10">
-        <v>0.5117445250486772</v>
+        <v>0.5117444804333255</v>
       </c>
     </row>
     <row r="11">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>23.49204404893672</v>
+        <v>23.49204404831875</v>
       </c>
       <c r="E11">
         <v>36.7783252635105</v>
@@ -2121,139 +2121,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H11">
-        <v>25.77177306819435</v>
+        <v>25.77177307283957</v>
       </c>
       <c r="I11">
-        <v>0.5205642637601677</v>
+        <v>0.5205642635882819</v>
       </c>
       <c r="J11">
-        <v>0.499725909870483</v>
+        <v>0.4997259096901235</v>
       </c>
       <c r="K11">
-        <v>23.67023109429435</v>
+        <v>23.67023109869761</v>
       </c>
       <c r="L11">
-        <v>0.6078198436452922</v>
+        <v>0.6078198434884154</v>
       </c>
       <c r="M11">
-        <v>0.5779786783326801</v>
+        <v>0.5779786781756561</v>
       </c>
       <c r="N11">
-        <v>22.21003383833665</v>
+        <v>22.21003382372495</v>
       </c>
       <c r="O11">
-        <v>0.6764687298641887</v>
+        <v>0.6764687301949653</v>
       </c>
       <c r="P11">
-        <v>0.6284199037103522</v>
+        <v>0.6284199041996327</v>
       </c>
       <c r="Q11">
-        <v>21.84557749756222</v>
+        <v>21.84557748408356</v>
       </c>
       <c r="R11">
-        <v>0.7026497284810076</v>
+        <v>0.7026497286332243</v>
       </c>
       <c r="S11">
-        <v>0.6404968937853383</v>
+        <v>0.6404968942290221</v>
       </c>
       <c r="T11">
-        <v>21.56438952988126</v>
+        <v>21.56438953991269</v>
       </c>
       <c r="U11">
-        <v>0.7099242198630991</v>
+        <v>0.7099242195641284</v>
       </c>
       <c r="V11">
-        <v>0.6496560102291485</v>
+        <v>0.6496560099039261</v>
       </c>
       <c r="W11">
-        <v>21.89938171511885</v>
+        <v>21.89938174861254</v>
       </c>
       <c r="X11">
-        <v>0.7288095526977996</v>
+        <v>0.7288095516452373</v>
       </c>
       <c r="Y11">
-        <v>0.6386965139368095</v>
+        <v>0.6386965128312287</v>
       </c>
       <c r="Z11">
-        <v>21.85284626699696</v>
+        <v>21.85284631779621</v>
       </c>
       <c r="AA11">
-        <v>0.7351042901912949</v>
+        <v>0.7351042888802444</v>
       </c>
       <c r="AB11">
-        <v>0.6402215298307551</v>
+        <v>0.6402215281580792</v>
       </c>
       <c r="AC11">
-        <v>22.00594440795632</v>
+        <v>22.00594448616762</v>
       </c>
       <c r="AD11">
-        <v>0.7448741713625877</v>
+        <v>0.7448741686629163</v>
       </c>
       <c r="AE11">
-        <v>0.6351517944607956</v>
+        <v>0.6351517918701541</v>
       </c>
       <c r="AF11">
-        <v>22.53911029349756</v>
+        <v>22.53911044121218</v>
       </c>
       <c r="AG11">
-        <v>0.7510992033293369</v>
+        <v>0.7510991991056868</v>
       </c>
       <c r="AH11">
-        <v>0.6171994075087799</v>
+        <v>0.6171994025104879</v>
       </c>
       <c r="AI11">
-        <v>22.657102642175</v>
+        <v>22.65710289069208</v>
       </c>
       <c r="AJ11">
-        <v>0.7589391668194596</v>
+        <v>0.758939160456013</v>
       </c>
       <c r="AK11">
-        <v>0.6131980569778731</v>
+        <v>0.6131980485171891</v>
       </c>
       <c r="AL11">
-        <v>22.63955681828047</v>
+        <v>22.63955725870131</v>
       </c>
       <c r="AM11">
-        <v>0.7632262826815993</v>
+        <v>0.7632262761089041</v>
       </c>
       <c r="AN11">
-        <v>0.6138146104506439</v>
+        <v>0.6138145954162879</v>
       </c>
       <c r="AO11">
-        <v>22.86106996090964</v>
+        <v>22.86107070225898</v>
       </c>
       <c r="AP11">
-        <v>0.7686588052349057</v>
+        <v>0.7686587994525806</v>
       </c>
       <c r="AQ11">
-        <v>0.6062125044734721</v>
+        <v>0.606212478943176</v>
       </c>
       <c r="AR11">
-        <v>23.72394573679263</v>
+        <v>23.72394661426948</v>
       </c>
       <c r="AS11">
-        <v>0.7718341747693007</v>
+        <v>0.771834169706343</v>
       </c>
       <c r="AT11">
-        <v>0.5758767856855294</v>
+        <v>0.575876754327061</v>
       </c>
       <c r="AU11">
-        <v>24.35863666409486</v>
+        <v>24.35863760571567</v>
       </c>
       <c r="AV11">
-        <v>0.7779698825016332</v>
+        <v>0.7779698787547843</v>
       </c>
       <c r="AW11">
-        <v>0.5528038039065752</v>
+        <v>0.5528037693450353</v>
       </c>
       <c r="AX11">
-        <v>24.76059892360055</v>
+        <v>24.76059995851732</v>
       </c>
       <c r="AY11">
-        <v>0.7807528906390273</v>
+        <v>0.7807528866368051</v>
       </c>
       <c r="AZ11">
-        <v>0.5379160002596108</v>
+        <v>0.5379159616250269</v>
       </c>
     </row>
     <row r="12">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>22.88304891629113</v>
+        <v>22.88304890526039</v>
       </c>
       <c r="E12">
         <v>36.7783252635105</v>
@@ -2285,139 +2285,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H12">
-        <v>22.89700744565065</v>
+        <v>22.89700743566843</v>
       </c>
       <c r="I12">
-        <v>0.6256684992605344</v>
+        <v>0.6256684995277224</v>
       </c>
       <c r="J12">
-        <v>0.6051000095029837</v>
+        <v>0.6051000098473991</v>
       </c>
       <c r="K12">
-        <v>22.60157923288419</v>
+        <v>22.60157920635554</v>
       </c>
       <c r="L12">
-        <v>0.6630786191967493</v>
+        <v>0.6630786196249348</v>
       </c>
       <c r="M12">
-        <v>0.6151827290492567</v>
+        <v>0.6151827299557535</v>
       </c>
       <c r="N12">
-        <v>22.36990954474219</v>
+        <v>22.36990951436889</v>
       </c>
       <c r="O12">
-        <v>0.6819965972183346</v>
+        <v>0.6819965975466808</v>
       </c>
       <c r="P12">
-        <v>0.6230081594335577</v>
+        <v>0.6230081604628288</v>
       </c>
       <c r="Q12">
-        <v>22.34741533722841</v>
+        <v>22.34741529334633</v>
       </c>
       <c r="R12">
-        <v>0.7147027132907793</v>
+        <v>0.7147027138091129</v>
       </c>
       <c r="S12">
-        <v>0.6236784946416618</v>
+        <v>0.6236784961274926</v>
       </c>
       <c r="T12">
-        <v>22.27320712257797</v>
+        <v>22.27320704878874</v>
       </c>
       <c r="U12">
-        <v>0.7362379508688577</v>
+        <v>0.7362379522115026</v>
       </c>
       <c r="V12">
-        <v>0.6261728412999161</v>
+        <v>0.6261728437839038</v>
       </c>
       <c r="W12">
-        <v>22.28145630259184</v>
+        <v>22.28145620363806</v>
       </c>
       <c r="X12">
-        <v>0.7469515443669583</v>
+        <v>0.7469515456445683</v>
       </c>
       <c r="Y12">
-        <v>0.6258876930353688</v>
+        <v>0.6258876963662515</v>
       </c>
       <c r="Z12">
-        <v>22.88827312335227</v>
+        <v>22.88827299924593</v>
       </c>
       <c r="AA12">
-        <v>0.7565681659873583</v>
+        <v>0.7565681673485567</v>
       </c>
       <c r="AB12">
-        <v>0.6052111361851702</v>
+        <v>0.6052111404748297</v>
       </c>
       <c r="AC12">
-        <v>24.05371346133022</v>
+        <v>24.05371328650001</v>
       </c>
       <c r="AD12">
-        <v>0.7683866818759123</v>
+        <v>0.7683866825986925</v>
       </c>
       <c r="AE12">
-        <v>0.5639306619255363</v>
+        <v>0.5639306682732099</v>
       </c>
       <c r="AF12">
-        <v>25.77243731338686</v>
+        <v>25.77243722345679</v>
       </c>
       <c r="AG12">
-        <v>0.7841498226811183</v>
+        <v>0.7841498234934453</v>
       </c>
       <c r="AH12">
-        <v>0.4993405266870967</v>
+        <v>0.4993405301937715</v>
       </c>
       <c r="AI12">
-        <v>27.25405175591855</v>
+        <v>27.25405179305302</v>
       </c>
       <c r="AJ12">
-        <v>0.8009544486888206</v>
+        <v>0.8009544512679112</v>
       </c>
       <c r="AK12">
-        <v>0.4400226248618244</v>
+        <v>0.4400226233681847</v>
       </c>
       <c r="AL12">
-        <v>28.860632189161</v>
+        <v>28.86063216652174</v>
       </c>
       <c r="AM12">
-        <v>0.8268471550639334</v>
+        <v>0.8268471557197383</v>
       </c>
       <c r="AN12">
-        <v>0.3719134458837232</v>
+        <v>0.3719134469652392</v>
       </c>
       <c r="AO12">
-        <v>29.45864253752315</v>
+        <v>29.45864241842154</v>
       </c>
       <c r="AP12">
-        <v>0.8406186594429166</v>
+        <v>0.8406186601867291</v>
       </c>
       <c r="AQ12">
-        <v>0.3456553183868946</v>
+        <v>0.3456553237604963</v>
       </c>
       <c r="AR12">
-        <v>29.28652664676022</v>
+        <v>29.28652657405198</v>
       </c>
       <c r="AS12">
-        <v>0.8534902639285242</v>
+        <v>0.8534902624007316</v>
       </c>
       <c r="AT12">
-        <v>0.3531473134071786</v>
+        <v>0.3531473167611571</v>
       </c>
       <c r="AU12">
-        <v>29.15260936891794</v>
+        <v>29.1526094620118</v>
       </c>
       <c r="AV12">
-        <v>0.8644780794675748</v>
+        <v>0.8644780766836552</v>
       </c>
       <c r="AW12">
-        <v>0.3590936518852654</v>
+        <v>0.3590936478696725</v>
       </c>
       <c r="AX12">
-        <v>29.70701160726849</v>
+        <v>29.70701202125428</v>
       </c>
       <c r="AY12">
-        <v>0.8749142902315558</v>
+        <v>0.8749142852881248</v>
       </c>
       <c r="AZ12">
-        <v>0.3345172527736233</v>
+        <v>0.3345172342247513</v>
       </c>
     </row>
     <row r="13">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>23.00901520072983</v>
+        <v>23.00901519834288</v>
       </c>
       <c r="E13">
         <v>36.7783252635105</v>
@@ -2449,139 +2449,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H13">
-        <v>22.99345687451578</v>
+        <v>22.99345687273329</v>
       </c>
       <c r="I13">
-        <v>0.623600934933505</v>
+        <v>0.6236009350049492</v>
       </c>
       <c r="J13">
-        <v>0.6017763648084599</v>
+        <v>0.6017763648702028</v>
       </c>
       <c r="K13">
-        <v>23.09043247035899</v>
+        <v>23.09043245762025</v>
       </c>
       <c r="L13">
-        <v>0.6724030165401826</v>
+        <v>0.6724030166463889</v>
       </c>
       <c r="M13">
-        <v>0.598325304619442</v>
+        <v>0.5983253050573983</v>
       </c>
       <c r="N13">
-        <v>22.72935286314836</v>
+        <v>22.72935284958584</v>
       </c>
       <c r="O13">
-        <v>0.7048940196226932</v>
+        <v>0.7048940195481492</v>
       </c>
       <c r="P13">
-        <v>0.6107006601181375</v>
+        <v>0.6107006605862177</v>
       </c>
       <c r="Q13">
-        <v>22.40662325473617</v>
+        <v>22.40662322365432</v>
       </c>
       <c r="R13">
-        <v>0.7262105491165037</v>
+        <v>0.7262105515173098</v>
       </c>
       <c r="S13">
-        <v>0.6217152221872957</v>
+        <v>0.6217152232416571</v>
       </c>
       <c r="T13">
-        <v>23.55894469529022</v>
+        <v>23.55894467386219</v>
       </c>
       <c r="U13">
-        <v>0.7383713157551386</v>
+        <v>0.738371318809367</v>
       </c>
       <c r="V13">
-        <v>0.5817592587248596</v>
+        <v>0.5817592594994119</v>
       </c>
       <c r="W13">
-        <v>24.09916932517081</v>
+        <v>24.09916915192431</v>
       </c>
       <c r="X13">
-        <v>0.7631285723867025</v>
+        <v>0.7631285737498877</v>
       </c>
       <c r="Y13">
-        <v>0.5622567425245549</v>
+        <v>0.5622567488976207</v>
       </c>
       <c r="Z13">
-        <v>24.12570763341241</v>
+        <v>24.1257074298578</v>
       </c>
       <c r="AA13">
-        <v>0.7768540342483207</v>
+        <v>0.7768540359774523</v>
       </c>
       <c r="AB13">
-        <v>0.5613888640055945</v>
+        <v>0.5613888714537271</v>
       </c>
       <c r="AC13">
-        <v>24.49952459363621</v>
+        <v>24.4995244760635</v>
       </c>
       <c r="AD13">
-        <v>0.7916642318861681</v>
+        <v>0.7916642338696807</v>
       </c>
       <c r="AE13">
-        <v>0.5476272051399351</v>
+        <v>0.5476272095233786</v>
       </c>
       <c r="AF13">
-        <v>26.37827172569118</v>
+        <v>26.37827135195021</v>
       </c>
       <c r="AG13">
-        <v>0.8111424369511484</v>
+        <v>0.8111424365140055</v>
       </c>
       <c r="AH13">
-        <v>0.4753227471852248</v>
+        <v>0.4753227620953092</v>
       </c>
       <c r="AI13">
-        <v>27.98693603588389</v>
+        <v>27.9869359697368</v>
       </c>
       <c r="AJ13">
-        <v>0.8292586947578544</v>
+        <v>0.8292586980788871</v>
       </c>
       <c r="AK13">
-        <v>0.4093760998991058</v>
+        <v>0.4093761027938649</v>
       </c>
       <c r="AL13">
-        <v>28.5365199121314</v>
+        <v>28.53651991117415</v>
       </c>
       <c r="AM13">
-        <v>0.838455531982401</v>
+        <v>0.8384555379789667</v>
       </c>
       <c r="AN13">
-        <v>0.385895625438136</v>
+        <v>0.3858956255608932</v>
       </c>
       <c r="AO13">
-        <v>28.56303224880342</v>
+        <v>28.56303219811656</v>
       </c>
       <c r="AP13">
-        <v>0.8476495289339984</v>
+        <v>0.8476495395506208</v>
       </c>
       <c r="AQ13">
-        <v>0.3846510861913531</v>
+        <v>0.3846510885131632</v>
       </c>
       <c r="AR13">
-        <v>29.08795354073128</v>
+        <v>29.08795365431898</v>
       </c>
       <c r="AS13">
-        <v>0.8552980048096673</v>
+        <v>0.8552980134334724</v>
       </c>
       <c r="AT13">
-        <v>0.3617976302076865</v>
+        <v>0.3617976253495353</v>
       </c>
       <c r="AU13">
-        <v>29.2182888038573</v>
+        <v>29.21828863082761</v>
       </c>
       <c r="AV13">
-        <v>0.8636449591608242</v>
+        <v>0.8636449676929638</v>
       </c>
       <c r="AW13">
-        <v>0.3560396188236627</v>
+        <v>0.3560396266091589</v>
       </c>
       <c r="AX13">
-        <v>29.98225553056636</v>
+        <v>29.98225492317958</v>
       </c>
       <c r="AY13">
-        <v>0.8705691232402755</v>
+        <v>0.8705691329727364</v>
       </c>
       <c r="AZ13">
-        <v>0.3218966079262589</v>
+        <v>0.3218966353645266</v>
       </c>
     </row>
     <row r="14">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>23.42021443921109</v>
+        <v>23.42021444099208</v>
       </c>
       <c r="E14">
         <v>36.7783252635105</v>
@@ -2613,139 +2613,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H14">
-        <v>27.60606589490132</v>
+        <v>27.60606589124647</v>
       </c>
       <c r="I14">
-        <v>0.4485398169543739</v>
+        <v>0.4485398170934217</v>
       </c>
       <c r="J14">
-        <v>0.4259866773691758</v>
+        <v>0.4259866775211756</v>
       </c>
       <c r="K14">
-        <v>23.64466095584059</v>
+        <v>23.64466095908183</v>
       </c>
       <c r="L14">
-        <v>0.6120047585857009</v>
+        <v>0.6120047584910573</v>
       </c>
       <c r="M14">
-        <v>0.5788855496486157</v>
+        <v>0.5788855495331494</v>
       </c>
       <c r="N14">
-        <v>22.26349513952713</v>
+        <v>22.26349513978322</v>
       </c>
       <c r="O14">
-        <v>0.6763062763003131</v>
+        <v>0.6763062760980596</v>
       </c>
       <c r="P14">
-        <v>0.6265842503391412</v>
+        <v>0.6265842503305433</v>
       </c>
       <c r="Q14">
-        <v>21.97191101103775</v>
+        <v>21.97191100605824</v>
       </c>
       <c r="R14">
-        <v>0.6878703626195042</v>
+        <v>0.6878703626393846</v>
       </c>
       <c r="S14">
-        <v>0.6363031620127618</v>
+        <v>0.6363031621768244</v>
       </c>
       <c r="T14">
-        <v>21.94418793014658</v>
+        <v>21.94418792458067</v>
       </c>
       <c r="U14">
-        <v>0.7128328963973657</v>
+        <v>0.7128328962262438</v>
       </c>
       <c r="V14">
-        <v>0.637168258726418</v>
+        <v>0.6371682589084904</v>
       </c>
       <c r="W14">
-        <v>21.51143818163562</v>
+        <v>21.5114381969727</v>
       </c>
       <c r="X14">
-        <v>0.7188079138014601</v>
+        <v>0.7188079132259079</v>
       </c>
       <c r="Y14">
-        <v>0.6513511554313515</v>
+        <v>0.6513511549353476</v>
       </c>
       <c r="Z14">
-        <v>21.87188628809542</v>
+        <v>21.87188632858232</v>
       </c>
       <c r="AA14">
-        <v>0.7321503554785089</v>
+        <v>0.7321503543348931</v>
       </c>
       <c r="AB14">
-        <v>0.6395466321422894</v>
+        <v>0.6395466308090545</v>
       </c>
       <c r="AC14">
-        <v>21.75857472513464</v>
+        <v>21.7585748008359</v>
       </c>
       <c r="AD14">
-        <v>0.7464360105776009</v>
+        <v>0.7464360093096869</v>
       </c>
       <c r="AE14">
-        <v>0.6432820255965533</v>
+        <v>0.6432820231142474</v>
       </c>
       <c r="AF14">
-        <v>21.90370462002536</v>
+        <v>21.90370469573387</v>
       </c>
       <c r="AG14">
-        <v>0.7575777158710986</v>
+        <v>0.757577714681643</v>
       </c>
       <c r="AH14">
-        <v>0.6384006947307795</v>
+        <v>0.6384006922296377</v>
       </c>
       <c r="AI14">
-        <v>22.30331961791545</v>
+        <v>22.30331977132392</v>
       </c>
       <c r="AJ14">
-        <v>0.7655713227924297</v>
+        <v>0.7655713206250591</v>
       </c>
       <c r="AK14">
-        <v>0.6250744182237202</v>
+        <v>0.6250744130780642</v>
       </c>
       <c r="AL14">
-        <v>22.4087906465057</v>
+        <v>22.40879041794375</v>
       </c>
       <c r="AM14">
-        <v>0.7732484260914736</v>
+        <v>0.7732484233298798</v>
       </c>
       <c r="AN14">
-        <v>0.6214878063881102</v>
+        <v>0.6214878142483484</v>
       </c>
       <c r="AO14">
-        <v>23.13311734908687</v>
+        <v>23.13312317019974</v>
       </c>
       <c r="AP14">
-        <v>0.7773295341039215</v>
+        <v>0.7773295323796515</v>
       </c>
       <c r="AQ14">
-        <v>0.5966179309399365</v>
+        <v>0.5966177302613578</v>
       </c>
       <c r="AR14">
-        <v>23.91885706162042</v>
+        <v>23.91885820366855</v>
       </c>
       <c r="AS14">
-        <v>0.7824535508271264</v>
+        <v>0.7824535513957942</v>
       </c>
       <c r="AT14">
-        <v>0.5686812365904859</v>
+        <v>0.56868119558305</v>
       </c>
       <c r="AU14">
-        <v>24.94812562043692</v>
+        <v>24.94812655154487</v>
       </c>
       <c r="AV14">
-        <v>0.7870817943225555</v>
+        <v>0.7870817985588006</v>
       </c>
       <c r="AW14">
-        <v>0.5307024975454619</v>
+        <v>0.5307024624650931</v>
       </c>
       <c r="AX14">
-        <v>26.21645496382816</v>
+        <v>26.21645564217529</v>
       </c>
       <c r="AY14">
-        <v>0.7927494725763725</v>
+        <v>0.7927494791658134</v>
       </c>
       <c r="AZ14">
-        <v>0.4817706674435866</v>
+        <v>0.4817706407640922</v>
       </c>
     </row>
     <row r="15">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>23.41323295937379</v>
+        <v>23.41323296228076</v>
       </c>
       <c r="E15">
         <v>36.7783252635105</v>
@@ -2777,139 +2777,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H15">
-        <v>27.59170027590058</v>
+        <v>27.59170027229619</v>
       </c>
       <c r="I15">
-        <v>0.448511715328396</v>
+        <v>0.4485117154680227</v>
       </c>
       <c r="J15">
-        <v>0.426582304168972</v>
+        <v>0.4265823043187869</v>
       </c>
       <c r="K15">
-        <v>23.59413662465715</v>
+        <v>23.5941366279579</v>
       </c>
       <c r="L15">
-        <v>0.6120032947009737</v>
+        <v>0.6120032946067177</v>
       </c>
       <c r="M15">
-        <v>0.5806889119271192</v>
+        <v>0.5806889118098054</v>
       </c>
       <c r="N15">
-        <v>22.21786788141292</v>
+        <v>22.21786788077658</v>
       </c>
       <c r="O15">
-        <v>0.6762586925598717</v>
+        <v>0.6762586923585296</v>
       </c>
       <c r="P15">
-        <v>0.628141816395726</v>
+        <v>0.6281418164179143</v>
       </c>
       <c r="Q15">
-        <v>21.97131201498312</v>
+        <v>21.97131200907974</v>
       </c>
       <c r="R15">
-        <v>0.6878087637275889</v>
+        <v>0.687808763748508</v>
       </c>
       <c r="S15">
-        <v>0.6363369524474436</v>
+        <v>0.6363369526434711</v>
       </c>
       <c r="T15">
-        <v>21.92415320054153</v>
+        <v>21.92415319564102</v>
       </c>
       <c r="U15">
-        <v>0.712700239775986</v>
+        <v>0.7127002396053117</v>
       </c>
       <c r="V15">
-        <v>0.6378467126661298</v>
+        <v>0.6378467128291959</v>
       </c>
       <c r="W15">
-        <v>21.68077781262449</v>
+        <v>21.68077782806868</v>
       </c>
       <c r="X15">
-        <v>0.7185632200713277</v>
+        <v>0.7185632195033188</v>
       </c>
       <c r="Y15">
-        <v>0.6458420352814049</v>
+        <v>0.6458420347786481</v>
       </c>
       <c r="Z15">
-        <v>21.87381079191639</v>
+        <v>21.87381083337904</v>
       </c>
       <c r="AA15">
-        <v>0.7313985817540859</v>
+        <v>0.7313985806369288</v>
       </c>
       <c r="AB15">
-        <v>0.6395098093529729</v>
+        <v>0.6395098079861467</v>
       </c>
       <c r="AC15">
-        <v>21.7221236021629</v>
+        <v>21.72212367662943</v>
       </c>
       <c r="AD15">
-        <v>0.7451195419212586</v>
+        <v>0.7451195407151904</v>
       </c>
       <c r="AE15">
-        <v>0.6444741665038215</v>
+        <v>0.6444741640662915</v>
       </c>
       <c r="AF15">
-        <v>21.68622426195142</v>
+        <v>21.68622433202991</v>
       </c>
       <c r="AG15">
-        <v>0.7551617992987796</v>
+        <v>0.7551617982218479</v>
       </c>
       <c r="AH15">
-        <v>0.6455478638604474</v>
+        <v>0.6455478615751734</v>
       </c>
       <c r="AI15">
-        <v>22.13685262361262</v>
+        <v>22.1368526966992</v>
       </c>
       <c r="AJ15">
-        <v>0.7623327996823989</v>
+        <v>0.7623327978307617</v>
       </c>
       <c r="AK15">
-        <v>0.6306475204323497</v>
+        <v>0.6306475180140872</v>
       </c>
       <c r="AL15">
-        <v>22.27251032691699</v>
+        <v>22.27251044828548</v>
       </c>
       <c r="AM15">
-        <v>0.768741351489313</v>
+        <v>0.7687413491641231</v>
       </c>
       <c r="AN15">
-        <v>0.6261437395520019</v>
+        <v>0.6261437354887247</v>
       </c>
       <c r="AO15">
-        <v>22.93153936470334</v>
+        <v>22.93153970438491</v>
       </c>
       <c r="AP15">
-        <v>0.7727528621171182</v>
+        <v>0.772752860381046</v>
       </c>
       <c r="AQ15">
-        <v>0.6036634207492984</v>
+        <v>0.6036634089986597</v>
       </c>
       <c r="AR15">
-        <v>23.87447966338266</v>
+        <v>23.87448034282295</v>
       </c>
       <c r="AS15">
-        <v>0.7791242477083333</v>
+        <v>0.7791242478563758</v>
       </c>
       <c r="AT15">
-        <v>0.5703108351178851</v>
+        <v>0.5703108106724142</v>
       </c>
       <c r="AU15">
-        <v>24.48465100593403</v>
+        <v>24.48465186035787</v>
       </c>
       <c r="AV15">
-        <v>0.783352542439949</v>
+        <v>0.7833525457493197</v>
       </c>
       <c r="AW15">
-        <v>0.5479881281384356</v>
+        <v>0.5479880965987717</v>
       </c>
       <c r="AX15">
-        <v>24.87294640495942</v>
+        <v>24.87294730792258</v>
       </c>
       <c r="AY15">
-        <v>0.7860256116781796</v>
+        <v>0.7860256165075203</v>
       </c>
       <c r="AZ15">
-        <v>0.5335676259700074</v>
+        <v>0.5335675921304046</v>
       </c>
     </row>
     <row r="16">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>23.38569913701723</v>
+        <v>23.38569913928153</v>
       </c>
       <c r="E16">
         <v>36.7783252635105</v>
@@ -2941,139 +2941,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H16">
-        <v>27.55013953430371</v>
+        <v>27.55013953036375</v>
       </c>
       <c r="I16">
-        <v>0.448476346110824</v>
+        <v>0.4484763462500794</v>
       </c>
       <c r="J16">
-        <v>0.428316045949979</v>
+        <v>0.4283160461134877</v>
       </c>
       <c r="K16">
-        <v>23.57626920252729</v>
+        <v>23.57626920582006</v>
       </c>
       <c r="L16">
-        <v>0.6119996016794711</v>
+        <v>0.6119996015841751</v>
       </c>
       <c r="M16">
-        <v>0.5813165641942674</v>
+        <v>0.581316564077342</v>
       </c>
       <c r="N16">
-        <v>22.15158784839401</v>
+        <v>22.15158784876487</v>
       </c>
       <c r="O16">
-        <v>0.6761995977983097</v>
+        <v>0.6761995975958544</v>
       </c>
       <c r="P16">
-        <v>0.6303489025766604</v>
+        <v>0.6303489025645743</v>
       </c>
       <c r="Q16">
-        <v>21.88742173820344</v>
+        <v>21.88742173297967</v>
       </c>
       <c r="R16">
-        <v>0.6877566283887291</v>
+        <v>0.6877566284081869</v>
       </c>
       <c r="S16">
-        <v>0.6391117153933984</v>
+        <v>0.6391117155657522</v>
       </c>
       <c r="T16">
-        <v>21.85556703820013</v>
+        <v>21.85556703485312</v>
       </c>
       <c r="U16">
-        <v>0.7126973949292821</v>
+        <v>0.71269739476026</v>
       </c>
       <c r="V16">
-        <v>0.6401182669737909</v>
+        <v>0.640118267083967</v>
       </c>
       <c r="W16">
-        <v>21.48473298142548</v>
+        <v>21.48473299901772</v>
       </c>
       <c r="X16">
-        <v>0.7185199001842656</v>
+        <v>0.7185198996171657</v>
       </c>
       <c r="Y16">
-        <v>0.6522391825315378</v>
+        <v>0.6522391819617206</v>
       </c>
       <c r="Z16">
-        <v>21.80813661634943</v>
+        <v>21.80813666239321</v>
       </c>
       <c r="AA16">
-        <v>0.7310524955354933</v>
+        <v>0.7310524944190255</v>
       </c>
       <c r="AB16">
-        <v>0.6416777042578031</v>
+        <v>0.6416777027466827</v>
       </c>
       <c r="AC16">
-        <v>21.72594072811846</v>
+        <v>21.72594081317169</v>
       </c>
       <c r="AD16">
-        <v>0.7442990558997337</v>
+        <v>0.7442990546667488</v>
       </c>
       <c r="AE16">
-        <v>0.6443647177612216</v>
+        <v>0.6443647149624139</v>
       </c>
       <c r="AF16">
-        <v>21.86229268593325</v>
+        <v>21.86229278093329</v>
       </c>
       <c r="AG16">
-        <v>0.7534807251128877</v>
+        <v>0.7534807239877417</v>
       </c>
       <c r="AH16">
-        <v>0.6398027348383444</v>
+        <v>0.6398027317047205</v>
       </c>
       <c r="AI16">
-        <v>22.236299124814</v>
+        <v>22.23629924965807</v>
       </c>
       <c r="AJ16">
-        <v>0.760408363610112</v>
+        <v>0.7604083617425883</v>
       </c>
       <c r="AK16">
-        <v>0.6273511222868448</v>
+        <v>0.627351118094336</v>
       </c>
       <c r="AL16">
-        <v>22.35968841805719</v>
+        <v>22.35968805993505</v>
       </c>
       <c r="AM16">
-        <v>0.765723677635098</v>
+        <v>0.765723675276799</v>
       </c>
       <c r="AN16">
-        <v>0.623190331150643</v>
+        <v>0.6231903441137577</v>
       </c>
       <c r="AO16">
-        <v>23.27933794412284</v>
+        <v>23.27934121961515</v>
       </c>
       <c r="AP16">
-        <v>0.770422751839026</v>
+        <v>0.7704227502643802</v>
       </c>
       <c r="AQ16">
-        <v>0.591504181022092</v>
+        <v>0.591504060647724</v>
       </c>
       <c r="AR16">
-        <v>24.38892326810109</v>
+        <v>24.38892585977937</v>
       </c>
       <c r="AS16">
-        <v>0.7763525053617326</v>
+        <v>0.7763525055791093</v>
       </c>
       <c r="AT16">
-        <v>0.5516242912197713</v>
+        <v>0.5516241930013434</v>
       </c>
       <c r="AU16">
-        <v>25.1722732278754</v>
+        <v>25.17227418393435</v>
       </c>
       <c r="AV16">
-        <v>0.7821635191024041</v>
+        <v>0.7821635236213812</v>
       </c>
       <c r="AW16">
-        <v>0.5223385003622713</v>
+        <v>0.5223384641283746</v>
       </c>
       <c r="AX16">
-        <v>25.45765798310528</v>
+        <v>25.45765907061669</v>
       </c>
       <c r="AY16">
-        <v>0.7850589466587238</v>
+        <v>0.7850589524700946</v>
       </c>
       <c r="AZ16">
-        <v>0.5113977505331011</v>
+        <v>0.5113977085784156</v>
       </c>
     </row>
     <row r="17">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>23.51267073655991</v>
+        <v>23.51267074021806</v>
       </c>
       <c r="E17">
         <v>36.7783252635105</v>
@@ -3105,139 +3105,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H17">
-        <v>27.61975331949987</v>
+        <v>27.61975331570352</v>
       </c>
       <c r="I17">
-        <v>0.4483883977671762</v>
+        <v>0.4483883979054948</v>
       </c>
       <c r="J17">
-        <v>0.425414093594182</v>
+        <v>0.4254140937521366</v>
       </c>
       <c r="K17">
-        <v>23.6145049643131</v>
+        <v>23.61450496777763</v>
       </c>
       <c r="L17">
-        <v>0.6119913577504019</v>
+        <v>0.6119913576537817</v>
       </c>
       <c r="M17">
-        <v>0.5799663772002934</v>
+        <v>0.5799663770770407</v>
       </c>
       <c r="N17">
-        <v>22.20936542526425</v>
+        <v>22.20936542524916</v>
       </c>
       <c r="O17">
-        <v>0.6760864073434152</v>
+        <v>0.6760864071390248</v>
       </c>
       <c r="P17">
-        <v>0.6284166136780801</v>
+        <v>0.6284166136793</v>
       </c>
       <c r="Q17">
-        <v>21.93797437188601</v>
+        <v>21.93797436692451</v>
       </c>
       <c r="R17">
-        <v>0.6876694066214953</v>
+        <v>0.6876694066381064</v>
       </c>
       <c r="S17">
-        <v>0.6374476312687694</v>
+        <v>0.6374476314334129</v>
       </c>
       <c r="T17">
-        <v>21.90046353852195</v>
+        <v>21.90046353509702</v>
       </c>
       <c r="U17">
-        <v>0.7127258522238242</v>
+        <v>0.7127258520534295</v>
       </c>
       <c r="V17">
-        <v>0.6386483778135</v>
+        <v>0.6386483779276955</v>
       </c>
       <c r="W17">
-        <v>21.58546381954101</v>
+        <v>21.58546383252595</v>
       </c>
       <c r="X17">
-        <v>0.7185493417264381</v>
+        <v>0.7185493411531061</v>
       </c>
       <c r="Y17">
-        <v>0.6489561298372426</v>
+        <v>0.6489561294207166</v>
       </c>
       <c r="Z17">
-        <v>21.76249050031661</v>
+        <v>21.76249054231277</v>
       </c>
       <c r="AA17">
-        <v>0.7308744008531578</v>
+        <v>0.730874399733848</v>
       </c>
       <c r="AB17">
-        <v>0.6431639786747028</v>
+        <v>0.6431639772971526</v>
       </c>
       <c r="AC17">
-        <v>21.65854282711069</v>
+        <v>21.65854289922422</v>
       </c>
       <c r="AD17">
-        <v>0.7440946090728079</v>
+        <v>0.7440946078391201</v>
       </c>
       <c r="AE17">
-        <v>0.6465567794211955</v>
+        <v>0.6465567770777291</v>
       </c>
       <c r="AF17">
-        <v>21.78464296283326</v>
+        <v>21.78464304005697</v>
       </c>
       <c r="AG17">
-        <v>0.7525416934845811</v>
+        <v>0.7525416923556033</v>
       </c>
       <c r="AH17">
-        <v>0.6423666945935415</v>
+        <v>0.6423666920596968</v>
       </c>
       <c r="AI17">
-        <v>22.10938132253519</v>
+        <v>22.10938143808346</v>
       </c>
       <c r="AJ17">
-        <v>0.7596468122731121</v>
+        <v>0.7596468104820376</v>
       </c>
       <c r="AK17">
-        <v>0.6315985783848117</v>
+        <v>0.6315985745445086</v>
       </c>
       <c r="AL17">
-        <v>22.20434947739927</v>
+        <v>22.20434966271311</v>
       </c>
       <c r="AM17">
-        <v>0.7642136766817194</v>
+        <v>0.764213674451597</v>
       </c>
       <c r="AN17">
-        <v>0.6284865556975443</v>
+        <v>0.6284865495406007</v>
       </c>
       <c r="AO17">
-        <v>23.09612588883173</v>
+        <v>23.09612627339046</v>
       </c>
       <c r="AP17">
-        <v>0.7689700890305078</v>
+        <v>0.7689700879393518</v>
       </c>
       <c r="AQ17">
-        <v>0.5980455456995405</v>
+        <v>0.5980455322956706</v>
       </c>
       <c r="AR17">
-        <v>24.07303430913865</v>
+        <v>24.07303516358704</v>
       </c>
       <c r="AS17">
-        <v>0.7735409597238408</v>
+        <v>0.7735409609506416</v>
       </c>
       <c r="AT17">
-        <v>0.5632134588008192</v>
+        <v>0.5632134277239086</v>
       </c>
       <c r="AU17">
-        <v>24.95160860784868</v>
+        <v>24.95160979000925</v>
       </c>
       <c r="AV17">
-        <v>0.7790692820746439</v>
+        <v>0.7790692874181352</v>
       </c>
       <c r="AW17">
-        <v>0.5307725051788302</v>
+        <v>0.5307724606787082</v>
       </c>
       <c r="AX17">
-        <v>25.13242046733274</v>
+        <v>25.13242153624124</v>
       </c>
       <c r="AY17">
-        <v>0.7817854829898545</v>
+        <v>0.7817854900815581</v>
       </c>
       <c r="AZ17">
-        <v>0.5239530228168146</v>
+        <v>0.5239529822483884</v>
       </c>
     </row>
     <row r="18">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>22.93002023258162</v>
+        <v>22.93002022252789</v>
       </c>
       <c r="E18">
         <v>36.7783252635105</v>
@@ -3269,139 +3269,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H18">
-        <v>22.90516967387523</v>
+        <v>22.90516966452478</v>
       </c>
       <c r="I18">
-        <v>0.6254383605318308</v>
+        <v>0.6254383607921536</v>
       </c>
       <c r="J18">
-        <v>0.6048280275615323</v>
+        <v>0.6048280278842164</v>
       </c>
       <c r="K18">
-        <v>22.65972778016634</v>
+        <v>22.65972775720069</v>
       </c>
       <c r="L18">
-        <v>0.6615932431008031</v>
+        <v>0.6615932435039857</v>
       </c>
       <c r="M18">
-        <v>0.6132125453901094</v>
+        <v>0.6132125461754889</v>
       </c>
       <c r="N18">
-        <v>22.53516786912764</v>
+        <v>22.53516784624815</v>
       </c>
       <c r="O18">
-        <v>0.6803159302351702</v>
+        <v>0.6803159305241049</v>
       </c>
       <c r="P18">
-        <v>0.6174224091509803</v>
+        <v>0.6174224099286715</v>
       </c>
       <c r="Q18">
-        <v>22.62887294912777</v>
+        <v>22.62887291749487</v>
       </c>
       <c r="R18">
-        <v>0.7141598823445331</v>
+        <v>0.7141598827666347</v>
       </c>
       <c r="S18">
-        <v>0.6141245868084009</v>
+        <v>0.6141245878936162</v>
       </c>
       <c r="T18">
-        <v>22.29499805086678</v>
+        <v>22.29499799293087</v>
       </c>
       <c r="U18">
-        <v>0.7359262614007329</v>
+        <v>0.7359262627309882</v>
       </c>
       <c r="V18">
-        <v>0.6254506645065848</v>
+        <v>0.625450666457595</v>
       </c>
       <c r="W18">
-        <v>22.71265358093166</v>
+        <v>22.71265349516694</v>
       </c>
       <c r="X18">
-        <v>0.7490036951458934</v>
+        <v>0.7490036965056753</v>
       </c>
       <c r="Y18">
-        <v>0.6112325596599963</v>
+        <v>0.6112325626022511</v>
       </c>
       <c r="Z18">
-        <v>23.06402160834019</v>
+        <v>23.06402148563959</v>
       </c>
       <c r="AA18">
-        <v>0.7548996462337879</v>
+        <v>0.7548996475605068</v>
       </c>
       <c r="AB18">
-        <v>0.5990669656960811</v>
+        <v>0.5990669699711547</v>
       </c>
       <c r="AC18">
-        <v>24.05604849232914</v>
+        <v>24.05604838061425</v>
       </c>
       <c r="AD18">
-        <v>0.7687696820856427</v>
+        <v>0.7687696827271002</v>
       </c>
       <c r="AE18">
-        <v>0.5638008815597547</v>
+        <v>0.5638008855919032</v>
       </c>
       <c r="AF18">
-        <v>25.53244051187466</v>
+        <v>25.53244038514083</v>
       </c>
       <c r="AG18">
-        <v>0.7851600933200761</v>
+        <v>0.785160093807154</v>
       </c>
       <c r="AH18">
-        <v>0.5085604627778048</v>
+        <v>0.5085604677525242</v>
       </c>
       <c r="AI18">
-        <v>26.93647133749117</v>
+        <v>26.93647139017809</v>
       </c>
       <c r="AJ18">
-        <v>0.8065791099999177</v>
+        <v>0.8065791129326897</v>
       </c>
       <c r="AK18">
-        <v>0.4528816169458693</v>
+        <v>0.4528816148081412</v>
       </c>
       <c r="AL18">
-        <v>28.12088341926346</v>
+        <v>28.12088346657677</v>
       </c>
       <c r="AM18">
-        <v>0.8337853679740084</v>
+        <v>0.8337853709063427</v>
       </c>
       <c r="AN18">
-        <v>0.4036717779086803</v>
+        <v>0.4036717758327261</v>
       </c>
       <c r="AO18">
-        <v>28.66611935089072</v>
+        <v>28.66611929878208</v>
       </c>
       <c r="AP18">
-        <v>0.8537398902986324</v>
+        <v>0.8537398959053895</v>
       </c>
       <c r="AQ18">
-        <v>0.3803605297511429</v>
+        <v>0.3803605318853507</v>
       </c>
       <c r="AR18">
-        <v>28.60670630005903</v>
+        <v>28.60670606825984</v>
       </c>
       <c r="AS18">
-        <v>0.8695941886802027</v>
+        <v>0.8695941941724757</v>
       </c>
       <c r="AT18">
-        <v>0.3829515780051978</v>
+        <v>0.3829515879148847</v>
       </c>
       <c r="AU18">
-        <v>28.54419198370611</v>
+        <v>28.54419168132018</v>
       </c>
       <c r="AV18">
-        <v>0.8802843150270426</v>
+        <v>0.8802843220730754</v>
       </c>
       <c r="AW18">
-        <v>0.3856053403727036</v>
+        <v>0.3856053533625796</v>
       </c>
       <c r="AX18">
-        <v>28.4958307833114</v>
+        <v>28.49583027500374</v>
       </c>
       <c r="AY18">
-        <v>0.8906915769326352</v>
+        <v>0.8906915856461557</v>
       </c>
       <c r="AZ18">
-        <v>0.3876453328147946</v>
+        <v>0.3876453545824327</v>
       </c>
     </row>
     <row r="19">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>22.88617254897265</v>
+        <v>22.88617253573263</v>
       </c>
       <c r="E19">
         <v>36.7783252635105</v>
@@ -3433,139 +3433,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H19">
-        <v>22.9430415393879</v>
+        <v>22.94304152974073</v>
       </c>
       <c r="I19">
-        <v>0.6224919371108901</v>
+        <v>0.6224919373947508</v>
       </c>
       <c r="J19">
-        <v>0.6035260226801238</v>
+        <v>0.6035260230135787</v>
       </c>
       <c r="K19">
-        <v>22.6793157246678</v>
+        <v>22.67931569106611</v>
       </c>
       <c r="L19">
-        <v>0.6569526195550701</v>
+        <v>0.6569526205101114</v>
       </c>
       <c r="M19">
-        <v>0.6125445767937102</v>
+        <v>0.6125445779415638</v>
       </c>
       <c r="N19">
-        <v>22.30516907960531</v>
+        <v>22.30516903381145</v>
       </c>
       <c r="O19">
-        <v>0.6800145127323822</v>
+        <v>0.6800145138052947</v>
       </c>
       <c r="P19">
-        <v>0.6251954338299706</v>
+        <v>0.6251954353705453</v>
       </c>
       <c r="Q19">
-        <v>22.10655515757632</v>
+        <v>22.10655509429925</v>
       </c>
       <c r="R19">
-        <v>0.7165034068000445</v>
+        <v>0.7165034082796765</v>
       </c>
       <c r="S19">
-        <v>0.631793468497566</v>
+        <v>0.6317934706086885</v>
       </c>
       <c r="T19">
-        <v>21.58192551259063</v>
+        <v>21.58192543834575</v>
       </c>
       <c r="U19">
-        <v>0.7328083539668219</v>
+        <v>0.7328083555274494</v>
       </c>
       <c r="V19">
-        <v>0.6490901607129477</v>
+        <v>0.6490901631293208</v>
       </c>
       <c r="W19">
-        <v>22.28802887224624</v>
+        <v>22.28802878301613</v>
       </c>
       <c r="X19">
-        <v>0.7496493698460083</v>
+        <v>0.7496493723881221</v>
       </c>
       <c r="Y19">
-        <v>0.6256713141672268</v>
+        <v>0.6256713171632933</v>
       </c>
       <c r="Z19">
-        <v>22.31018242922438</v>
+        <v>22.3101823584862</v>
       </c>
       <c r="AA19">
-        <v>0.7537754773242387</v>
+        <v>0.7537754793563489</v>
       </c>
       <c r="AB19">
-        <v>0.6248825765472829</v>
+        <v>0.6248825789529077</v>
       </c>
       <c r="AC19">
-        <v>23.10108851053826</v>
+        <v>23.10108843252641</v>
       </c>
       <c r="AD19">
-        <v>0.7681085013189776</v>
+        <v>0.7681085036352001</v>
       </c>
       <c r="AE19">
-        <v>0.597833241393123</v>
+        <v>0.5978332441133322</v>
       </c>
       <c r="AF19">
-        <v>23.95846370923473</v>
+        <v>23.95846370822508</v>
       </c>
       <c r="AG19">
-        <v>0.7814253983096977</v>
+        <v>0.7814254014204703</v>
       </c>
       <c r="AH19">
-        <v>0.5674346315954505</v>
+        <v>0.5674346316461001</v>
       </c>
       <c r="AI19">
-        <v>24.97324740068089</v>
+        <v>24.9732475997866</v>
       </c>
       <c r="AJ19">
-        <v>0.7960308910790488</v>
+        <v>0.7960308973195072</v>
       </c>
       <c r="AK19">
-        <v>0.5300060466212377</v>
+        <v>0.5300060391269682</v>
       </c>
       <c r="AL19">
-        <v>25.91170996561246</v>
+        <v>25.91171019757588</v>
       </c>
       <c r="AM19">
-        <v>0.8111325045249616</v>
+        <v>0.8111325128062459</v>
       </c>
       <c r="AN19">
-        <v>0.4939871825334476</v>
+        <v>0.4939871734830261</v>
       </c>
       <c r="AO19">
-        <v>26.45919657665976</v>
+        <v>26.45919664550242</v>
       </c>
       <c r="AP19">
-        <v>0.8255041231691379</v>
+        <v>0.825504135421071</v>
       </c>
       <c r="AQ19">
-        <v>0.4722500957525277</v>
+        <v>0.4722500930028244</v>
       </c>
       <c r="AR19">
-        <v>27.03156649998978</v>
+        <v>27.03156635459789</v>
       </c>
       <c r="AS19">
-        <v>0.8464922887994928</v>
+        <v>0.8464923064611596</v>
       </c>
       <c r="AT19">
-        <v>0.4490855669258114</v>
+        <v>0.449085572847302</v>
       </c>
       <c r="AU19">
-        <v>27.28029391838836</v>
+        <v>27.28029353780907</v>
       </c>
       <c r="AV19">
-        <v>0.8601290595470664</v>
+        <v>0.8601290798431303</v>
       </c>
       <c r="AW19">
-        <v>0.438766961381643</v>
+        <v>0.4387669770594776</v>
       </c>
       <c r="AX19">
-        <v>27.72987483727537</v>
+        <v>27.72987398287913</v>
       </c>
       <c r="AY19">
-        <v>0.8763064415308368</v>
+        <v>0.8763064613178148</v>
       </c>
       <c r="AZ19">
-        <v>0.4200046458487685</v>
+        <v>0.4200046817305113</v>
       </c>
     </row>
     <row r="20">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="D20">
-        <v>22.97406102832392</v>
+        <v>22.97406101924467</v>
       </c>
       <c r="E20">
         <v>36.7783252635105</v>
@@ -3597,139 +3597,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H20">
-        <v>22.96490732064066</v>
+        <v>22.96490731466415</v>
       </c>
       <c r="I20">
-        <v>0.6210910742831441</v>
+        <v>0.6210910744724669</v>
       </c>
       <c r="J20">
-        <v>0.6027578627871766</v>
+        <v>0.6027578629939608</v>
       </c>
       <c r="K20">
-        <v>22.51573262260802</v>
+        <v>22.51573259749283</v>
       </c>
       <c r="L20">
-        <v>0.652308683871048</v>
+        <v>0.6523086847929229</v>
       </c>
       <c r="M20">
-        <v>0.6180968301972832</v>
+        <v>0.6180968310477329</v>
       </c>
       <c r="N20">
-        <v>21.97081063064355</v>
+        <v>21.97081058896649</v>
       </c>
       <c r="O20">
-        <v>0.6890106574368681</v>
+        <v>0.6890106585289716</v>
       </c>
       <c r="P20">
-        <v>0.6363694576856784</v>
+        <v>0.6363694590648233</v>
       </c>
       <c r="Q20">
-        <v>21.90573259404525</v>
+        <v>21.90573254436877</v>
       </c>
       <c r="R20">
-        <v>0.7201519444868552</v>
+        <v>0.7201519454943919</v>
       </c>
       <c r="S20">
-        <v>0.6384660344500601</v>
+        <v>0.6384660360902915</v>
       </c>
       <c r="T20">
-        <v>21.55522011534194</v>
+        <v>21.55522007588914</v>
       </c>
       <c r="U20">
-        <v>0.7271502225270039</v>
+        <v>0.7271502235733336</v>
       </c>
       <c r="V20">
-        <v>0.6499411537076493</v>
+        <v>0.6499411549892145</v>
       </c>
       <c r="W20">
-        <v>21.55098299062412</v>
+        <v>21.55098296764943</v>
       </c>
       <c r="X20">
-        <v>0.7365979628652959</v>
+        <v>0.7365979630255401</v>
       </c>
       <c r="Y20">
-        <v>0.6500919321258721</v>
+        <v>0.6500919328757052</v>
       </c>
       <c r="Z20">
-        <v>22.0239883648014</v>
+        <v>22.0239882803284</v>
       </c>
       <c r="AA20">
-        <v>0.7417708681833041</v>
+        <v>0.7417708682939842</v>
       </c>
       <c r="AB20">
-        <v>0.6344770703052395</v>
+        <v>0.6344770731502605</v>
       </c>
       <c r="AC20">
-        <v>22.9210410251444</v>
+        <v>22.92104110347071</v>
       </c>
       <c r="AD20">
-        <v>0.7585368445752898</v>
+        <v>0.7585368442245055</v>
       </c>
       <c r="AE20">
-        <v>0.604108092770223</v>
+        <v>0.6041080901604421</v>
       </c>
       <c r="AF20">
-        <v>23.57048488950909</v>
+        <v>23.57048524518121</v>
       </c>
       <c r="AG20">
-        <v>0.7672528962768913</v>
+        <v>0.7672528959920923</v>
       </c>
       <c r="AH20">
-        <v>0.5813513405686792</v>
+        <v>0.5813513280500652</v>
       </c>
       <c r="AI20">
-        <v>23.89414666110813</v>
+        <v>23.89414700918949</v>
       </c>
       <c r="AJ20">
-        <v>0.7804805812174564</v>
+        <v>0.7804805828666369</v>
       </c>
       <c r="AK20">
-        <v>0.5697630735988712</v>
+        <v>0.5697630610207722</v>
       </c>
       <c r="AL20">
-        <v>24.64305588180323</v>
+        <v>24.64305642576057</v>
       </c>
       <c r="AM20">
-        <v>0.7933934279889968</v>
+        <v>0.793393432740533</v>
       </c>
       <c r="AN20">
-        <v>0.5422588137568572</v>
+        <v>0.5422587934921683</v>
       </c>
       <c r="AO20">
-        <v>25.210933524989</v>
+        <v>25.21093407051527</v>
       </c>
       <c r="AP20">
-        <v>0.8052069952171826</v>
+        <v>0.8052070049323004</v>
       </c>
       <c r="AQ20">
-        <v>0.5207899725358203</v>
+        <v>0.5207899516909357</v>
       </c>
       <c r="AR20">
-        <v>25.3413645197961</v>
+        <v>25.34136484988977</v>
       </c>
       <c r="AS20">
-        <v>0.8128029480333711</v>
+        <v>0.8128029607183663</v>
       </c>
       <c r="AT20">
-        <v>0.5157607058078953</v>
+        <v>0.5157606930561089</v>
       </c>
       <c r="AU20">
-        <v>25.93297678088353</v>
+        <v>25.93297659719411</v>
       </c>
       <c r="AV20">
-        <v>0.8252811874362772</v>
+        <v>0.8252812046124661</v>
       </c>
       <c r="AW20">
-        <v>0.4928270958398208</v>
+        <v>0.4928271029398635</v>
       </c>
       <c r="AX20">
-        <v>26.45152686799232</v>
+        <v>26.45152584906034</v>
       </c>
       <c r="AY20">
-        <v>0.8408514889068348</v>
+        <v>0.8408515097192512</v>
       </c>
       <c r="AZ20">
-        <v>0.4722141956514787</v>
+        <v>0.4722142361540881</v>
       </c>
     </row>
     <row r="21">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>23.47506551945678</v>
+        <v>23.47506552306848</v>
       </c>
       <c r="E21">
         <v>36.7783252635105</v>
@@ -3761,139 +3761,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H21">
-        <v>26.78942463160896</v>
+        <v>26.78942474889375</v>
       </c>
       <c r="I21">
-        <v>0.4998168181581377</v>
+        <v>0.4998168131317556</v>
       </c>
       <c r="J21">
-        <v>0.4594094967201821</v>
+        <v>0.4594094919896185</v>
       </c>
       <c r="K21">
-        <v>23.27975194712953</v>
+        <v>23.27975193378632</v>
       </c>
       <c r="L21">
-        <v>0.6309499478194083</v>
+        <v>0.6309499477565452</v>
       </c>
       <c r="M21">
-        <v>0.5917621620045774</v>
+        <v>0.5917621624770708</v>
       </c>
       <c r="N21">
-        <v>23.68551136539971</v>
+        <v>23.68551134883124</v>
       </c>
       <c r="O21">
-        <v>0.6473903684835799</v>
+        <v>0.6473903688093816</v>
       </c>
       <c r="P21">
-        <v>0.5773449418066126</v>
+        <v>0.5773449424015602</v>
       </c>
       <c r="Q21">
-        <v>24.79598854105599</v>
+        <v>24.79598843195637</v>
       </c>
       <c r="R21">
-        <v>0.7024265058158221</v>
+        <v>0.7024265033399304</v>
       </c>
       <c r="S21">
-        <v>0.5365997377830849</v>
+        <v>0.5365997418673072</v>
       </c>
       <c r="T21">
-        <v>23.90445916029439</v>
+        <v>23.90445918096359</v>
       </c>
       <c r="U21">
-        <v>0.712791072219251</v>
+        <v>0.7127910714888923</v>
       </c>
       <c r="V21">
-        <v>0.5694354552847616</v>
+        <v>0.5694354545618674</v>
       </c>
       <c r="W21">
-        <v>24.22428109623043</v>
+        <v>24.22428114485273</v>
       </c>
       <c r="X21">
-        <v>0.729866326392413</v>
+        <v>0.729866325147372</v>
       </c>
       <c r="Y21">
-        <v>0.5576961020148301</v>
+        <v>0.5576961003548669</v>
       </c>
       <c r="Z21">
-        <v>25.78591288719219</v>
+        <v>25.78591276022516</v>
       </c>
       <c r="AA21">
-        <v>0.7532352813101333</v>
+        <v>0.7532352815743071</v>
       </c>
       <c r="AB21">
-        <v>0.4988121814989039</v>
+        <v>0.4988121865818193</v>
       </c>
       <c r="AC21">
-        <v>27.42094788180254</v>
+        <v>27.42094787553187</v>
       </c>
       <c r="AD21">
-        <v>0.7806191687085745</v>
+        <v>0.7806191704272818</v>
       </c>
       <c r="AE21">
-        <v>0.4332271354968424</v>
+        <v>0.4332271357994179</v>
       </c>
       <c r="AF21">
-        <v>27.88834621851845</v>
+        <v>27.88834634257059</v>
       </c>
       <c r="AG21">
-        <v>0.7994655046766843</v>
+        <v>0.7994655118822841</v>
       </c>
       <c r="AH21">
-        <v>0.4135817208280108</v>
+        <v>0.4135817155424485</v>
       </c>
       <c r="AI21">
-        <v>28.6913723288981</v>
+        <v>28.69137250725412</v>
       </c>
       <c r="AJ21">
-        <v>0.8225420820690176</v>
+        <v>0.8225420957461171</v>
       </c>
       <c r="AK21">
-        <v>0.379157856814734</v>
+        <v>0.3791578491959781</v>
       </c>
       <c r="AL21">
-        <v>28.97248457623677</v>
+        <v>28.97248441877643</v>
       </c>
       <c r="AM21">
-        <v>0.8438822741112624</v>
+        <v>0.8438822866260492</v>
       </c>
       <c r="AN21">
-        <v>0.3669193569855166</v>
+        <v>0.3669193639487042</v>
       </c>
       <c r="AO21">
-        <v>29.1629788123382</v>
+        <v>29.16297788357895</v>
       </c>
       <c r="AP21">
-        <v>0.8584961400551591</v>
+        <v>0.8584961460922937</v>
       </c>
       <c r="AQ21">
-        <v>0.3584796034121402</v>
+        <v>0.3584796444055692</v>
       </c>
       <c r="AR21">
-        <v>29.15534306742411</v>
+        <v>29.15534154495304</v>
       </c>
       <c r="AS21">
-        <v>0.8809394737254775</v>
+        <v>0.8809394755801971</v>
       </c>
       <c r="AT21">
-        <v>0.358657109321518</v>
+        <v>0.3586571761052978</v>
       </c>
       <c r="AU21">
-        <v>28.98013743699961</v>
+        <v>28.98013616791956</v>
       </c>
       <c r="AV21">
-        <v>0.8908000221854809</v>
+        <v>0.8908000184569481</v>
       </c>
       <c r="AW21">
-        <v>0.3662511898578257</v>
+        <v>0.3662512452329014</v>
       </c>
       <c r="AX21">
-        <v>29.35646368834329</v>
+        <v>29.35646270202353</v>
       </c>
       <c r="AY21">
-        <v>0.9011362193708056</v>
+        <v>0.9011362186316173</v>
       </c>
       <c r="AZ21">
-        <v>0.3496131153966723</v>
+        <v>0.3496131589380351</v>
       </c>
     </row>
     <row r="22">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>23.41930943252927</v>
+        <v>23.41930943027561</v>
       </c>
       <c r="E22">
         <v>36.7783252635105</v>
@@ -3925,139 +3925,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H22">
-        <v>26.81148537458581</v>
+        <v>26.81148549121632</v>
       </c>
       <c r="I22">
-        <v>0.4985239285187345</v>
+        <v>0.4985239234639995</v>
       </c>
       <c r="J22">
-        <v>0.4585224463223009</v>
+        <v>0.4585224416135819</v>
       </c>
       <c r="K22">
-        <v>23.26535551224678</v>
+        <v>23.26535549842227</v>
       </c>
       <c r="L22">
-        <v>0.6304023384182063</v>
+        <v>0.6304023383533806</v>
       </c>
       <c r="M22">
-        <v>0.5922650287191309</v>
+        <v>0.592265029205132</v>
       </c>
       <c r="N22">
-        <v>23.62417904699555</v>
+        <v>23.62417903176148</v>
       </c>
       <c r="O22">
-        <v>0.6456991833217144</v>
+        <v>0.6456991835551377</v>
       </c>
       <c r="P22">
-        <v>0.5795517816912952</v>
+        <v>0.5795517822341977</v>
       </c>
       <c r="Q22">
-        <v>24.89863637681983</v>
+        <v>24.89863626252833</v>
       </c>
       <c r="R22">
-        <v>0.7036636498679292</v>
+        <v>0.7036636470613336</v>
       </c>
       <c r="S22">
-        <v>0.5327466401852715</v>
+        <v>0.5327466444667849</v>
       </c>
       <c r="T22">
-        <v>23.81089272910262</v>
+        <v>23.81089273653851</v>
       </c>
       <c r="U22">
-        <v>0.7159647422967884</v>
+        <v>0.7159647419985862</v>
       </c>
       <c r="V22">
-        <v>0.5728129017844955</v>
+        <v>0.5728129015073971</v>
       </c>
       <c r="W22">
-        <v>23.7946602631421</v>
+        <v>23.79466044641018</v>
       </c>
       <c r="X22">
-        <v>0.7283842663457809</v>
+        <v>0.7283842674024126</v>
       </c>
       <c r="Y22">
-        <v>0.5733642259025805</v>
+        <v>0.5733642193218943</v>
       </c>
       <c r="Z22">
-        <v>25.53248809087905</v>
+        <v>25.53248793278602</v>
       </c>
       <c r="AA22">
-        <v>0.7572032707875759</v>
+        <v>0.7572032751311787</v>
       </c>
       <c r="AB22">
-        <v>0.5086481354375327</v>
+        <v>0.5086481414540436</v>
       </c>
       <c r="AC22">
-        <v>26.94566064617943</v>
+        <v>26.94566031029102</v>
       </c>
       <c r="AD22">
-        <v>0.7742680749506569</v>
+        <v>0.7742680820437958</v>
       </c>
       <c r="AE22">
-        <v>0.4527241006196184</v>
+        <v>0.4527241142240094</v>
       </c>
       <c r="AF22">
-        <v>27.71039427757603</v>
+        <v>27.71039364235025</v>
       </c>
       <c r="AG22">
-        <v>0.8005978862523466</v>
+        <v>0.8005979043706564</v>
       </c>
       <c r="AH22">
-        <v>0.4211246233507139</v>
+        <v>0.4211246497586936</v>
       </c>
       <c r="AI22">
-        <v>28.09895045042226</v>
+        <v>28.09894936732792</v>
       </c>
       <c r="AJ22">
-        <v>0.8249564073981428</v>
+        <v>0.8249564347533315</v>
       </c>
       <c r="AK22">
-        <v>0.4048716853945379</v>
+        <v>0.4048717309245515</v>
       </c>
       <c r="AL22">
-        <v>28.73921587843889</v>
+        <v>28.73921420832135</v>
       </c>
       <c r="AM22">
-        <v>0.8477920301836672</v>
+        <v>0.847792059529779</v>
       </c>
       <c r="AN22">
-        <v>0.377273312417102</v>
+        <v>0.3772733847023861</v>
       </c>
       <c r="AO22">
-        <v>28.82217457648393</v>
+        <v>28.82217089889605</v>
       </c>
       <c r="AP22">
-        <v>0.8760459809096657</v>
+        <v>0.8760460070707023</v>
       </c>
       <c r="AQ22">
-        <v>0.3733434522000036</v>
+        <v>0.3733436118642536</v>
       </c>
       <c r="AR22">
-        <v>28.71138884369403</v>
+        <v>28.71138415619367</v>
       </c>
       <c r="AS22">
-        <v>0.8865231969815063</v>
+        <v>0.8865232176191793</v>
       </c>
       <c r="AT22">
-        <v>0.3781146936590822</v>
+        <v>0.3781148961812735</v>
       </c>
       <c r="AU22">
-        <v>28.65798570068539</v>
+        <v>28.65798045111059</v>
       </c>
       <c r="AV22">
-        <v>0.8941932170273209</v>
+        <v>0.8941932349051586</v>
       </c>
       <c r="AW22">
-        <v>0.3803303859355568</v>
+        <v>0.3803306126783735</v>
       </c>
       <c r="AX22">
-        <v>29.36832966913992</v>
+        <v>29.36832426027894</v>
       </c>
       <c r="AY22">
-        <v>0.9039007781150128</v>
+        <v>0.9039007926455856</v>
       </c>
       <c r="AZ22">
-        <v>0.3491629838298661</v>
+        <v>0.3491632236332814</v>
       </c>
     </row>
     <row r="23">
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>23.08224982213964</v>
+        <v>23.08224983121686</v>
       </c>
       <c r="E23">
         <v>36.7783252635105</v>
@@ -4089,139 +4089,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H23">
-        <v>23.08224982213964</v>
+        <v>23.08224983121686</v>
       </c>
       <c r="I23">
-        <v>0.6203813130959508</v>
+        <v>0.6203813126714877</v>
       </c>
       <c r="J23">
-        <v>0.5986823751912357</v>
+        <v>0.5986823748766439</v>
       </c>
       <c r="K23">
-        <v>23.13723052455438</v>
+        <v>23.13723052785045</v>
       </c>
       <c r="L23">
-        <v>0.6311306728877625</v>
+        <v>0.6311306725670776</v>
       </c>
       <c r="M23">
-        <v>0.5967550790986996</v>
+        <v>0.5967550789903154</v>
       </c>
       <c r="N23">
-        <v>23.70027765998368</v>
+        <v>23.70027763250533</v>
       </c>
       <c r="O23">
-        <v>0.6684970969902839</v>
+        <v>0.6684970991238876</v>
       </c>
       <c r="P23">
-        <v>0.5767383474364214</v>
+        <v>0.5767383484498408</v>
       </c>
       <c r="Q23">
-        <v>23.06154718274425</v>
+        <v>23.06154723684969</v>
       </c>
       <c r="R23">
-        <v>0.6722097472374784</v>
+        <v>0.6722097484262515</v>
       </c>
       <c r="S23">
-        <v>0.5993398950115182</v>
+        <v>0.5993398930892981</v>
       </c>
       <c r="T23">
-        <v>24.68783372707723</v>
+        <v>24.68783517305369</v>
       </c>
       <c r="U23">
-        <v>0.7017561025895327</v>
+        <v>0.701756098617776</v>
       </c>
       <c r="V23">
-        <v>0.5407008956124489</v>
+        <v>0.5407008430522319</v>
       </c>
       <c r="W23">
-        <v>26.07134598977085</v>
+        <v>26.07134627445735</v>
       </c>
       <c r="X23">
-        <v>0.7431719140563344</v>
+        <v>0.7431718975152655</v>
       </c>
       <c r="Y23">
-        <v>0.4877450919148572</v>
+        <v>0.4877450806761628</v>
       </c>
       <c r="Z23">
-        <v>27.55295605841863</v>
+        <v>27.5529568695391</v>
       </c>
       <c r="AA23">
-        <v>0.7714812935442726</v>
+        <v>0.7714812670421631</v>
       </c>
       <c r="AB23">
-        <v>0.427686584466544</v>
+        <v>0.4276865509386583</v>
       </c>
       <c r="AC23">
-        <v>27.97418375021152</v>
+        <v>27.97418502429809</v>
       </c>
       <c r="AD23">
-        <v>0.7921852391362674</v>
+        <v>0.7921852126728467</v>
       </c>
       <c r="AE23">
-        <v>0.4098257213324562</v>
+        <v>0.4098256678929973</v>
       </c>
       <c r="AF23">
-        <v>27.63461971491568</v>
+        <v>27.63462148089881</v>
       </c>
       <c r="AG23">
-        <v>0.815613428682767</v>
+        <v>0.8156133804286628</v>
       </c>
       <c r="AH23">
-        <v>0.4242356891821279</v>
+        <v>0.424235615913058</v>
       </c>
       <c r="AI23">
-        <v>28.63561277880749</v>
+        <v>28.63561503055276</v>
       </c>
       <c r="AJ23">
-        <v>0.842783184662832</v>
+        <v>0.8427831095245482</v>
       </c>
       <c r="AK23">
-        <v>0.381739865475829</v>
+        <v>0.3817397687217724</v>
       </c>
       <c r="AL23">
-        <v>29.2169474568577</v>
+        <v>29.21695206203162</v>
       </c>
       <c r="AM23">
-        <v>0.8673403315813437</v>
+        <v>0.8673402571454644</v>
       </c>
       <c r="AN23">
-        <v>0.3563541371338694</v>
+        <v>0.3563539349760688</v>
       </c>
       <c r="AO23">
-        <v>29.7355990302515</v>
+        <v>29.73560673961908</v>
       </c>
       <c r="AP23">
-        <v>0.8845524947129213</v>
+        <v>0.8845524261151968</v>
       </c>
       <c r="AQ23">
-        <v>0.3333556180296163</v>
+        <v>0.3333552729662472</v>
       </c>
       <c r="AR23">
-        <v>30.28575896325516</v>
+        <v>30.28576999199843</v>
       </c>
       <c r="AS23">
-        <v>0.89876866316934</v>
+        <v>0.8987685952355365</v>
       </c>
       <c r="AT23">
-        <v>0.3084708376245854</v>
+        <v>0.3084703342384907</v>
       </c>
       <c r="AU23">
-        <v>30.540944329852</v>
+        <v>30.54095703458973</v>
       </c>
       <c r="AV23">
-        <v>0.9076164970125759</v>
+        <v>0.9076164382615417</v>
       </c>
       <c r="AW23">
-        <v>0.2967073881625283</v>
+        <v>0.2967068028997719</v>
       </c>
       <c r="AX23">
-        <v>31.17797726601507</v>
+        <v>31.17799332022113</v>
       </c>
       <c r="AY23">
-        <v>0.9213825246937632</v>
+        <v>0.9213824780548048</v>
       </c>
       <c r="AZ23">
-        <v>0.2671532111969103</v>
+        <v>0.2671524583229998</v>
       </c>
     </row>
     <row r="24">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>23.19619883619035</v>
+        <v>23.19619883157998</v>
       </c>
       <c r="E24">
         <v>36.7783252635105</v>
@@ -4253,139 +4253,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H24">
-        <v>23.23124185629132</v>
+        <v>23.23124185559629</v>
       </c>
       <c r="I24">
-        <v>0.614293658835778</v>
+        <v>0.6142936588429682</v>
       </c>
       <c r="J24">
-        <v>0.5934885223214688</v>
+        <v>0.5934885223458384</v>
       </c>
       <c r="K24">
-        <v>22.28736723990458</v>
+        <v>22.28736724256146</v>
       </c>
       <c r="L24">
-        <v>0.6579530093224538</v>
+        <v>0.6579530092539756</v>
       </c>
       <c r="M24">
-        <v>0.6258504372193241</v>
+        <v>0.6258504371301894</v>
       </c>
       <c r="N24">
-        <v>22.99235100395869</v>
+        <v>22.99235099575919</v>
       </c>
       <c r="O24">
-        <v>0.6786271129734901</v>
+        <v>0.6786271126509198</v>
       </c>
       <c r="P24">
-        <v>0.6017023910180581</v>
+        <v>0.6017023913037026</v>
       </c>
       <c r="Q24">
-        <v>22.42993328764484</v>
+        <v>22.42993329652992</v>
       </c>
       <c r="R24">
-        <v>0.6848071581086843</v>
+        <v>0.6848071578053214</v>
       </c>
       <c r="S24">
-        <v>0.6209745694250984</v>
+        <v>0.6209745691263406</v>
       </c>
       <c r="T24">
-        <v>22.52876063669881</v>
+        <v>22.52876063718686</v>
       </c>
       <c r="U24">
-        <v>0.6959954095143736</v>
+        <v>0.6959954086694966</v>
       </c>
       <c r="V24">
-        <v>0.6176128291677047</v>
+        <v>0.6176128291583023</v>
       </c>
       <c r="W24">
-        <v>22.39615813574379</v>
+        <v>22.39615817616497</v>
       </c>
       <c r="X24">
-        <v>0.7129194161128041</v>
+        <v>0.7129194143049866</v>
       </c>
       <c r="Y24">
-        <v>0.6220736538754028</v>
+        <v>0.6220736525080853</v>
       </c>
       <c r="Z24">
-        <v>22.78753377233469</v>
+        <v>22.78753380698353</v>
       </c>
       <c r="AA24">
-        <v>0.7221748618644271</v>
+        <v>0.7221748605540443</v>
       </c>
       <c r="AB24">
-        <v>0.6086577868072386</v>
+        <v>0.6086577856202452</v>
       </c>
       <c r="AC24">
-        <v>23.41548132489516</v>
+        <v>23.41548162132493</v>
       </c>
       <c r="AD24">
-        <v>0.7783328774450973</v>
+        <v>0.7783328814092324</v>
       </c>
       <c r="AE24">
-        <v>0.5867579546165964</v>
+        <v>0.5867579442047997</v>
       </c>
       <c r="AF24">
-        <v>23.20689482244038</v>
+        <v>23.20689473662167</v>
       </c>
       <c r="AG24">
-        <v>0.8127068975113949</v>
+        <v>0.8127069100834183</v>
       </c>
       <c r="AH24">
-        <v>0.5941106729750146</v>
+        <v>0.5941106759017265</v>
       </c>
       <c r="AI24">
-        <v>23.44891239329111</v>
+        <v>23.44891197518797</v>
       </c>
       <c r="AJ24">
-        <v>0.8383391899263134</v>
+        <v>0.838339207036938</v>
       </c>
       <c r="AK24">
-        <v>0.5854319288143235</v>
+        <v>0.5854319434291901</v>
       </c>
       <c r="AL24">
-        <v>24.08722839111477</v>
+        <v>24.08722734827679</v>
       </c>
       <c r="AM24">
-        <v>0.8636918438811174</v>
+        <v>0.8636918676412975</v>
       </c>
       <c r="AN24">
-        <v>0.5626108741672166</v>
+        <v>0.5626109118364971</v>
       </c>
       <c r="AO24">
-        <v>25.52479685392189</v>
+        <v>25.52479486062217</v>
       </c>
       <c r="AP24">
-        <v>0.8915462502703473</v>
+        <v>0.8915462736969275</v>
       </c>
       <c r="AQ24">
-        <v>0.5087939235329731</v>
+        <v>0.5087939999628466</v>
       </c>
       <c r="AR24">
-        <v>26.33302517587888</v>
+        <v>26.33302256452181</v>
       </c>
       <c r="AS24">
-        <v>0.9021152091386175</v>
+        <v>0.9021152315276106</v>
       </c>
       <c r="AT24">
-        <v>0.4771745486594925</v>
+        <v>0.4771746521076722</v>
       </c>
       <c r="AU24">
-        <v>27.86562119076055</v>
+        <v>27.86561730937759</v>
       </c>
       <c r="AV24">
-        <v>0.9152495330703383</v>
+        <v>0.9152495469616676</v>
       </c>
       <c r="AW24">
-        <v>0.4144713933144742</v>
+        <v>0.4144715563357911</v>
       </c>
       <c r="AX24">
-        <v>29.31889164988896</v>
+        <v>29.31888788456615</v>
       </c>
       <c r="AY24">
-        <v>0.928462629866889</v>
+        <v>0.9284626377002055</v>
       </c>
       <c r="AZ24">
-        <v>0.3518792851084365</v>
+        <v>0.3518794525368596</v>
       </c>
     </row>
     <row r="25">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>23.10395055933318</v>
+        <v>23.1039505528964</v>
       </c>
       <c r="E25">
         <v>36.7783252635105</v>
@@ -4417,139 +4417,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H25">
-        <v>23.12280978493632</v>
+        <v>23.12280978439215</v>
       </c>
       <c r="I25">
-        <v>0.6181119563074844</v>
+        <v>0.6181119563178272</v>
       </c>
       <c r="J25">
-        <v>0.5972785101075291</v>
+        <v>0.597278510126438</v>
       </c>
       <c r="K25">
-        <v>22.18400502747989</v>
+        <v>22.18400503001977</v>
       </c>
       <c r="L25">
-        <v>0.6612598818690909</v>
+        <v>0.6612598818016115</v>
       </c>
       <c r="M25">
-        <v>0.6293092126345329</v>
+        <v>0.6293092125497199</v>
       </c>
       <c r="N25">
-        <v>22.91536405465557</v>
+        <v>22.91536404766341</v>
       </c>
       <c r="O25">
-        <v>0.6845441378969188</v>
+        <v>0.6845441376268329</v>
       </c>
       <c r="P25">
-        <v>0.604351580133934</v>
+        <v>0.6043515803768907</v>
       </c>
       <c r="Q25">
-        <v>22.38397926674374</v>
+        <v>22.38397926856744</v>
       </c>
       <c r="R25">
-        <v>0.689906399203346</v>
+        <v>0.6899063989589901</v>
       </c>
       <c r="S25">
-        <v>0.6225059580134844</v>
+        <v>0.622505957955782</v>
       </c>
       <c r="T25">
-        <v>22.69673782817375</v>
+        <v>22.69673783550703</v>
       </c>
       <c r="U25">
-        <v>0.6985594922472322</v>
+        <v>0.6985594915420643</v>
       </c>
       <c r="V25">
-        <v>0.6118472301642182</v>
+        <v>0.611847229922898</v>
       </c>
       <c r="W25">
-        <v>23.30403114132656</v>
+        <v>23.3040311731857</v>
       </c>
       <c r="X25">
-        <v>0.7176185594169233</v>
+        <v>0.7176185583662016</v>
       </c>
       <c r="Y25">
-        <v>0.5906463178018146</v>
+        <v>0.5906463166702735</v>
       </c>
       <c r="Z25">
-        <v>24.10625017307588</v>
+        <v>24.10625023224456</v>
       </c>
       <c r="AA25">
-        <v>0.7251891423444052</v>
+        <v>0.7251891415379905</v>
       </c>
       <c r="AB25">
-        <v>0.5617118212276521</v>
+        <v>0.5617118190575814</v>
       </c>
       <c r="AC25">
-        <v>23.96371938544476</v>
+        <v>23.96371956562471</v>
       </c>
       <c r="AD25">
-        <v>0.7836483357880547</v>
+        <v>0.7836483413555221</v>
       </c>
       <c r="AE25">
-        <v>0.5666825876818999</v>
+        <v>0.5666825810560977</v>
       </c>
       <c r="AF25">
-        <v>23.83254692301788</v>
+        <v>23.83254683438264</v>
       </c>
       <c r="AG25">
-        <v>0.7971968629236641</v>
+        <v>0.7971968713790782</v>
       </c>
       <c r="AH25">
-        <v>0.5717386242421354</v>
+        <v>0.5717386273416948</v>
       </c>
       <c r="AI25">
-        <v>23.55238790718725</v>
+        <v>23.5523875034571</v>
       </c>
       <c r="AJ25">
-        <v>0.8286904476556984</v>
+        <v>0.8286904664392614</v>
       </c>
       <c r="AK25">
-        <v>0.5817932866474412</v>
+        <v>0.5817933008478881</v>
       </c>
       <c r="AL25">
-        <v>24.07554523007822</v>
+        <v>24.07554451283751</v>
       </c>
       <c r="AM25">
-        <v>0.8467960573097729</v>
+        <v>0.8467960777004282</v>
       </c>
       <c r="AN25">
-        <v>0.5629827626310441</v>
+        <v>0.5629827885284283</v>
       </c>
       <c r="AO25">
-        <v>24.86829506373262</v>
+        <v>24.86829295594557</v>
       </c>
       <c r="AP25">
-        <v>0.8754871832530274</v>
+        <v>0.8754872121112122</v>
       </c>
       <c r="AQ25">
-        <v>0.5337867039550176</v>
+        <v>0.5337867827745277</v>
       </c>
       <c r="AR25">
-        <v>26.02991059337381</v>
+        <v>26.02990771753436</v>
       </c>
       <c r="AS25">
-        <v>0.8975799559938856</v>
+        <v>0.8975799831435368</v>
       </c>
       <c r="AT25">
-        <v>0.4891000991504086</v>
+        <v>0.4891002117547597</v>
       </c>
       <c r="AU25">
-        <v>26.93872134565923</v>
+        <v>26.93871787466788</v>
       </c>
       <c r="AV25">
-        <v>0.9053066278574506</v>
+        <v>0.9053066518786463</v>
       </c>
       <c r="AW25">
-        <v>0.4527739929027468</v>
+        <v>0.4527741336750511</v>
       </c>
       <c r="AX25">
-        <v>28.5320596847988</v>
+        <v>28.53205513758067</v>
       </c>
       <c r="AY25">
-        <v>0.9201168820736503</v>
+        <v>0.9201168967531077</v>
       </c>
       <c r="AZ25">
-        <v>0.3861000846123437</v>
+        <v>0.3861002801593135</v>
       </c>
     </row>
     <row r="26">
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>22.34732335293532</v>
+        <v>22.34732335445556</v>
       </c>
       <c r="E26">
         <v>36.7783252635105</v>
@@ -4581,139 +4581,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H26">
-        <v>22.30135363148166</v>
+        <v>22.30135363288353</v>
       </c>
       <c r="I26">
-        <v>0.643643059036058</v>
+        <v>0.6436430589688942</v>
       </c>
       <c r="J26">
-        <v>0.6253818160041873</v>
+        <v>0.6253818159571509</v>
       </c>
       <c r="K26">
-        <v>22.18520777390454</v>
+        <v>22.18520777696715</v>
       </c>
       <c r="L26">
-        <v>0.6607478569503746</v>
+        <v>0.6607478568038931</v>
       </c>
       <c r="M26">
-        <v>0.6292621450337401</v>
+        <v>0.6292621449314934</v>
       </c>
       <c r="N26">
-        <v>22.84748787328994</v>
+        <v>22.84748787783845</v>
       </c>
       <c r="O26">
-        <v>0.6824024175880773</v>
+        <v>0.6824024171685525</v>
       </c>
       <c r="P26">
-        <v>0.6066493380222926</v>
+        <v>0.6066493378671561</v>
       </c>
       <c r="Q26">
-        <v>22.31813824171928</v>
+        <v>22.318138253444</v>
       </c>
       <c r="R26">
-        <v>0.694668234845035</v>
+        <v>0.6946682342648626</v>
       </c>
       <c r="S26">
-        <v>0.6247573198780786</v>
+        <v>0.6247573194844889</v>
       </c>
       <c r="T26">
-        <v>22.46450187150302</v>
+        <v>22.46450188786699</v>
       </c>
       <c r="U26">
-        <v>0.7038283457352166</v>
+        <v>0.7038283446462205</v>
       </c>
       <c r="V26">
-        <v>0.6198159138617596</v>
+        <v>0.6198159133077619</v>
       </c>
       <c r="W26">
-        <v>22.32223930888907</v>
+        <v>22.32223934776253</v>
       </c>
       <c r="X26">
-        <v>0.7157744390010624</v>
+        <v>0.7157744376775026</v>
       </c>
       <c r="Y26">
-        <v>0.624636916538303</v>
+        <v>0.6246369152301146</v>
       </c>
       <c r="Z26">
-        <v>22.8144850894979</v>
+        <v>22.81448514186631</v>
       </c>
       <c r="AA26">
-        <v>0.7374059753172015</v>
+        <v>0.7374059752211362</v>
       </c>
       <c r="AB26">
-        <v>0.6078651961448228</v>
+        <v>0.6078651943382766</v>
       </c>
       <c r="AC26">
-        <v>23.38720161484682</v>
+        <v>23.38720171240876</v>
       </c>
       <c r="AD26">
-        <v>0.7857617118363971</v>
+        <v>0.7857617180714711</v>
       </c>
       <c r="AE26">
-        <v>0.5877667929361369</v>
+        <v>0.587766789432583</v>
       </c>
       <c r="AF26">
-        <v>23.52703275077557</v>
+        <v>23.52703260041895</v>
       </c>
       <c r="AG26">
-        <v>0.8241709802787103</v>
+        <v>0.8241709980820863</v>
       </c>
       <c r="AH26">
-        <v>0.5827428790418099</v>
+        <v>0.58274288418013</v>
       </c>
       <c r="AI26">
-        <v>23.79993766257171</v>
+        <v>23.79993687930419</v>
       </c>
       <c r="AJ26">
-        <v>0.8492042828109301</v>
+        <v>0.8492043070156939</v>
       </c>
       <c r="AK26">
-        <v>0.57303436264969</v>
+        <v>0.5730343905513177</v>
       </c>
       <c r="AL26">
-        <v>24.87009963453895</v>
+        <v>24.87009790334045</v>
       </c>
       <c r="AM26">
-        <v>0.8771257292440526</v>
+        <v>0.8771257583357863</v>
       </c>
       <c r="AN26">
-        <v>0.5337226709850578</v>
+        <v>0.5337227357912389</v>
       </c>
       <c r="AO26">
-        <v>25.91282521422524</v>
+        <v>25.91282289637274</v>
       </c>
       <c r="AP26">
-        <v>0.8953398359376862</v>
+        <v>0.8953398626245881</v>
       </c>
       <c r="AQ26">
-        <v>0.493737014634747</v>
+        <v>0.4937371050196527</v>
       </c>
       <c r="AR26">
-        <v>27.38298967897982</v>
+        <v>27.3829867134353</v>
       </c>
       <c r="AS26">
-        <v>0.9094359937522729</v>
+        <v>0.9094360180637688</v>
       </c>
       <c r="AT26">
-        <v>0.4346803976452118</v>
+        <v>0.4346805198799068</v>
       </c>
       <c r="AU26">
-        <v>28.7755955531026</v>
+        <v>28.77559183526915</v>
       </c>
       <c r="AV26">
-        <v>0.9196243994109886</v>
+        <v>0.9196244175768796</v>
       </c>
       <c r="AW26">
-        <v>0.3755868763995021</v>
+        <v>0.3755870377148071</v>
       </c>
       <c r="AX26">
-        <v>31.06527910675134</v>
+        <v>31.06527516394339</v>
       </c>
       <c r="AY26">
-        <v>0.9333125664937219</v>
+        <v>0.9333125771748735</v>
       </c>
       <c r="AZ26">
-        <v>0.2722154700109565</v>
+        <v>0.2722156546974768</v>
       </c>
     </row>
     <row r="27">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>22.35215611247413</v>
+        <v>22.35215611646589</v>
       </c>
       <c r="E27">
         <v>36.7783252635105</v>
@@ -4745,139 +4745,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H27">
-        <v>22.30157349617412</v>
+        <v>22.30157349747331</v>
       </c>
       <c r="I27">
-        <v>0.6435691565508974</v>
+        <v>0.6435691564857373</v>
       </c>
       <c r="J27">
-        <v>0.6253737102441186</v>
+        <v>0.6253737102006008</v>
       </c>
       <c r="K27">
-        <v>22.20382682607948</v>
+        <v>22.20382682928396</v>
       </c>
       <c r="L27">
-        <v>0.6605499431309139</v>
+        <v>0.66054994298548</v>
       </c>
       <c r="M27">
-        <v>0.6286354264906843</v>
+        <v>0.6286354263837762</v>
       </c>
       <c r="N27">
-        <v>22.82371420737601</v>
+        <v>22.82371421355119</v>
       </c>
       <c r="O27">
-        <v>0.6812871811312768</v>
+        <v>0.6812871806842075</v>
       </c>
       <c r="P27">
-        <v>0.6073370634487254</v>
+        <v>0.6073370632417774</v>
       </c>
       <c r="Q27">
-        <v>22.32558878389974</v>
+        <v>22.32558879760621</v>
       </c>
       <c r="R27">
-        <v>0.6925218906424037</v>
+        <v>0.6925218899901124</v>
       </c>
       <c r="S27">
-        <v>0.6243918463438123</v>
+        <v>0.6243918458889819</v>
       </c>
       <c r="T27">
-        <v>22.39579638144877</v>
+        <v>22.3957964039739</v>
       </c>
       <c r="U27">
-        <v>0.7000037964908183</v>
+        <v>0.7000037952319267</v>
       </c>
       <c r="V27">
-        <v>0.6220316335922121</v>
+        <v>0.6220316328372508</v>
       </c>
       <c r="W27">
-        <v>22.28071497695999</v>
+        <v>22.28071503179886</v>
       </c>
       <c r="X27">
-        <v>0.7074864729925403</v>
+        <v>0.7074864709844555</v>
       </c>
       <c r="Y27">
-        <v>0.6259372920788489</v>
+        <v>0.6259372902415432</v>
       </c>
       <c r="Z27">
-        <v>22.44632122782164</v>
+        <v>22.4463213090462</v>
       </c>
       <c r="AA27">
-        <v>0.7167442989824901</v>
+        <v>0.7167442956178165</v>
       </c>
       <c r="AB27">
-        <v>0.6203358226392128</v>
+        <v>0.6203358198963504</v>
       </c>
       <c r="AC27">
-        <v>22.64181031463891</v>
+        <v>22.64181048248318</v>
       </c>
       <c r="AD27">
-        <v>0.7392307037361072</v>
+        <v>0.7392306961070378</v>
       </c>
       <c r="AE27">
-        <v>0.613606105003614</v>
+        <v>0.613606099273394</v>
       </c>
       <c r="AF27">
-        <v>22.41260910898866</v>
+        <v>22.41260947776421</v>
       </c>
       <c r="AG27">
-        <v>0.7585286140299142</v>
+        <v>0.758528607314942</v>
       </c>
       <c r="AH27">
-        <v>0.6214616222961766</v>
+        <v>0.6214616098099485</v>
       </c>
       <c r="AI27">
-        <v>22.19892778959036</v>
+        <v>22.19892798256673</v>
       </c>
       <c r="AJ27">
-        <v>0.7734864733688631</v>
+        <v>0.7734864690698751</v>
       </c>
       <c r="AK27">
-        <v>0.6286702279020031</v>
+        <v>0.6286702214437259</v>
       </c>
       <c r="AL27">
-        <v>22.32572332286126</v>
+        <v>22.32572339827406</v>
       </c>
       <c r="AM27">
-        <v>0.7816578468911607</v>
+        <v>0.7816578444698501</v>
       </c>
       <c r="AN27">
-        <v>0.6244246597706591</v>
+        <v>0.6244246572365714</v>
       </c>
       <c r="AO27">
-        <v>22.79559559298269</v>
+        <v>22.79559579682998</v>
       </c>
       <c r="AP27">
-        <v>0.7967872486406814</v>
+        <v>0.7967872524569435</v>
       </c>
       <c r="AQ27">
-        <v>0.6084071825857746</v>
+        <v>0.6084071755094116</v>
       </c>
       <c r="AR27">
-        <v>23.70103606515718</v>
+        <v>23.70103592824402</v>
       </c>
       <c r="AS27">
-        <v>0.8089131261226953</v>
+        <v>0.8089131361839709</v>
       </c>
       <c r="AT27">
-        <v>0.5766175356602479</v>
+        <v>0.5766175406203091</v>
       </c>
       <c r="AU27">
-        <v>23.90856473092141</v>
+        <v>23.90856403604174</v>
       </c>
       <c r="AV27">
-        <v>0.8116973613255045</v>
+        <v>0.8116973679106421</v>
       </c>
       <c r="AW27">
-        <v>0.5692240128230974</v>
+        <v>0.569224037799048</v>
       </c>
       <c r="AX27">
-        <v>25.92836574983927</v>
+        <v>25.92836524854777</v>
       </c>
       <c r="AY27">
-        <v>0.8267956429844036</v>
+        <v>0.8267956478217933</v>
       </c>
       <c r="AZ27">
-        <v>0.4931352187780187</v>
+        <v>0.4931352379319821</v>
       </c>
     </row>
     <row r="28">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>23.07811272382682</v>
+        <v>23.07811272245921</v>
       </c>
       <c r="E28">
         <v>36.7783252635105</v>
@@ -4909,139 +4909,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H28">
-        <v>23.10292601458669</v>
+        <v>23.10292601395267</v>
       </c>
       <c r="I28">
-        <v>0.6179891865896963</v>
+        <v>0.6179891866015162</v>
       </c>
       <c r="J28">
-        <v>0.5979660677624783</v>
+        <v>0.5979660677845973</v>
       </c>
       <c r="K28">
-        <v>22.1687958457596</v>
+        <v>22.16879584831619</v>
       </c>
       <c r="L28">
-        <v>0.6611152238378326</v>
+        <v>0.6611152237713082</v>
       </c>
       <c r="M28">
-        <v>0.6298139121999458</v>
+        <v>0.6298139121145794</v>
       </c>
       <c r="N28">
-        <v>22.9393670277166</v>
+        <v>22.93936702091128</v>
       </c>
       <c r="O28">
-        <v>0.6836626028756381</v>
+        <v>0.6836626025598704</v>
       </c>
       <c r="P28">
-        <v>0.6035210142959742</v>
+        <v>0.6035210145315298</v>
       </c>
       <c r="Q28">
-        <v>22.38905495748809</v>
+        <v>22.3890549641112</v>
       </c>
       <c r="R28">
-        <v>0.6887345541958698</v>
+        <v>0.6887345538872895</v>
       </c>
       <c r="S28">
-        <v>0.6223056877541866</v>
+        <v>0.6223056875337432</v>
       </c>
       <c r="T28">
-        <v>22.72166480884211</v>
+        <v>22.72166481164995</v>
       </c>
       <c r="U28">
-        <v>0.6960480111656706</v>
+        <v>0.6960480103266826</v>
       </c>
       <c r="V28">
-        <v>0.6109722231908266</v>
+        <v>0.6109722230919871</v>
       </c>
       <c r="W28">
-        <v>23.20396690573278</v>
+        <v>23.20396691491234</v>
       </c>
       <c r="X28">
-        <v>0.7062118776724273</v>
+        <v>0.7062118753990116</v>
       </c>
       <c r="Y28">
-        <v>0.5942075462530816</v>
+        <v>0.5942075459372904</v>
       </c>
       <c r="Z28">
-        <v>23.76232632467745</v>
+        <v>23.76232637800928</v>
       </c>
       <c r="AA28">
-        <v>0.709713034817502</v>
+        <v>0.7097130320335933</v>
       </c>
       <c r="AB28">
-        <v>0.574245173534681</v>
+        <v>0.5742451716673724</v>
       </c>
       <c r="AC28">
-        <v>23.3289563897113</v>
+        <v>23.32895667976526</v>
       </c>
       <c r="AD28">
-        <v>0.7363622836172203</v>
+        <v>0.7363622777038785</v>
       </c>
       <c r="AE28">
-        <v>0.5893812613166354</v>
+        <v>0.589381251160737</v>
       </c>
       <c r="AF28">
-        <v>23.27091926680697</v>
+        <v>23.27091946988236</v>
       </c>
       <c r="AG28">
-        <v>0.7427841844724516</v>
+        <v>0.7427841779928873</v>
       </c>
       <c r="AH28">
-        <v>0.5917405174755618</v>
+        <v>0.5917405102892508</v>
       </c>
       <c r="AI28">
-        <v>22.78431922951665</v>
+        <v>22.78431936460346</v>
       </c>
       <c r="AJ28">
-        <v>0.757822860353172</v>
+        <v>0.7578228559464546</v>
       </c>
       <c r="AK28">
-        <v>0.6087455655997113</v>
+        <v>0.6087455609278054</v>
       </c>
       <c r="AL28">
-        <v>22.92552880978287</v>
+        <v>22.92552902164582</v>
       </c>
       <c r="AM28">
-        <v>0.7662494642028771</v>
+        <v>0.7662494584347559</v>
       </c>
       <c r="AN28">
-        <v>0.6038632603998236</v>
+        <v>0.6038632530708261</v>
       </c>
       <c r="AO28">
-        <v>23.32494634071239</v>
+        <v>23.32494639919512</v>
       </c>
       <c r="AP28">
-        <v>0.7767167953365317</v>
+        <v>0.77671679294007</v>
       </c>
       <c r="AQ28">
-        <v>0.5899063124772749</v>
+        <v>0.5899063104473617</v>
       </c>
       <c r="AR28">
-        <v>24.18126527045981</v>
+        <v>24.18126519442607</v>
       </c>
       <c r="AS28">
-        <v>0.7866994273157979</v>
+        <v>0.7866994311490485</v>
       </c>
       <c r="AT28">
-        <v>0.5591888322778202</v>
+        <v>0.5591888347981032</v>
       </c>
       <c r="AU28">
-        <v>24.37153268814858</v>
+        <v>24.37153260936358</v>
       </c>
       <c r="AV28">
-        <v>0.7921250303626941</v>
+        <v>0.7921250372877984</v>
       </c>
       <c r="AW28">
-        <v>0.552172389567211</v>
+        <v>0.5521723924084179</v>
       </c>
       <c r="AX28">
-        <v>25.40301731063927</v>
+        <v>25.40301612342529</v>
       </c>
       <c r="AY28">
-        <v>0.8076328324146124</v>
+        <v>0.8076328427359666</v>
       </c>
       <c r="AZ28">
-        <v>0.5135090394615178</v>
+        <v>0.5135090850368411</v>
       </c>
     </row>
     <row r="29">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>23.12422564763277</v>
+        <v>23.12422564661435</v>
       </c>
       <c r="E29">
         <v>36.7783252635105</v>
@@ -5073,139 +5073,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H29">
-        <v>23.13766284948791</v>
+        <v>23.13766284861809</v>
       </c>
       <c r="I29">
-        <v>0.6178848867318328</v>
+        <v>0.6178848867457871</v>
       </c>
       <c r="J29">
-        <v>0.5967554722830209</v>
+        <v>0.5967554723133834</v>
       </c>
       <c r="K29">
-        <v>22.18571822545039</v>
+        <v>22.1857182278442</v>
       </c>
       <c r="L29">
-        <v>0.6610786094462839</v>
+        <v>0.6610786093847789</v>
       </c>
       <c r="M29">
-        <v>0.6292448430559687</v>
+        <v>0.6292448429760226</v>
       </c>
       <c r="N29">
-        <v>22.93685022581949</v>
+        <v>22.93685021739186</v>
       </c>
       <c r="O29">
-        <v>0.6834860611700893</v>
+        <v>0.6834860608602404</v>
       </c>
       <c r="P29">
-        <v>0.6035937861420456</v>
+        <v>0.6035937864364849</v>
       </c>
       <c r="Q29">
-        <v>22.43330731262206</v>
+        <v>22.43330731549799</v>
       </c>
       <c r="R29">
-        <v>0.6885893400912492</v>
+        <v>0.6885893397904805</v>
       </c>
       <c r="S29">
-        <v>0.6208259147787204</v>
+        <v>0.6208259146835858</v>
       </c>
       <c r="T29">
-        <v>22.72690337820855</v>
+        <v>22.72690337279736</v>
       </c>
       <c r="U29">
-        <v>0.695833622446561</v>
+        <v>0.695833621633885</v>
       </c>
       <c r="V29">
-        <v>0.6108141879716894</v>
+        <v>0.6108141881731151</v>
       </c>
       <c r="W29">
-        <v>23.18210005271328</v>
+        <v>23.18210006849861</v>
       </c>
       <c r="X29">
-        <v>0.7055925712205507</v>
+        <v>0.7055925690327332</v>
       </c>
       <c r="Y29">
-        <v>0.5949856691770429</v>
+        <v>0.5949856686392656</v>
       </c>
       <c r="Z29">
-        <v>23.70975639300849</v>
+        <v>23.70975640256009</v>
       </c>
       <c r="AA29">
-        <v>0.7089411430829455</v>
+        <v>0.7089411404110958</v>
       </c>
       <c r="AB29">
-        <v>0.5761287914708833</v>
+        <v>0.5761287911484779</v>
       </c>
       <c r="AC29">
-        <v>23.3897865198733</v>
+        <v>23.38978675089357</v>
       </c>
       <c r="AD29">
-        <v>0.7349364769389461</v>
+        <v>0.7349364709209951</v>
       </c>
       <c r="AE29">
-        <v>0.5871704458927809</v>
+        <v>0.5871704377825026</v>
       </c>
       <c r="AF29">
-        <v>23.36429361901686</v>
+        <v>23.36429378462776</v>
       </c>
       <c r="AG29">
-        <v>0.7415074642921033</v>
+        <v>0.7415074575521712</v>
       </c>
       <c r="AH29">
-        <v>0.5883575966688835</v>
+        <v>0.588357590796874</v>
       </c>
       <c r="AI29">
-        <v>22.87334430703193</v>
+        <v>22.87334447097446</v>
       </c>
       <c r="AJ29">
-        <v>0.7568542498303981</v>
+        <v>0.7568542448442196</v>
       </c>
       <c r="AK29">
-        <v>0.6055704404911495</v>
+        <v>0.6055704347861968</v>
       </c>
       <c r="AL29">
-        <v>22.9376666297534</v>
+        <v>22.93766678346467</v>
       </c>
       <c r="AM29">
-        <v>0.7649157545725253</v>
+        <v>0.7649157480563085</v>
       </c>
       <c r="AN29">
-        <v>0.6034246289846346</v>
+        <v>0.6034246237154982</v>
       </c>
       <c r="AO29">
-        <v>23.17392487504033</v>
+        <v>23.17392480268692</v>
       </c>
       <c r="AP29">
-        <v>0.7749173248090728</v>
+        <v>0.7749173208381277</v>
       </c>
       <c r="AQ29">
-        <v>0.5951937542239877</v>
+        <v>0.5951937568430841</v>
       </c>
       <c r="AR29">
-        <v>23.94148146813928</v>
+        <v>23.94148138850845</v>
       </c>
       <c r="AS29">
-        <v>0.7835198925039324</v>
+        <v>0.7835198932301287</v>
       </c>
       <c r="AT29">
-        <v>0.5679469680102267</v>
+        <v>0.5679469707445851</v>
       </c>
       <c r="AU29">
-        <v>24.00216824627586</v>
+        <v>24.00216807784874</v>
       </c>
       <c r="AV29">
-        <v>0.7882716410613257</v>
+        <v>0.788271644260203</v>
       </c>
       <c r="AW29">
-        <v>0.5657044679676012</v>
+        <v>0.565704473986841</v>
       </c>
       <c r="AX29">
-        <v>25.03222995658892</v>
+        <v>25.03222884720771</v>
       </c>
       <c r="AY29">
-        <v>0.8009491368097972</v>
+        <v>0.8009491441325753</v>
       </c>
       <c r="AZ29">
-        <v>0.5276548358348159</v>
+        <v>0.5276548775699419</v>
       </c>
     </row>
     <row r="30">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>23.0949280630902</v>
+        <v>23.09492805873664</v>
       </c>
       <c r="E30">
         <v>36.7783252635105</v>
@@ -5237,139 +5237,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H30">
-        <v>23.12499079161933</v>
+        <v>23.12499079092073</v>
       </c>
       <c r="I30">
-        <v>0.6178146309984232</v>
+        <v>0.6178146310136537</v>
       </c>
       <c r="J30">
-        <v>0.597190857656735</v>
+        <v>0.597190857681116</v>
       </c>
       <c r="K30">
-        <v>22.17598302064018</v>
+        <v>22.17598302318584</v>
       </c>
       <c r="L30">
-        <v>0.6610574173285608</v>
+        <v>0.6610574172698331</v>
       </c>
       <c r="M30">
-        <v>0.6295655152078538</v>
+        <v>0.6295655151228073</v>
       </c>
       <c r="N30">
-        <v>22.8763139492545</v>
+        <v>22.87631394405639</v>
       </c>
       <c r="O30">
-        <v>0.6833779493554066</v>
+        <v>0.6833779490519853</v>
       </c>
       <c r="P30">
-        <v>0.6056640477958737</v>
+        <v>0.6056640479764894</v>
       </c>
       <c r="Q30">
-        <v>22.29354175663261</v>
+        <v>22.29354176153176</v>
       </c>
       <c r="R30">
-        <v>0.6885050392337422</v>
+        <v>0.6885050389420853</v>
       </c>
       <c r="S30">
-        <v>0.6255503326917495</v>
+        <v>0.6255503325302429</v>
       </c>
       <c r="T30">
-        <v>22.58634690526145</v>
+        <v>22.58634690599078</v>
       </c>
       <c r="U30">
-        <v>0.6957169276824462</v>
+        <v>0.6957169268955381</v>
       </c>
       <c r="V30">
-        <v>0.6156284140288003</v>
+        <v>0.6156284140064616</v>
       </c>
       <c r="W30">
-        <v>23.00029828461168</v>
+        <v>23.00029830257077</v>
       </c>
       <c r="X30">
-        <v>0.7052657659617585</v>
+        <v>0.7052657638497026</v>
       </c>
       <c r="Y30">
-        <v>0.6013513047779631</v>
+        <v>0.6013513041593674</v>
       </c>
       <c r="Z30">
-        <v>23.46013340826243</v>
+        <v>23.4601334511463</v>
       </c>
       <c r="AA30">
-        <v>0.708541238120582</v>
+        <v>0.7085412355449253</v>
       </c>
       <c r="AB30">
-        <v>0.5852136116242659</v>
+        <v>0.5852136101243813</v>
       </c>
       <c r="AC30">
-        <v>23.02558710729859</v>
+        <v>23.02558741791991</v>
       </c>
       <c r="AD30">
-        <v>0.7341999190195752</v>
+        <v>0.7341999130270795</v>
       </c>
       <c r="AE30">
-        <v>0.6005242296045683</v>
+        <v>0.600524218815619</v>
       </c>
       <c r="AF30">
-        <v>22.97821584141129</v>
+        <v>22.97821599287794</v>
       </c>
       <c r="AG30">
-        <v>0.7408773663386967</v>
+        <v>0.7408773595551421</v>
       </c>
       <c r="AH30">
-        <v>0.6021066238035712</v>
+        <v>0.6021066186162359</v>
       </c>
       <c r="AI30">
-        <v>22.64324094785929</v>
+        <v>22.64324112622071</v>
       </c>
       <c r="AJ30">
-        <v>0.7565936723959916</v>
+        <v>0.7565936672841623</v>
       </c>
       <c r="AK30">
-        <v>0.6136754060745586</v>
+        <v>0.6136753999739003</v>
       </c>
       <c r="AL30">
-        <v>22.65983730378849</v>
+        <v>22.65983766850989</v>
       </c>
       <c r="AM30">
-        <v>0.7646208076536372</v>
+        <v>0.7646208010122885</v>
       </c>
       <c r="AN30">
-        <v>0.6130932689383987</v>
+        <v>0.6130932564595177</v>
       </c>
       <c r="AO30">
-        <v>22.81797456001067</v>
+        <v>22.81797462314605</v>
       </c>
       <c r="AP30">
-        <v>0.7744324548962728</v>
+        <v>0.774432450510616</v>
       </c>
       <c r="AQ30">
-        <v>0.607695152902066</v>
+        <v>0.607695150706</v>
       </c>
       <c r="AR30">
-        <v>23.52283342498921</v>
+        <v>23.52283359868993</v>
       </c>
       <c r="AS30">
-        <v>0.7826804810354266</v>
+        <v>0.7826804807662116</v>
       </c>
       <c r="AT30">
-        <v>0.5830104642593321</v>
+        <v>0.5830104580296128</v>
       </c>
       <c r="AU30">
-        <v>23.62076552206172</v>
+        <v>23.62076665106142</v>
       </c>
       <c r="AV30">
-        <v>0.7873159526512181</v>
+        <v>0.7873159546265008</v>
       </c>
       <c r="AW30">
-        <v>0.5795103693884839</v>
+        <v>0.5795103288736759</v>
       </c>
       <c r="AX30">
-        <v>24.54161534551639</v>
+        <v>24.54161449911298</v>
       </c>
       <c r="AY30">
-        <v>0.7980438149125544</v>
+        <v>0.7980438206644715</v>
       </c>
       <c r="AZ30">
-        <v>0.5459966392545235</v>
+        <v>0.5459966703065601</v>
       </c>
     </row>
     <row r="31">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>23.0635181857057</v>
+        <v>23.06351818495921</v>
       </c>
       <c r="E31">
         <v>36.7783252635105</v>
@@ -5401,139 +5401,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H31">
-        <v>23.09237591335621</v>
+        <v>23.09237591266093</v>
       </c>
       <c r="I31">
-        <v>0.6176325889485793</v>
+        <v>0.6176325889673548</v>
       </c>
       <c r="J31">
-        <v>0.5983343541481473</v>
+        <v>0.5983343541723485</v>
       </c>
       <c r="K31">
-        <v>22.13641969773129</v>
+        <v>22.13641970011043</v>
       </c>
       <c r="L31">
-        <v>0.6609981323144348</v>
+        <v>0.6609981322631662</v>
       </c>
       <c r="M31">
-        <v>0.6309010242390727</v>
+        <v>0.6309010241597218</v>
       </c>
       <c r="N31">
-        <v>22.84213397951406</v>
+        <v>22.8421339719299</v>
       </c>
       <c r="O31">
-        <v>0.6831351137334064</v>
+        <v>0.6831351134499069</v>
       </c>
       <c r="P31">
-        <v>0.6068894101078016</v>
+        <v>0.6068894103704627</v>
       </c>
       <c r="Q31">
-        <v>22.35797457435601</v>
+        <v>22.35797457915665</v>
       </c>
       <c r="R31">
-        <v>0.6883233221319154</v>
+        <v>0.6883233218668205</v>
       </c>
       <c r="S31">
-        <v>0.6233681569294257</v>
+        <v>0.62336815676585</v>
       </c>
       <c r="T31">
-        <v>22.61439931449411</v>
+        <v>22.61439931833882</v>
       </c>
       <c r="U31">
-        <v>0.6954741708434762</v>
+        <v>0.6954741701198959</v>
       </c>
       <c r="V31">
-        <v>0.6146517710490463</v>
+        <v>0.6146517709168022</v>
       </c>
       <c r="W31">
-        <v>23.05998065341845</v>
+        <v>23.05998064839581</v>
       </c>
       <c r="X31">
-        <v>0.7044678160203042</v>
+        <v>0.704467814096515</v>
       </c>
       <c r="Y31">
-        <v>0.5991730024421331</v>
+        <v>0.5991730026249036</v>
       </c>
       <c r="Z31">
-        <v>23.47874864140958</v>
+        <v>23.47874870204986</v>
       </c>
       <c r="AA31">
-        <v>0.707510463727157</v>
+        <v>0.7075104613992718</v>
       </c>
       <c r="AB31">
-        <v>0.5843160841940586</v>
+        <v>0.5843160820783305</v>
       </c>
       <c r="AC31">
-        <v>23.20341358959199</v>
+        <v>23.20341372600149</v>
       </c>
       <c r="AD31">
-        <v>0.7315454497338227</v>
+        <v>0.7315454439490272</v>
       </c>
       <c r="AE31">
-        <v>0.5938111638149998</v>
+        <v>0.593811158970998</v>
       </c>
       <c r="AF31">
-        <v>23.25443432846832</v>
+        <v>23.25443432210147</v>
       </c>
       <c r="AG31">
-        <v>0.7382764610092023</v>
+        <v>0.7382764542401323</v>
       </c>
       <c r="AH31">
-        <v>0.5921686726585854</v>
+        <v>0.5921686727550822</v>
       </c>
       <c r="AI31">
-        <v>22.7124263137454</v>
+        <v>22.7124265425091</v>
       </c>
       <c r="AJ31">
-        <v>0.7541596523540838</v>
+        <v>0.7541596466828143</v>
       </c>
       <c r="AK31">
-        <v>0.6111347055481133</v>
+        <v>0.6111346976562323</v>
       </c>
       <c r="AL31">
-        <v>22.74481465153961</v>
+        <v>22.74481496315064</v>
       </c>
       <c r="AM31">
-        <v>0.7622905377148462</v>
+        <v>0.7622905305611709</v>
       </c>
       <c r="AN31">
-        <v>0.6100952273588983</v>
+        <v>0.610095216696096</v>
       </c>
       <c r="AO31">
-        <v>22.86179272575597</v>
+        <v>22.86179289255122</v>
       </c>
       <c r="AP31">
-        <v>0.7709882594654982</v>
+        <v>0.7709882537035537</v>
       </c>
       <c r="AQ31">
-        <v>0.6060348789017382</v>
+        <v>0.6060348731752</v>
       </c>
       <c r="AR31">
-        <v>23.45975811741462</v>
+        <v>23.45975819491585</v>
       </c>
       <c r="AS31">
-        <v>0.7778701055902639</v>
+        <v>0.7778701026809433</v>
       </c>
       <c r="AT31">
-        <v>0.5850981910248567</v>
+        <v>0.5850981882230022</v>
       </c>
       <c r="AU31">
-        <v>23.62884271489524</v>
+        <v>23.62884271753154</v>
       </c>
       <c r="AV31">
-        <v>0.7818142748581243</v>
+        <v>0.7818142738135706</v>
       </c>
       <c r="AW31">
-        <v>0.5791066047757251</v>
+        <v>0.5791066047116468</v>
       </c>
       <c r="AX31">
-        <v>24.14774686402687</v>
+        <v>24.14774593042727</v>
       </c>
       <c r="AY31">
-        <v>0.7889477468538194</v>
+        <v>0.7889477493910303</v>
       </c>
       <c r="AZ31">
-        <v>0.5603870836899643</v>
+        <v>0.5603871179230554</v>
       </c>
     </row>
     <row r="32">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>23.06855621589696</v>
+        <v>23.06855621415826</v>
       </c>
       <c r="E32">
         <v>36.7783252635105</v>
@@ -5565,139 +5565,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H32">
-        <v>23.09873993538283</v>
+        <v>23.09873993500754</v>
       </c>
       <c r="I32">
-        <v>0.6180798884888821</v>
+        <v>0.6180798884993984</v>
       </c>
       <c r="J32">
-        <v>0.5981123547563237</v>
+        <v>0.598112354769437</v>
       </c>
       <c r="K32">
-        <v>22.19014988899618</v>
+        <v>22.19014989208246</v>
       </c>
       <c r="L32">
-        <v>0.661174442282767</v>
+        <v>0.661174442213132</v>
       </c>
       <c r="M32">
-        <v>0.6291055290759393</v>
+        <v>0.6291055289728128</v>
       </c>
       <c r="N32">
-        <v>23.01337275266835</v>
+        <v>23.01337274598014</v>
       </c>
       <c r="O32">
-        <v>0.6838510955361977</v>
+        <v>0.6838510952217719</v>
       </c>
       <c r="P32">
-        <v>0.6009622113891995</v>
+        <v>0.6009622116216372</v>
       </c>
       <c r="Q32">
-        <v>22.42049522585699</v>
+        <v>22.42049523429369</v>
       </c>
       <c r="R32">
-        <v>0.6889228491124338</v>
+        <v>0.688922848802207</v>
       </c>
       <c r="S32">
-        <v>0.6212864783545687</v>
+        <v>0.6212864780706899</v>
       </c>
       <c r="T32">
-        <v>22.74127926170976</v>
+        <v>22.74127925383404</v>
       </c>
       <c r="U32">
-        <v>0.6964035925163539</v>
+        <v>0.6964035916512616</v>
       </c>
       <c r="V32">
-        <v>0.6103563291087259</v>
+        <v>0.610356329378467</v>
       </c>
       <c r="W32">
-        <v>23.30233699698508</v>
+        <v>23.30233707398148</v>
       </c>
       <c r="X32">
-        <v>0.7077767500089767</v>
+        <v>0.7077767476584839</v>
       </c>
       <c r="Y32">
-        <v>0.5907734513579633</v>
+        <v>0.5907734487124543</v>
       </c>
       <c r="Z32">
-        <v>23.80630375014221</v>
+        <v>23.80630383077156</v>
       </c>
       <c r="AA32">
-        <v>0.7118187606643449</v>
+        <v>0.7118187578119486</v>
       </c>
       <c r="AB32">
-        <v>0.5727002799236942</v>
+        <v>0.5727002771021867</v>
       </c>
       <c r="AC32">
-        <v>23.58064092585175</v>
+        <v>23.58064122834209</v>
       </c>
       <c r="AD32">
-        <v>0.7431808669189185</v>
+        <v>0.7431808619736284</v>
       </c>
       <c r="AE32">
-        <v>0.5804865279366238</v>
+        <v>0.5804865172042875</v>
       </c>
       <c r="AF32">
-        <v>23.4235504592998</v>
+        <v>23.42355067202594</v>
       </c>
       <c r="AG32">
-        <v>0.7503701524050619</v>
+        <v>0.7503701474690325</v>
       </c>
       <c r="AH32">
-        <v>0.5863231234250736</v>
+        <v>0.5863231158906607</v>
       </c>
       <c r="AI32">
-        <v>22.85693124874779</v>
+        <v>22.85693136539301</v>
       </c>
       <c r="AJ32">
-        <v>0.7673365562319682</v>
+        <v>0.7673365552339745</v>
       </c>
       <c r="AK32">
-        <v>0.6061586030865854</v>
+        <v>0.6061585990148001</v>
       </c>
       <c r="AL32">
-        <v>22.98295032666232</v>
+        <v>22.98295053594836</v>
       </c>
       <c r="AM32">
-        <v>0.7781592678344087</v>
+        <v>0.7781592663634087</v>
       </c>
       <c r="AN32">
-        <v>0.6018881855054367</v>
+        <v>0.6018881782907843</v>
       </c>
       <c r="AO32">
-        <v>23.49517116439174</v>
+        <v>23.49517091215751</v>
       </c>
       <c r="AP32">
-        <v>0.7945010048580714</v>
+        <v>0.7945010106176846</v>
       </c>
       <c r="AQ32">
-        <v>0.5838908835157637</v>
+        <v>0.5838908926505972</v>
       </c>
       <c r="AR32">
-        <v>24.30234390766749</v>
+        <v>24.30234334197547</v>
       </c>
       <c r="AS32">
-        <v>0.8112410023459448</v>
+        <v>0.811241017376892</v>
       </c>
       <c r="AT32">
-        <v>0.5547389273358089</v>
+        <v>0.5547389480910545</v>
       </c>
       <c r="AU32">
-        <v>24.21938255778832</v>
+        <v>24.21938150250902</v>
       </c>
       <c r="AV32">
-        <v>0.817506386068773</v>
+        <v>0.8175064035131481</v>
       </c>
       <c r="AW32">
-        <v>0.5577710207640508</v>
+        <v>0.5577710592313925</v>
       </c>
       <c r="AX32">
-        <v>24.98349557619063</v>
+        <v>24.98349396362487</v>
       </c>
       <c r="AY32">
-        <v>0.8312356677261645</v>
+        <v>0.8312356895993132</v>
       </c>
       <c r="AZ32">
-        <v>0.5294600159933327</v>
+        <v>0.5294600769274689</v>
       </c>
     </row>
     <row r="33">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>23.01204755393896</v>
+        <v>23.01204755332362</v>
       </c>
       <c r="E33">
         <v>36.7783252635105</v>
@@ -5729,139 +5729,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H33">
-        <v>23.09382497248628</v>
+        <v>23.09382497194248</v>
       </c>
       <c r="I33">
-        <v>0.6180592335406229</v>
+        <v>0.6180592335517461</v>
       </c>
       <c r="J33">
-        <v>0.5982819530010279</v>
+        <v>0.5982819530199538</v>
       </c>
       <c r="K33">
-        <v>22.16579144199038</v>
+        <v>22.16579144444207</v>
       </c>
       <c r="L33">
-        <v>0.66116444829425</v>
+        <v>0.6611644482259755</v>
       </c>
       <c r="M33">
-        <v>0.6299211515938394</v>
+        <v>0.629921151511969</v>
       </c>
       <c r="N33">
-        <v>22.86854122785586</v>
+        <v>22.86854122111279</v>
       </c>
       <c r="O33">
-        <v>0.6838012519195112</v>
+        <v>0.6838012516077212</v>
       </c>
       <c r="P33">
-        <v>0.6059829623311739</v>
+        <v>0.6059829625650824</v>
       </c>
       <c r="Q33">
-        <v>22.36528517677571</v>
+        <v>22.36528518503347</v>
       </c>
       <c r="R33">
-        <v>0.6888709840074104</v>
+        <v>0.6888709837025475</v>
       </c>
       <c r="S33">
-        <v>0.62316706090326</v>
+        <v>0.6231670606230256</v>
       </c>
       <c r="T33">
-        <v>22.6697582314455</v>
+        <v>22.66975822584154</v>
       </c>
       <c r="U33">
-        <v>0.6963204791949642</v>
+        <v>0.6963204783503028</v>
       </c>
       <c r="V33">
-        <v>0.6128184524604449</v>
+        <v>0.6128184526644753</v>
       </c>
       <c r="W33">
-        <v>23.22410828784336</v>
+        <v>23.2241082361581</v>
       </c>
       <c r="X33">
-        <v>0.7074913603255171</v>
+        <v>0.7074913580445941</v>
       </c>
       <c r="Y33">
-        <v>0.5935250159643283</v>
+        <v>0.5935250178907702</v>
       </c>
       <c r="Z33">
-        <v>23.79670428185826</v>
+        <v>23.79670435430469</v>
       </c>
       <c r="AA33">
-        <v>0.7114491513952791</v>
+        <v>0.7114491486282617</v>
       </c>
       <c r="AB33">
-        <v>0.5730318453597777</v>
+        <v>0.5730318427407941</v>
       </c>
       <c r="AC33">
-        <v>23.44443042050235</v>
+        <v>23.44443070704161</v>
       </c>
       <c r="AD33">
-        <v>0.7423612951787404</v>
+        <v>0.7423612902436345</v>
       </c>
       <c r="AE33">
-        <v>0.5851666795119749</v>
+        <v>0.5851666694167904</v>
       </c>
       <c r="AF33">
-        <v>23.24492700441487</v>
+        <v>23.24492702911738</v>
       </c>
       <c r="AG33">
-        <v>0.7495453886269636</v>
+        <v>0.7495453836318582</v>
       </c>
       <c r="AH33">
-        <v>0.5924257710150699</v>
+        <v>0.5924257699371845</v>
       </c>
       <c r="AI33">
-        <v>22.69360688862349</v>
+        <v>22.6936070341827</v>
       </c>
       <c r="AJ33">
-        <v>0.7665749868376014</v>
+        <v>0.7665749856751454</v>
       </c>
       <c r="AK33">
-        <v>0.6116110271146136</v>
+        <v>0.611611022037692</v>
       </c>
       <c r="AL33">
-        <v>22.73110454276448</v>
+        <v>22.73110462813462</v>
       </c>
       <c r="AM33">
-        <v>0.7772216719199205</v>
+        <v>0.777221670128255</v>
       </c>
       <c r="AN33">
-        <v>0.6105209588876502</v>
+        <v>0.6105209559104258</v>
       </c>
       <c r="AO33">
-        <v>23.1487383750432</v>
+        <v>23.1487382049647</v>
       </c>
       <c r="AP33">
-        <v>0.7937793159931373</v>
+        <v>0.7937793211123556</v>
       </c>
       <c r="AQ33">
-        <v>0.5959755711617106</v>
+        <v>0.5959755769949142</v>
       </c>
       <c r="AR33">
-        <v>23.92063030946403</v>
+        <v>23.92062998135043</v>
       </c>
       <c r="AS33">
-        <v>0.8104287431268917</v>
+        <v>0.8104287570867508</v>
       </c>
       <c r="AT33">
-        <v>0.5685048840214203</v>
+        <v>0.5685048956935684</v>
       </c>
       <c r="AU33">
-        <v>23.93296415029109</v>
+        <v>23.93296357348662</v>
       </c>
       <c r="AV33">
-        <v>0.8167861382579822</v>
+        <v>0.8167861543881101</v>
       </c>
       <c r="AW33">
-        <v>0.5681073974235353</v>
+        <v>0.5681074181707575</v>
       </c>
       <c r="AX33">
-        <v>24.6099725833843</v>
+        <v>24.60997101620473</v>
       </c>
       <c r="AY33">
-        <v>0.8308019003483891</v>
+        <v>0.8308019184351164</v>
       </c>
       <c r="AZ33">
-        <v>0.5432852410470904</v>
+        <v>0.5432852990750039</v>
       </c>
     </row>
     <row r="34">
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>23.09130738232558</v>
+        <v>23.09130738393918</v>
       </c>
       <c r="E34">
         <v>36.7783252635105</v>
@@ -5893,139 +5893,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H34">
-        <v>23.14385577721444</v>
+        <v>23.14385577672535</v>
       </c>
       <c r="I34">
-        <v>0.6180310735987883</v>
+        <v>0.6180310736105222</v>
       </c>
       <c r="J34">
-        <v>0.5965466009276867</v>
+        <v>0.5965466009447441</v>
       </c>
       <c r="K34">
-        <v>22.20066653686231</v>
+        <v>22.20066653993478</v>
       </c>
       <c r="L34">
-        <v>0.6611521097597738</v>
+        <v>0.6611521096925692</v>
       </c>
       <c r="M34">
-        <v>0.6287520800128935</v>
+        <v>0.6287520799100407</v>
       </c>
       <c r="N34">
-        <v>22.97827799673806</v>
+        <v>22.97827799059887</v>
       </c>
       <c r="O34">
-        <v>0.6837308856743245</v>
+        <v>0.6837308853640313</v>
       </c>
       <c r="P34">
-        <v>0.6022126057586739</v>
+        <v>0.6022126059719956</v>
       </c>
       <c r="Q34">
-        <v>22.43045238265405</v>
+        <v>22.43045239087701</v>
       </c>
       <c r="R34">
-        <v>0.6888038109726343</v>
+        <v>0.6888038106701424</v>
       </c>
       <c r="S34">
-        <v>0.6209156080989726</v>
+        <v>0.6209156078250304</v>
       </c>
       <c r="T34">
-        <v>22.72927109464134</v>
+        <v>22.72927109858281</v>
       </c>
       <c r="U34">
-        <v>0.6962044028996262</v>
+        <v>0.6962044020648903</v>
       </c>
       <c r="V34">
-        <v>0.6107307603157536</v>
+        <v>0.6107307601827909</v>
       </c>
       <c r="W34">
-        <v>23.14413429725808</v>
+        <v>23.14413431776531</v>
       </c>
       <c r="X34">
-        <v>0.7070722927604218</v>
+        <v>0.7070722904940367</v>
       </c>
       <c r="Y34">
-        <v>0.5962983241614153</v>
+        <v>0.5962983234494537</v>
       </c>
       <c r="Z34">
-        <v>23.67992236945596</v>
+        <v>23.6799224015592</v>
       </c>
       <c r="AA34">
-        <v>0.7108927045641135</v>
+        <v>0.7108927018031206</v>
       </c>
       <c r="AB34">
-        <v>0.5772241078608343</v>
+        <v>0.5772241067183475</v>
       </c>
       <c r="AC34">
-        <v>23.33379985110889</v>
+        <v>23.33380014428542</v>
       </c>
       <c r="AD34">
-        <v>0.7408014526744857</v>
+        <v>0.7408014473509696</v>
       </c>
       <c r="AE34">
-        <v>0.5892348795007754</v>
+        <v>0.5892348692123011</v>
       </c>
       <c r="AF34">
-        <v>23.22175405843157</v>
+        <v>23.22175427611409</v>
       </c>
       <c r="AG34">
-        <v>0.7477674868031832</v>
+        <v>0.7477674812294375</v>
       </c>
       <c r="AH34">
-        <v>0.5933550789970321</v>
+        <v>0.5933550713335545</v>
       </c>
       <c r="AI34">
-        <v>22.61865561990444</v>
+        <v>22.61865577150324</v>
       </c>
       <c r="AJ34">
-        <v>0.7637391426381358</v>
+        <v>0.7637391400866147</v>
       </c>
       <c r="AK34">
-        <v>0.6143521292366032</v>
+        <v>0.6143521240449841</v>
       </c>
       <c r="AL34">
-        <v>22.77387379872762</v>
+        <v>22.77387396502941</v>
       </c>
       <c r="AM34">
-        <v>0.7734920332965789</v>
+        <v>0.7734920297714635</v>
       </c>
       <c r="AN34">
-        <v>0.6091929992294639</v>
+        <v>0.6091929936897863</v>
       </c>
       <c r="AO34">
-        <v>23.19296065383396</v>
+        <v>23.19296067202134</v>
       </c>
       <c r="AP34">
-        <v>0.7884367946622814</v>
+        <v>0.7884367964762423</v>
       </c>
       <c r="AQ34">
-        <v>0.5945637108168182</v>
+        <v>0.5945637101332762</v>
       </c>
       <c r="AR34">
-        <v>23.89387665850223</v>
+        <v>23.89387635818347</v>
       </c>
       <c r="AS34">
-        <v>0.804048843885897</v>
+        <v>0.8040488537789454</v>
       </c>
       <c r="AT34">
-        <v>0.5696233327867892</v>
+        <v>0.5696233434600699</v>
       </c>
       <c r="AU34">
-        <v>23.76754305592666</v>
+        <v>23.76754248601103</v>
       </c>
       <c r="AV34">
-        <v>0.8098402207905973</v>
+        <v>0.8098402325800589</v>
       </c>
       <c r="AW34">
-        <v>0.5741952625943242</v>
+        <v>0.5741952828594874</v>
       </c>
       <c r="AX34">
-        <v>24.53339379730529</v>
+        <v>24.53339252058725</v>
       </c>
       <c r="AY34">
-        <v>0.8236718459068502</v>
+        <v>0.8236718578523646</v>
       </c>
       <c r="AZ34">
-        <v>0.5462957336010502</v>
+        <v>0.5462957806151448</v>
       </c>
     </row>
     <row r="35">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>23.05344953484236</v>
+        <v>23.05344953325911</v>
       </c>
       <c r="E35">
         <v>36.7783252635105</v>
@@ -6057,139 +6057,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H35">
-        <v>23.09273363324128</v>
+        <v>23.09273363287555</v>
       </c>
       <c r="I35">
-        <v>0.617995194249328</v>
+        <v>0.617995194261569</v>
       </c>
       <c r="J35">
-        <v>0.5983205485742765</v>
+        <v>0.5983205485870157</v>
       </c>
       <c r="K35">
-        <v>22.13753534048172</v>
+        <v>22.13753534335453</v>
       </c>
       <c r="L35">
-        <v>0.6611417899323763</v>
+        <v>0.6611417898659965</v>
       </c>
       <c r="M35">
-        <v>0.6308585888014309</v>
+        <v>0.6308585887055151</v>
       </c>
       <c r="N35">
-        <v>22.8349445490784</v>
+        <v>22.83494454390478</v>
       </c>
       <c r="O35">
-        <v>0.6836410818050516</v>
+        <v>0.6836410814938477</v>
       </c>
       <c r="P35">
-        <v>0.607097806784521</v>
+        <v>0.6070978069627303</v>
       </c>
       <c r="Q35">
-        <v>22.36823806508183</v>
+        <v>22.36823807379821</v>
       </c>
       <c r="R35">
-        <v>0.6887230346077483</v>
+        <v>0.6887230343037238</v>
       </c>
       <c r="S35">
-        <v>0.6230476406661273</v>
+        <v>0.6230476403731492</v>
       </c>
       <c r="T35">
-        <v>22.61175697591824</v>
+        <v>22.61175696360887</v>
       </c>
       <c r="U35">
-        <v>0.6960749758000186</v>
+        <v>0.6960749749662334</v>
       </c>
       <c r="V35">
-        <v>0.6147740012290861</v>
+        <v>0.6147740016504871</v>
       </c>
       <c r="W35">
-        <v>23.076131509712</v>
+        <v>23.07613152593255</v>
       </c>
       <c r="X35">
-        <v>0.7066742281563816</v>
+        <v>0.7066742258667384</v>
       </c>
       <c r="Y35">
-        <v>0.598632636116593</v>
+        <v>0.5986326355648045</v>
       </c>
       <c r="Z35">
-        <v>23.4903603366733</v>
+        <v>23.49036038035827</v>
       </c>
       <c r="AA35">
-        <v>0.7103690221384849</v>
+        <v>0.7103690193349264</v>
       </c>
       <c r="AB35">
-        <v>0.5839370089065129</v>
+        <v>0.5839370073944814</v>
       </c>
       <c r="AC35">
-        <v>23.20518528306718</v>
+        <v>23.2051855560693</v>
       </c>
       <c r="AD35">
-        <v>0.7394452486860534</v>
+        <v>0.7394452428240018</v>
       </c>
       <c r="AE35">
-        <v>0.5938867622313976</v>
+        <v>0.5938867526996555</v>
       </c>
       <c r="AF35">
-        <v>23.24232059243287</v>
+        <v>23.24232079756103</v>
       </c>
       <c r="AG35">
-        <v>0.7462042379762602</v>
+        <v>0.7462042316341396</v>
       </c>
       <c r="AH35">
-        <v>0.5927354767318285</v>
+        <v>0.5927354695279402</v>
       </c>
       <c r="AI35">
-        <v>22.69347945702233</v>
+        <v>22.69347957829186</v>
       </c>
       <c r="AJ35">
-        <v>0.7612108448963886</v>
+        <v>0.7612108406507569</v>
       </c>
       <c r="AK35">
-        <v>0.6118052554052151</v>
+        <v>0.6118052512800932</v>
       </c>
       <c r="AL35">
-        <v>22.72303875456901</v>
+        <v>22.72303901852915</v>
       </c>
       <c r="AM35">
-        <v>0.770039119328475</v>
+        <v>0.7700391136141292</v>
       </c>
       <c r="AN35">
-        <v>0.610907119226102</v>
+        <v>0.6109071101902164</v>
       </c>
       <c r="AO35">
-        <v>23.02511173313541</v>
+        <v>23.02511191446585</v>
       </c>
       <c r="AP35">
-        <v>0.7832830265259871</v>
+        <v>0.7832830241647174</v>
       </c>
       <c r="AQ35">
-        <v>0.600493287904543</v>
+        <v>0.6004932815497845</v>
       </c>
       <c r="AR35">
-        <v>23.7318639833714</v>
+        <v>23.73186416231179</v>
       </c>
       <c r="AS35">
-        <v>0.7965826135905658</v>
+        <v>0.7965826171981045</v>
       </c>
       <c r="AT35">
-        <v>0.5755411555177274</v>
+        <v>0.5755411491699082</v>
       </c>
       <c r="AU35">
-        <v>23.64715092019183</v>
+        <v>23.6471443082622</v>
       </c>
       <c r="AV35">
-        <v>0.8013718017417313</v>
+        <v>0.8013718066835418</v>
       </c>
       <c r="AW35">
-        <v>0.5784789277507388</v>
+        <v>0.5784791585963421</v>
       </c>
       <c r="AX35">
-        <v>24.28788501507309</v>
+        <v>24.28788398820688</v>
       </c>
       <c r="AY35">
-        <v>0.8119303040251304</v>
+        <v>0.8119303080145418</v>
       </c>
       <c r="AZ35">
-        <v>0.5553502059021389</v>
+        <v>0.5553502431862443</v>
       </c>
     </row>
     <row r="36">
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="D36">
-        <v>23.0608733011215</v>
+        <v>23.06087330044621</v>
       </c>
       <c r="E36">
         <v>36.7783252635105</v>
@@ -6221,139 +6221,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H36">
-        <v>23.11954846358823</v>
+        <v>23.11954846271749</v>
       </c>
       <c r="I36">
-        <v>0.6176374428783138</v>
+        <v>0.6176374428955664</v>
       </c>
       <c r="J36">
-        <v>0.5973986270969242</v>
+        <v>0.5973986271272735</v>
       </c>
       <c r="K36">
-        <v>22.15690426308864</v>
+        <v>22.15690426504289</v>
       </c>
       <c r="L36">
-        <v>0.6610309869644317</v>
+        <v>0.6610309869122564</v>
       </c>
       <c r="M36">
-        <v>0.6302191615886715</v>
+        <v>0.6302191615234176</v>
       </c>
       <c r="N36">
-        <v>22.90270575526258</v>
+        <v>22.90270574745689</v>
       </c>
       <c r="O36">
-        <v>0.6830410955684432</v>
+        <v>0.6830410952847965</v>
       </c>
       <c r="P36">
-        <v>0.6047729413450942</v>
+        <v>0.6047729416156713</v>
       </c>
       <c r="Q36">
-        <v>22.39984136577718</v>
+        <v>22.39984136952984</v>
       </c>
       <c r="R36">
-        <v>0.6882641874686758</v>
+        <v>0.688264187204386</v>
       </c>
       <c r="S36">
-        <v>0.6219527045366355</v>
+        <v>0.6219527044111151</v>
       </c>
       <c r="T36">
-        <v>22.65919051897293</v>
+        <v>22.65919051482775</v>
       </c>
       <c r="U36">
-        <v>0.6954382226243554</v>
+        <v>0.6954382219054712</v>
       </c>
       <c r="V36">
-        <v>0.6131057187118798</v>
+        <v>0.6131057188604494</v>
       </c>
       <c r="W36">
-        <v>23.11785662991304</v>
+        <v>23.11785663730015</v>
       </c>
       <c r="X36">
-        <v>0.704601317694082</v>
+        <v>0.7046013157798527</v>
       </c>
       <c r="Y36">
-        <v>0.5971983464715483</v>
+        <v>0.5971983462169966</v>
       </c>
       <c r="Z36">
-        <v>23.65515659834846</v>
+        <v>23.655156616071</v>
       </c>
       <c r="AA36">
-        <v>0.7076719493595529</v>
+        <v>0.7076719470447799</v>
       </c>
       <c r="AB36">
-        <v>0.5781335197242551</v>
+        <v>0.5781335191043684</v>
       </c>
       <c r="AC36">
-        <v>23.30796053739882</v>
+        <v>23.30796076109535</v>
       </c>
       <c r="AD36">
-        <v>0.7328392466161948</v>
+        <v>0.7328392408816321</v>
       </c>
       <c r="AE36">
-        <v>0.5901379194476916</v>
+        <v>0.5901379115137048</v>
       </c>
       <c r="AF36">
-        <v>23.24987827071127</v>
+        <v>23.24987845291415</v>
       </c>
       <c r="AG36">
-        <v>0.7398914845152426</v>
+        <v>0.7398914778506011</v>
       </c>
       <c r="AH36">
-        <v>0.592303227498431</v>
+        <v>0.5923032210923552</v>
       </c>
       <c r="AI36">
-        <v>22.75017540475999</v>
+        <v>22.750175607453</v>
       </c>
       <c r="AJ36">
-        <v>0.7553611808501715</v>
+        <v>0.7553611753547694</v>
       </c>
       <c r="AK36">
-        <v>0.6097338329288984</v>
+        <v>0.609733825980431</v>
       </c>
       <c r="AL36">
-        <v>22.82311484085613</v>
+        <v>22.82311513941272</v>
       </c>
       <c r="AM36">
-        <v>0.7629851017662035</v>
+        <v>0.7629850947860841</v>
       </c>
       <c r="AN36">
-        <v>0.6073023305435077</v>
+        <v>0.6073023201781841</v>
       </c>
       <c r="AO36">
-        <v>22.87765131376776</v>
+        <v>22.87765114875862</v>
       </c>
       <c r="AP36">
-        <v>0.7734014676482637</v>
+        <v>0.7734014622366525</v>
       </c>
       <c r="AQ36">
-        <v>0.605429360631802</v>
+        <v>0.6054293660578043</v>
       </c>
       <c r="AR36">
-        <v>23.54915873367149</v>
+        <v>23.54915909572239</v>
       </c>
       <c r="AS36">
-        <v>0.7810384565266301</v>
+        <v>0.7810384542294808</v>
       </c>
       <c r="AT36">
-        <v>0.5818376264613488</v>
+        <v>0.581837613723709</v>
       </c>
       <c r="AU36">
-        <v>23.59714156663345</v>
+        <v>23.59714153360903</v>
       </c>
       <c r="AV36">
-        <v>0.784842566190218</v>
+        <v>0.7848425654260541</v>
       </c>
       <c r="AW36">
-        <v>0.5801445912106643</v>
+        <v>0.5801445924918328</v>
       </c>
       <c r="AX36">
-        <v>24.03462809012567</v>
+        <v>24.03462782762035</v>
       </c>
       <c r="AY36">
-        <v>0.7916868678540425</v>
+        <v>0.7916868690815128</v>
       </c>
       <c r="AZ36">
-        <v>0.5644621179764001</v>
+        <v>0.5644621277452242</v>
       </c>
     </row>
     <row r="37">
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>22.10393742808749</v>
+        <v>22.10393744731806</v>
       </c>
       <c r="E37">
         <v>36.7783252635105</v>
@@ -6385,139 +6385,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H37">
-        <v>22.10393742808749</v>
+        <v>22.10393744731806</v>
       </c>
       <c r="I37">
-        <v>0.6491293981171593</v>
+        <v>0.6491293974836646</v>
       </c>
       <c r="J37">
-        <v>0.6319831478123158</v>
+        <v>0.6319831471719984</v>
       </c>
       <c r="K37">
-        <v>22.1663888486286</v>
+        <v>22.16638884199873</v>
       </c>
       <c r="L37">
-        <v>0.6726938100643867</v>
+        <v>0.6726938094357966</v>
       </c>
       <c r="M37">
-        <v>0.6298334709520158</v>
+        <v>0.6298334711834668</v>
       </c>
       <c r="N37">
-        <v>22.18031607616891</v>
+        <v>22.18031609777524</v>
       </c>
       <c r="O37">
-        <v>0.7138724559852694</v>
+        <v>0.713872453569791</v>
       </c>
       <c r="P37">
-        <v>0.6293310574607023</v>
+        <v>0.629331056757214</v>
       </c>
       <c r="Q37">
-        <v>22.21612206879708</v>
+        <v>22.21612219808565</v>
       </c>
       <c r="R37">
-        <v>0.7330735681796979</v>
+        <v>0.7330735650141639</v>
       </c>
       <c r="S37">
-        <v>0.6281425149536812</v>
+        <v>0.6281425106140773</v>
       </c>
       <c r="T37">
-        <v>23.10877302248595</v>
+        <v>23.10877347893753</v>
       </c>
       <c r="U37">
-        <v>0.7641145701796569</v>
+        <v>0.7641145729134087</v>
       </c>
       <c r="V37">
-        <v>0.5976180638805242</v>
+        <v>0.5976180479799079</v>
       </c>
       <c r="W37">
-        <v>23.89751555269296</v>
+        <v>23.89751614945255</v>
       </c>
       <c r="X37">
-        <v>0.8050135970665708</v>
+        <v>0.8050136128397272</v>
       </c>
       <c r="Y37">
-        <v>0.5696571615683536</v>
+        <v>0.5696571400078868</v>
       </c>
       <c r="Z37">
-        <v>23.43411622497721</v>
+        <v>23.43411556280579</v>
       </c>
       <c r="AA37">
-        <v>0.8312799512450997</v>
+        <v>0.8312799815672782</v>
       </c>
       <c r="AB37">
-        <v>0.5861980571914297</v>
+        <v>0.5861980804170525</v>
       </c>
       <c r="AC37">
-        <v>23.74122354505201</v>
+        <v>23.74122268414983</v>
       </c>
       <c r="AD37">
-        <v>0.844798996076043</v>
+        <v>0.8447990342058093</v>
       </c>
       <c r="AE37">
-        <v>0.5751892001982707</v>
+        <v>0.5751892306182468</v>
       </c>
       <c r="AF37">
-        <v>24.09345367917906</v>
+        <v>24.09345128984396</v>
       </c>
       <c r="AG37">
-        <v>0.8552680924950157</v>
+        <v>0.855268129262565</v>
       </c>
       <c r="AH37">
-        <v>0.5625180062419399</v>
+        <v>0.5625180931363116</v>
       </c>
       <c r="AI37">
-        <v>25.04340009920627</v>
+        <v>25.04339649920679</v>
       </c>
       <c r="AJ37">
-        <v>0.867386202617997</v>
+        <v>0.8673862380756263</v>
       </c>
       <c r="AK37">
-        <v>0.5272172628910261</v>
+        <v>0.5272173990441194</v>
       </c>
       <c r="AL37">
-        <v>26.22389431220714</v>
+        <v>26.22388752831692</v>
       </c>
       <c r="AM37">
-        <v>0.8786659602863093</v>
+        <v>0.8786659982071164</v>
       </c>
       <c r="AN37">
-        <v>0.4815660284953596</v>
+        <v>0.4815662985139236</v>
       </c>
       <c r="AO37">
-        <v>27.67808743736451</v>
+        <v>27.67814648116039</v>
       </c>
       <c r="AP37">
-        <v>0.8873752875208518</v>
+        <v>0.887375330747286</v>
       </c>
       <c r="AQ37">
-        <v>0.4223315551744488</v>
+        <v>0.4223290296348496</v>
       </c>
       <c r="AR37">
-        <v>29.70058004907724</v>
+        <v>29.70061013568963</v>
       </c>
       <c r="AS37">
-        <v>0.9006802935262573</v>
+        <v>0.9006803613184917</v>
       </c>
       <c r="AT37">
-        <v>0.3345535787313146</v>
+        <v>0.3345522124439876</v>
       </c>
       <c r="AU37">
-        <v>30.93459908890777</v>
+        <v>30.93459211040215</v>
       </c>
       <c r="AV37">
-        <v>0.9084155037317208</v>
+        <v>0.9084155839464005</v>
       </c>
       <c r="AW37">
-        <v>0.2778819866403686</v>
+        <v>0.2778823119793755</v>
       </c>
       <c r="AX37">
-        <v>32.08987709176358</v>
+        <v>32.08986935651145</v>
       </c>
       <c r="AY37">
-        <v>0.9158862420280217</v>
+        <v>0.9158863365929928</v>
       </c>
       <c r="AZ37">
-        <v>0.2228010330702021</v>
+        <v>0.2228014045769923</v>
       </c>
     </row>
     <row r="38">
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>22.23215319271402</v>
+        <v>22.23215321315867</v>
       </c>
       <c r="E38">
         <v>36.7783252635105</v>
@@ -6549,139 +6549,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H38">
-        <v>22.21336832122952</v>
+        <v>22.21336834244824</v>
       </c>
       <c r="I38">
-        <v>0.6472802226904981</v>
+        <v>0.6472802219905976</v>
       </c>
       <c r="J38">
-        <v>0.6283314248539937</v>
+        <v>0.6283314241440906</v>
       </c>
       <c r="K38">
-        <v>22.17668523443627</v>
+        <v>22.1766852474829</v>
       </c>
       <c r="L38">
-        <v>0.6663741688953713</v>
+        <v>0.6663741680455113</v>
       </c>
       <c r="M38">
-        <v>0.6295143037516912</v>
+        <v>0.6295143033188001</v>
       </c>
       <c r="N38">
-        <v>22.09647526464956</v>
+        <v>22.09647529264286</v>
       </c>
       <c r="O38">
-        <v>0.697702230969182</v>
+        <v>0.6977022290907371</v>
       </c>
       <c r="P38">
-        <v>0.6321178416584672</v>
+        <v>0.6321178407323635</v>
       </c>
       <c r="Q38">
-        <v>22.08427348267199</v>
+        <v>22.08427359038169</v>
       </c>
       <c r="R38">
-        <v>0.7109358571589171</v>
+        <v>0.7109358538318201</v>
       </c>
       <c r="S38">
-        <v>0.6325210862943751</v>
+        <v>0.632521082711178</v>
       </c>
       <c r="T38">
-        <v>22.52052886247612</v>
+        <v>22.5205290081705</v>
       </c>
       <c r="U38">
-        <v>0.723360917531636</v>
+        <v>0.7233609125605374</v>
       </c>
       <c r="V38">
-        <v>0.6177942424464151</v>
+        <v>0.6177942374963239</v>
       </c>
       <c r="W38">
-        <v>23.00887686894284</v>
+        <v>23.00887721796509</v>
       </c>
       <c r="X38">
-        <v>0.7396261355081913</v>
+        <v>0.7396261330782155</v>
       </c>
       <c r="Y38">
-        <v>0.6010430435740617</v>
+        <v>0.601043031459777</v>
       </c>
       <c r="Z38">
-        <v>23.06005852233731</v>
+        <v>23.0600587758778</v>
       </c>
       <c r="AA38">
-        <v>0.7539983296425135</v>
+        <v>0.753998330398027</v>
       </c>
       <c r="AB38">
-        <v>0.599325372080844</v>
+        <v>0.5993253632543724</v>
       </c>
       <c r="AC38">
-        <v>23.84738695502346</v>
+        <v>23.84738691778777</v>
       </c>
       <c r="AD38">
-        <v>0.7792358700064386</v>
+        <v>0.7792358752792456</v>
       </c>
       <c r="AE38">
-        <v>0.5714472422559815</v>
+        <v>0.5714472435902768</v>
       </c>
       <c r="AF38">
-        <v>25.49003816192742</v>
+        <v>25.49003830851661</v>
       </c>
       <c r="AG38">
-        <v>0.7947521245689063</v>
+        <v>0.7947521338282755</v>
       </c>
       <c r="AH38">
-        <v>0.5102644164450149</v>
+        <v>0.5102644107250786</v>
       </c>
       <c r="AI38">
-        <v>26.20359534947436</v>
+        <v>26.20359525437953</v>
       </c>
       <c r="AJ38">
-        <v>0.8287249317479332</v>
+        <v>0.8287249604958051</v>
       </c>
       <c r="AK38">
-        <v>0.482411851869546</v>
+        <v>0.4824118553709781</v>
       </c>
       <c r="AL38">
-        <v>26.51943438616479</v>
+        <v>26.51943380052586</v>
       </c>
       <c r="AM38">
-        <v>0.849121666411473</v>
+        <v>0.8491216692996308</v>
       </c>
       <c r="AN38">
-        <v>0.4698564720756657</v>
+        <v>0.4698564949056742</v>
       </c>
       <c r="AO38">
-        <v>25.9865480000763</v>
+        <v>25.98654663656215</v>
       </c>
       <c r="AP38">
-        <v>0.8530308527280686</v>
+        <v>0.8530308856965728</v>
       </c>
       <c r="AQ38">
-        <v>0.4908699552215187</v>
+        <v>0.4908700091848545</v>
       </c>
       <c r="AR38">
-        <v>25.52771206862847</v>
+        <v>25.52770837621152</v>
       </c>
       <c r="AS38">
-        <v>0.8677731712103081</v>
+        <v>0.867773223578244</v>
       </c>
       <c r="AT38">
-        <v>0.5086184798112612</v>
+        <v>0.5086186215991663</v>
       </c>
       <c r="AU38">
-        <v>26.02314667278941</v>
+        <v>26.02314051595133</v>
       </c>
       <c r="AV38">
-        <v>0.8766867149564259</v>
+        <v>0.8766867646095983</v>
       </c>
       <c r="AW38">
-        <v>0.4892998881320823</v>
+        <v>0.4893001287340341</v>
       </c>
       <c r="AX38">
-        <v>26.56163101974402</v>
+        <v>26.56162538239185</v>
       </c>
       <c r="AY38">
-        <v>0.8833651244186799</v>
+        <v>0.8833651731229223</v>
       </c>
       <c r="AZ38">
-        <v>0.4679414453226308</v>
+        <v>0.4679416702948714</v>
       </c>
     </row>
     <row r="39">
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>22.26706264125324</v>
+        <v>22.26706266212441</v>
       </c>
       <c r="E39">
         <v>36.7783252635105</v>
@@ -6713,139 +6713,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H39">
-        <v>22.19889393183644</v>
+        <v>22.19889395394818</v>
       </c>
       <c r="I39">
-        <v>0.6472287373179957</v>
+        <v>0.647228736624641</v>
       </c>
       <c r="J39">
-        <v>0.628816545312174</v>
+        <v>0.6288165445724452</v>
       </c>
       <c r="K39">
-        <v>22.20897384202701</v>
+        <v>22.20897386016404</v>
       </c>
       <c r="L39">
-        <v>0.6662561930641608</v>
+        <v>0.6662561921609627</v>
       </c>
       <c r="M39">
-        <v>0.6284350182280195</v>
+        <v>0.6284350176232585</v>
       </c>
       <c r="N39">
-        <v>22.0830585136105</v>
+        <v>22.08305856908887</v>
       </c>
       <c r="O39">
-        <v>0.6951197036800285</v>
+        <v>0.6951197017243294</v>
       </c>
       <c r="P39">
-        <v>0.6326256329068237</v>
+        <v>0.632625631065846</v>
       </c>
       <c r="Q39">
-        <v>22.11365606231145</v>
+        <v>22.11365616829987</v>
       </c>
       <c r="R39">
-        <v>0.7082661397085106</v>
+        <v>0.7082661357708864</v>
       </c>
       <c r="S39">
-        <v>0.6316155965162789</v>
+        <v>0.6316155929866665</v>
       </c>
       <c r="T39">
-        <v>22.53470242727872</v>
+        <v>22.53470256303951</v>
       </c>
       <c r="U39">
-        <v>0.7204592489087327</v>
+        <v>0.7204592425498192</v>
       </c>
       <c r="V39">
-        <v>0.6173431115136748</v>
+        <v>0.6173431069269782</v>
       </c>
       <c r="W39">
-        <v>22.94781539556352</v>
+        <v>22.94781572486906</v>
       </c>
       <c r="X39">
-        <v>0.7364241948925039</v>
+        <v>0.7364241889241603</v>
       </c>
       <c r="Y39">
-        <v>0.6031438663670634</v>
+        <v>0.6031438549825928</v>
       </c>
       <c r="Z39">
-        <v>22.6006244576922</v>
+        <v>22.60062467409398</v>
       </c>
       <c r="AA39">
-        <v>0.7469732062341955</v>
+        <v>0.7469732010820553</v>
       </c>
       <c r="AB39">
-        <v>0.615075419879871</v>
+        <v>0.6150754125092321</v>
       </c>
       <c r="AC39">
-        <v>23.11285152115039</v>
+        <v>23.11285174176409</v>
       </c>
       <c r="AD39">
-        <v>0.7646449185916887</v>
+        <v>0.7646449146027694</v>
       </c>
       <c r="AE39">
-        <v>0.5974202708609596</v>
+        <v>0.597420263147986</v>
       </c>
       <c r="AF39">
-        <v>25.11370787950299</v>
+        <v>25.11370797027345</v>
       </c>
       <c r="AG39">
-        <v>0.7802541028556874</v>
+        <v>0.7802540994664462</v>
       </c>
       <c r="AH39">
-        <v>0.5245460585794742</v>
+        <v>0.5245460550648302</v>
       </c>
       <c r="AI39">
-        <v>25.69204040406584</v>
+        <v>25.69204042422135</v>
       </c>
       <c r="AJ39">
-        <v>0.8000112483524892</v>
+        <v>0.8000112465597109</v>
       </c>
       <c r="AK39">
-        <v>0.5022953174739677</v>
+        <v>0.5022953164342936</v>
       </c>
       <c r="AL39">
-        <v>26.03864697760438</v>
+        <v>26.03864702093733</v>
       </c>
       <c r="AM39">
-        <v>0.80700683213346</v>
+        <v>0.807006829395282</v>
       </c>
       <c r="AN39">
-        <v>0.4887054060607111</v>
+        <v>0.4887054041410626</v>
       </c>
       <c r="AO39">
-        <v>26.2134940584765</v>
+        <v>26.21349400527679</v>
       </c>
       <c r="AP39">
-        <v>0.827274343004009</v>
+        <v>0.827274351789443</v>
       </c>
       <c r="AQ39">
-        <v>0.4817065181585592</v>
+        <v>0.4817065195506103</v>
       </c>
       <c r="AR39">
-        <v>26.17786053146744</v>
+        <v>26.17785999986748</v>
       </c>
       <c r="AS39">
-        <v>0.8401025460734068</v>
+        <v>0.8401025601720132</v>
       </c>
       <c r="AT39">
-        <v>0.4830602051810329</v>
+        <v>0.4830602253227006</v>
       </c>
       <c r="AU39">
-        <v>26.20205390017057</v>
+        <v>26.20205264782381</v>
       </c>
       <c r="AV39">
-        <v>0.848624980571242</v>
+        <v>0.8486249966415282</v>
       </c>
       <c r="AW39">
-        <v>0.4819289188066779</v>
+        <v>0.4819289672739041</v>
       </c>
       <c r="AX39">
-        <v>27.14795566004147</v>
+        <v>27.14795426767785</v>
       </c>
       <c r="AY39">
-        <v>0.8612558416679517</v>
+        <v>0.8612558788575371</v>
       </c>
       <c r="AZ39">
-        <v>0.4437121109955692</v>
+        <v>0.4437121669647044</v>
       </c>
     </row>
     <row r="40">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>23.4079131814763</v>
+        <v>23.40791318930587</v>
       </c>
       <c r="E40">
         <v>36.7783252635105</v>
@@ -6877,139 +6877,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H40">
-        <v>23.22905148159902</v>
+        <v>23.22905152867819</v>
       </c>
       <c r="I40">
-        <v>0.619735203434455</v>
+        <v>0.6197352015763288</v>
       </c>
       <c r="J40">
-        <v>0.5935608743064132</v>
+        <v>0.5935608726587871</v>
       </c>
       <c r="K40">
-        <v>23.44885894529377</v>
+        <v>23.44885894198043</v>
       </c>
       <c r="L40">
-        <v>0.6333832928066546</v>
+        <v>0.6333832920684528</v>
       </c>
       <c r="M40">
-        <v>0.5857924748211119</v>
+        <v>0.5857924749423371</v>
       </c>
       <c r="N40">
-        <v>23.89396757822901</v>
+        <v>23.89396749579228</v>
       </c>
       <c r="O40">
-        <v>0.6787383133515561</v>
+        <v>0.6787383138212542</v>
       </c>
       <c r="P40">
-        <v>0.5697095367490579</v>
+        <v>0.5697095397470512</v>
       </c>
       <c r="Q40">
-        <v>22.94928918825111</v>
+        <v>22.94928906048966</v>
       </c>
       <c r="R40">
-        <v>0.7124562340646758</v>
+        <v>0.7124562328143054</v>
       </c>
       <c r="S40">
-        <v>0.6031674254669076</v>
+        <v>0.6031674298744828</v>
       </c>
       <c r="T40">
-        <v>22.42719525672033</v>
+        <v>22.42719516422494</v>
       </c>
       <c r="U40">
-        <v>0.7496361943136062</v>
+        <v>0.7496362009720235</v>
       </c>
       <c r="V40">
-        <v>0.6210334881073715</v>
+        <v>0.6210334912288265</v>
       </c>
       <c r="W40">
-        <v>23.24623132458421</v>
+        <v>23.24623127762615</v>
       </c>
       <c r="X40">
-        <v>0.7695284008053538</v>
+        <v>0.7695284086164346</v>
       </c>
       <c r="Y40">
-        <v>0.5927822152376228</v>
+        <v>0.5927822169636211</v>
       </c>
       <c r="Z40">
-        <v>24.28943689014853</v>
+        <v>24.28943670669189</v>
       </c>
       <c r="AA40">
-        <v>0.7976390916157918</v>
+        <v>0.7976391115670192</v>
       </c>
       <c r="AB40">
-        <v>0.5553813160123359</v>
+        <v>0.5553813226852292</v>
       </c>
       <c r="AC40">
-        <v>25.17663121409698</v>
+        <v>25.17663048031405</v>
       </c>
       <c r="AD40">
-        <v>0.8204771615311517</v>
+        <v>0.8204771921701448</v>
       </c>
       <c r="AE40">
-        <v>0.5221998150127227</v>
+        <v>0.5221998427435709</v>
       </c>
       <c r="AF40">
-        <v>25.66329195775386</v>
+        <v>25.66328996040546</v>
       </c>
       <c r="AG40">
-        <v>0.8370226248867162</v>
+        <v>0.8370226563979093</v>
       </c>
       <c r="AH40">
-        <v>0.5034864855964408</v>
+        <v>0.5034865628896729</v>
       </c>
       <c r="AI40">
-        <v>26.21332004065749</v>
+        <v>26.21331718998603</v>
       </c>
       <c r="AJ40">
-        <v>0.848164293111459</v>
+        <v>0.8481643268437629</v>
       </c>
       <c r="AK40">
-        <v>0.4818498928032821</v>
+        <v>0.481850005458966</v>
       </c>
       <c r="AL40">
-        <v>27.25224568783856</v>
+        <v>27.25224228647756</v>
       </c>
       <c r="AM40">
-        <v>0.8611226525745019</v>
+        <v>0.8611226841895985</v>
       </c>
       <c r="AN40">
-        <v>0.439959500999161</v>
+        <v>0.4399596408571014</v>
       </c>
       <c r="AO40">
-        <v>29.18368978238489</v>
+        <v>29.18368603908092</v>
       </c>
       <c r="AP40">
-        <v>0.874107463704207</v>
+        <v>0.874107506403637</v>
       </c>
       <c r="AQ40">
-        <v>0.3577729313257353</v>
+        <v>0.3577730965142043</v>
       </c>
       <c r="AR40">
-        <v>31.42216677871811</v>
+        <v>31.42216211157808</v>
       </c>
       <c r="AS40">
-        <v>0.8878957158863929</v>
+        <v>0.8878957750936631</v>
       </c>
       <c r="AT40">
-        <v>0.255366874017857</v>
+        <v>0.2553670951741511</v>
       </c>
       <c r="AU40">
-        <v>33.43621416102988</v>
+        <v>33.43620723048705</v>
       </c>
       <c r="AV40">
-        <v>0.8982594701310169</v>
+        <v>0.898259526472314</v>
       </c>
       <c r="AW40">
-        <v>0.1567117136470396</v>
+        <v>0.1567120631394307</v>
       </c>
       <c r="AX40">
-        <v>34.42567943712844</v>
+        <v>34.42567027560303</v>
       </c>
       <c r="AY40">
-        <v>0.9086657345150582</v>
+        <v>0.9086657915635197</v>
       </c>
       <c r="AZ40">
-        <v>0.1060963969453542</v>
+        <v>0.1060968731519982</v>
       </c>
     </row>
     <row r="41">
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>23.4511212046266</v>
+        <v>23.45112119925905</v>
       </c>
       <c r="E41">
         <v>36.7783252635105</v>
@@ -7041,139 +7041,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H41">
-        <v>23.4511212046266</v>
+        <v>23.45112119925905</v>
       </c>
       <c r="I41">
-        <v>0.6173773223053315</v>
+        <v>0.6173773222893426</v>
       </c>
       <c r="J41">
-        <v>0.5857595008498613</v>
+        <v>0.5857595010399009</v>
       </c>
       <c r="K41">
-        <v>22.71667281731481</v>
+        <v>22.71667278343584</v>
       </c>
       <c r="L41">
-        <v>0.6628752012978114</v>
+        <v>0.6628752020505418</v>
       </c>
       <c r="M41">
-        <v>0.6113013615069568</v>
+        <v>0.6113013626661949</v>
       </c>
       <c r="N41">
-        <v>24.35678332323823</v>
+        <v>24.35678320069415</v>
       </c>
       <c r="O41">
-        <v>0.7229838463206135</v>
+        <v>0.7229838493183236</v>
       </c>
       <c r="P41">
-        <v>0.5530348672991638</v>
+        <v>0.5530348717811173</v>
       </c>
       <c r="Q41">
-        <v>24.56411763070299</v>
+        <v>24.56411746587215</v>
       </c>
       <c r="R41">
-        <v>0.7601420134698175</v>
+        <v>0.760142017794564</v>
       </c>
       <c r="S41">
-        <v>0.5453535789350331</v>
+        <v>0.5453535850254324</v>
       </c>
       <c r="T41">
-        <v>24.2469203737808</v>
+        <v>24.24691998367375</v>
       </c>
       <c r="U41">
-        <v>0.7912858450045748</v>
+        <v>0.7912858532086549</v>
       </c>
       <c r="V41">
-        <v>0.5570333365996577</v>
+        <v>0.5570333508886635</v>
       </c>
       <c r="W41">
-        <v>25.54518770789621</v>
+        <v>25.54518700153416</v>
       </c>
       <c r="X41">
-        <v>0.8183358407599028</v>
+        <v>0.8183358537432327</v>
       </c>
       <c r="Y41">
-        <v>0.5082074662141096</v>
+        <v>0.5082074934590594</v>
       </c>
       <c r="Z41">
-        <v>25.84249731590164</v>
+        <v>25.84249621446489</v>
       </c>
       <c r="AA41">
-        <v>0.8360150271944462</v>
+        <v>0.8360150394881654</v>
       </c>
       <c r="AB41">
-        <v>0.4966989580261165</v>
+        <v>0.4966990010092699</v>
       </c>
       <c r="AC41">
-        <v>26.00556685615377</v>
+        <v>26.00556549214616</v>
       </c>
       <c r="AD41">
-        <v>0.8472208098695676</v>
+        <v>0.8472208224127464</v>
       </c>
       <c r="AE41">
-        <v>0.4902622556603111</v>
+        <v>0.4902623091243979</v>
       </c>
       <c r="AF41">
-        <v>26.67722601777638</v>
+        <v>26.67722423145592</v>
       </c>
       <c r="AG41">
-        <v>0.8625139580719926</v>
+        <v>0.8625139736760895</v>
       </c>
       <c r="AH41">
-        <v>0.463540778257415</v>
+        <v>0.4635408500581236</v>
       </c>
       <c r="AI41">
-        <v>27.49129475123706</v>
+        <v>27.4912925641121</v>
       </c>
       <c r="AJ41">
-        <v>0.8700905091512906</v>
+        <v>0.8700905259785945</v>
       </c>
       <c r="AK41">
-        <v>0.430264654306641</v>
+        <v>0.4302647449174605</v>
       </c>
       <c r="AL41">
-        <v>28.75411500128819</v>
+        <v>28.75411185753419</v>
       </c>
       <c r="AM41">
-        <v>0.888471474998785</v>
+        <v>0.8884714914446397</v>
       </c>
       <c r="AN41">
-        <v>0.3765677302659472</v>
+        <v>0.3765678666805813</v>
       </c>
       <c r="AO41">
-        <v>30.85795166708219</v>
+        <v>30.85794737823632</v>
       </c>
       <c r="AP41">
-        <v>0.9070302450830061</v>
+        <v>0.9070302617557144</v>
       </c>
       <c r="AQ41">
-        <v>0.2818984390508165</v>
+        <v>0.2818986387367317</v>
       </c>
       <c r="AR41">
-        <v>31.66502699671733</v>
+        <v>31.66502185723201</v>
       </c>
       <c r="AS41">
-        <v>0.9182267021434549</v>
+        <v>0.9182267183582721</v>
       </c>
       <c r="AT41">
-        <v>0.2436968373199161</v>
+        <v>0.2436970828284237</v>
       </c>
       <c r="AU41">
-        <v>32.48741327160942</v>
+        <v>32.48740728247973</v>
       </c>
       <c r="AV41">
-        <v>0.9278150153230389</v>
+        <v>0.9278150284209226</v>
       </c>
       <c r="AW41">
-        <v>0.2038701690763918</v>
+        <v>0.203870462549094</v>
       </c>
       <c r="AX41">
-        <v>33.03649388619452</v>
+        <v>33.03648721530396</v>
       </c>
       <c r="AY41">
-        <v>0.9365466625774925</v>
+        <v>0.9365466735039305</v>
       </c>
       <c r="AZ41">
-        <v>0.1767702997632739</v>
+        <v>0.1767706320960028</v>
       </c>
     </row>
     <row r="42">
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>22.89133441265551</v>
+        <v>22.89133441461042</v>
       </c>
       <c r="E42">
         <v>36.7783252635105</v>
@@ -7205,139 +7205,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H42">
-        <v>26.73247845769018</v>
+        <v>26.73247857783609</v>
       </c>
       <c r="I42">
-        <v>0.5038544743145424</v>
+        <v>0.503854469106769</v>
       </c>
       <c r="J42">
-        <v>0.4617035365669464</v>
+        <v>0.4617035317337</v>
       </c>
       <c r="K42">
-        <v>22.74894564340975</v>
+        <v>22.74894564017373</v>
       </c>
       <c r="L42">
-        <v>0.6511762017213585</v>
+        <v>0.6511762012683223</v>
       </c>
       <c r="M42">
-        <v>0.610181922835112</v>
+        <v>0.6101819229480125</v>
       </c>
       <c r="N42">
-        <v>23.82196585209693</v>
+        <v>23.82196580931764</v>
       </c>
       <c r="O42">
-        <v>0.6744938819741688</v>
+        <v>0.6744938813866904</v>
       </c>
       <c r="P42">
-        <v>0.5724653041328985</v>
+        <v>0.5724653056750378</v>
       </c>
       <c r="Q42">
-        <v>25.21121173360656</v>
+        <v>25.21121163769594</v>
       </c>
       <c r="R42">
-        <v>0.7216140036739931</v>
+        <v>0.7216139995210047</v>
       </c>
       <c r="S42">
-        <v>0.5210364606148404</v>
+        <v>0.5210364642675039</v>
       </c>
       <c r="T42">
-        <v>24.60869523423765</v>
+        <v>24.60869534753296</v>
       </c>
       <c r="U42">
-        <v>0.751146005814281</v>
+        <v>0.7511460017569795</v>
       </c>
       <c r="V42">
-        <v>0.5436869667195766</v>
+        <v>0.5436869625076471</v>
       </c>
       <c r="W42">
-        <v>24.16453103198456</v>
+        <v>24.16453136518279</v>
       </c>
       <c r="X42">
-        <v>0.7658088206510554</v>
+        <v>0.7658088152039755</v>
       </c>
       <c r="Y42">
-        <v>0.5600078884905455</v>
+        <v>0.5600078763714641</v>
       </c>
       <c r="Z42">
-        <v>24.69287891798501</v>
+        <v>24.69287937662958</v>
       </c>
       <c r="AA42">
-        <v>0.7826458849980422</v>
+        <v>0.7826458789567519</v>
       </c>
       <c r="AB42">
-        <v>0.5405200881409535</v>
+        <v>0.5405200710155644</v>
       </c>
       <c r="AC42">
-        <v>26.32009800361815</v>
+        <v>26.32009804195232</v>
       </c>
       <c r="AD42">
-        <v>0.7947978155069327</v>
+        <v>0.7947978048339628</v>
       </c>
       <c r="AE42">
-        <v>0.4778467604889289</v>
+        <v>0.4778467589405594</v>
       </c>
       <c r="AF42">
-        <v>27.9968191173394</v>
+        <v>27.99681972317623</v>
       </c>
       <c r="AG42">
-        <v>0.8287876589326277</v>
+        <v>0.8287876457515237</v>
       </c>
       <c r="AH42">
-        <v>0.4092466087643933</v>
+        <v>0.4092465830072781</v>
       </c>
       <c r="AI42">
-        <v>29.07998822257478</v>
+        <v>29.07998911200184</v>
       </c>
       <c r="AJ42">
-        <v>0.8484811224511225</v>
+        <v>0.8484811094726428</v>
       </c>
       <c r="AK42">
-        <v>0.3623469649915194</v>
+        <v>0.3623469258968839</v>
       </c>
       <c r="AL42">
-        <v>29.98350243608951</v>
+        <v>29.98350328116958</v>
       </c>
       <c r="AM42">
-        <v>0.864581405783565</v>
+        <v>0.8645813935470631</v>
       </c>
       <c r="AN42">
-        <v>0.3221431356929617</v>
+        <v>0.3221430976391101</v>
       </c>
       <c r="AO42">
-        <v>30.5411100833722</v>
+        <v>30.54111166378524</v>
       </c>
       <c r="AP42">
-        <v>0.8933271136131946</v>
+        <v>0.8933271058954488</v>
       </c>
       <c r="AQ42">
-        <v>0.2964890701855939</v>
+        <v>0.2964889975984593</v>
       </c>
       <c r="AR42">
-        <v>31.08511648032851</v>
+        <v>31.08511842777281</v>
       </c>
       <c r="AS42">
-        <v>0.9007914603296567</v>
+        <v>0.900791452793072</v>
       </c>
       <c r="AT42">
-        <v>0.2711089765873933</v>
+        <v>0.2711088858169266</v>
       </c>
       <c r="AU42">
-        <v>32.02943613560208</v>
+        <v>32.02943873986855</v>
       </c>
       <c r="AV42">
-        <v>0.9094671571744516</v>
+        <v>0.9094671460999927</v>
       </c>
       <c r="AW42">
-        <v>0.2259799655467406</v>
+        <v>0.2259798400503988</v>
       </c>
       <c r="AX42">
-        <v>33.04277862508632</v>
+        <v>33.04278127716891</v>
       </c>
       <c r="AY42">
-        <v>0.9226142305883073</v>
+        <v>0.9226142191523412</v>
       </c>
       <c r="AZ42">
-        <v>0.1760857710788321</v>
+        <v>0.1760856395689323</v>
       </c>
     </row>
     <row r="43">
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>22.69975939451975</v>
+        <v>22.69975938903599</v>
       </c>
       <c r="E43">
         <v>36.7783252635105</v>
@@ -7369,139 +7369,139 @@
         <v>-0.018778932657874</v>
       </c>
       <c r="H43">
-        <v>22.68082301985628</v>
+        <v>22.68082301412029</v>
       </c>
       <c r="I43">
-        <v>0.6355865009659161</v>
+        <v>0.6355865011206092</v>
       </c>
       <c r="J43">
-        <v>0.612532829099214</v>
+        <v>0.6125328292952568</v>
       </c>
       <c r="K43">
-        <v>23.10884236761735</v>
+        <v>23.108842355873</v>
       </c>
       <c r="L43">
-        <v>0.669414599609491</v>
+        <v>0.6694146000518137</v>
       </c>
       <c r="M43">
-        <v>0.5976855507179578</v>
+        <v>0.5976855511267729</v>
       </c>
       <c r="N43">
-        <v>23.49929784307953</v>
+        <v>23.49929782059379</v>
       </c>
       <c r="O43">
-        <v>0.7030182470801745</v>
+        <v>0.7030182470275347</v>
       </c>
       <c r="P43">
-        <v>0.5838310903579925</v>
+        <v>0.583831091158178</v>
       </c>
       <c r="Q43">
-        <v>23.2754481981239</v>
+        <v>23.27544819454866</v>
       </c>
       <c r="R43">
-        <v>0.7259403648356724</v>
+        <v>0.7259403644686389</v>
       </c>
       <c r="S43">
-        <v>0.5917854990805922</v>
+        <v>0.5917854992086604</v>
       </c>
       <c r="T43">
-        <v>24.43665044720631</v>
+        <v>24.43665047033842</v>
       </c>
       <c r="U43">
-        <v>0.7571791451578468</v>
+        <v>0.7571791454238677</v>
       </c>
       <c r="V43">
-        <v>0.5499871159851841</v>
+        <v>0.5499871151429566</v>
       </c>
       <c r="W43">
-        <v>24.53316526377354</v>
+        <v>24.53316529333671</v>
       </c>
       <c r="X43">
-        <v>0.7788414061450253</v>
+        <v>0.7788414077843024</v>
       </c>
       <c r="Y43">
-        <v>0.546323083656601</v>
+        <v>0.5463230825735366</v>
       </c>
       <c r="Z43">
-        <v>25.23350918494233</v>
+        <v>25.23350919167495</v>
       </c>
       <c r="AA43">
-        <v>0.8037869263306345</v>
+        <v>0.8037869288504806</v>
       </c>
       <c r="AB43">
-        <v>0.5200912033896373</v>
+        <v>0.5200912031468977</v>
       </c>
       <c r="AC43">
-        <v>25.76698196765998</v>
+        <v>25.7669818250428</v>
       </c>
       <c r="AD43">
-        <v>0.8175071837806387</v>
+        <v>0.8175071863120069</v>
       </c>
       <c r="AE43">
-        <v>0.4995073213625885</v>
+        <v>0.4995073269353105</v>
       </c>
       <c r="AF43">
-        <v>26.80709707526522</v>
+        <v>26.80709681272984</v>
       </c>
       <c r="AG43">
-        <v>0.8386567458185377</v>
+        <v>0.8386567468447788</v>
       </c>
       <c r="AH43">
-        <v>0.4582997340494743</v>
+        <v>0.4582997447414868</v>
       </c>
       <c r="AI43">
-        <v>28.23290723267012</v>
+        <v>28.23290704532224</v>
       </c>
       <c r="AJ43">
-        <v>0.8669944780684178</v>
+        <v>0.866994479100287</v>
       </c>
       <c r="AK43">
-        <v>0.3990492084740457</v>
+        <v>0.3990492165420338</v>
       </c>
       <c r="AL43">
-        <v>29.60552968977899</v>
+        <v>29.60552971933608</v>
       </c>
       <c r="AM43">
-        <v>0.883769512092448</v>
+        <v>0.8837695154590711</v>
       </c>
       <c r="AN43">
-        <v>0.3391063539165919</v>
+        <v>0.3391063526096236</v>
       </c>
       <c r="AO43">
-        <v>30.7043944664307</v>
+        <v>30.70439480869582</v>
       </c>
       <c r="AP43">
-        <v>0.8975871751366885</v>
+        <v>0.8975871820087352</v>
       </c>
       <c r="AQ43">
-        <v>0.2891660743689997</v>
+        <v>0.2891660584863238</v>
       </c>
       <c r="AR43">
-        <v>31.10324955762805</v>
+        <v>31.1032497581669</v>
       </c>
       <c r="AS43">
-        <v>0.9090488446200516</v>
+        <v>0.9090488525643271</v>
       </c>
       <c r="AT43">
-        <v>0.2705505521415412</v>
+        <v>0.2705505427638978</v>
       </c>
       <c r="AU43">
-        <v>31.18145538853662</v>
+        <v>31.18145549051237</v>
       </c>
       <c r="AV43">
-        <v>0.9204252326123947</v>
+        <v>0.9204252433592552</v>
       </c>
       <c r="AW43">
-        <v>0.2667886983454261</v>
+        <v>0.2667886936276218</v>
       </c>
       <c r="AX43">
-        <v>31.5341403794124</v>
+        <v>31.53414017766568</v>
       </c>
       <c r="AY43">
-        <v>0.9274162461382027</v>
+        <v>0.9274162547352472</v>
       </c>
       <c r="AZ43">
-        <v>0.2501311960359755</v>
+        <v>0.2501312055311742</v>
       </c>
     </row>
   </sheetData>
